--- a/STUDIO/org.openl.rules.test/test-resources/functionality/properties_all_table_type_allowed.xlsx
+++ b/STUDIO/org.openl.rules.test/test-resources/functionality/properties_all_table_type_allowed.xlsx
@@ -16,7 +16,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="B102" authorId="0">
+    <comment ref="B99" authorId="0">
       <text>
         <r>
           <rPr>
@@ -29,7 +29,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F104" authorId="0">
+    <comment ref="F101" authorId="0">
       <text>
         <r>
           <rPr>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="233">
   <si>
     <t>Spreadsheet SpreadsheetResult SpreadsheetTable (ByteValue a_byte)</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>parallel</t>
-  </si>
-  <si>
-    <t>cacheable</t>
   </si>
   <si>
     <t>buildPhase</t>
@@ -1412,12 +1409,12 @@
     <xf numFmtId="0" fontId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1463,10 +1460,10 @@
     <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -2762,7 +2759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.85156" style="1" customWidth="1"/>
@@ -2841,10 +2838,10 @@
       <c r="C6" t="s" s="6">
         <v>4</v>
       </c>
-      <c r="D6" t="b" s="11">
-        <v>1</v>
-      </c>
-      <c r="E6" s="17"/>
+      <c r="D6" t="s" s="17">
+        <v>5</v>
+      </c>
+      <c r="E6" s="18"/>
       <c r="F6" s="13"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -2853,12 +2850,12 @@
       <c r="A7" s="5"/>
       <c r="B7" s="14"/>
       <c r="C7" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s" s="18">
         <v>6</v>
       </c>
-      <c r="E7" s="17"/>
+      <c r="D7" t="s" s="17">
+        <v>7</v>
+      </c>
+      <c r="E7" s="18"/>
       <c r="F7" s="13"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -2867,12 +2864,12 @@
       <c r="A8" s="5"/>
       <c r="B8" s="14"/>
       <c r="C8" t="s" s="6">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s" s="18">
         <v>8</v>
       </c>
-      <c r="E8" s="17"/>
+      <c r="D8" t="s" s="17">
+        <v>9</v>
+      </c>
+      <c r="E8" s="18"/>
       <c r="F8" s="13"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -2881,12 +2878,12 @@
       <c r="A9" s="5"/>
       <c r="B9" s="14"/>
       <c r="C9" t="s" s="6">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s" s="18">
         <v>10</v>
       </c>
-      <c r="E9" s="17"/>
+      <c r="D9" t="s" s="17">
+        <v>11</v>
+      </c>
+      <c r="E9" s="18"/>
       <c r="F9" s="13"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -2895,12 +2892,12 @@
       <c r="A10" s="5"/>
       <c r="B10" s="14"/>
       <c r="C10" t="s" s="6">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s" s="18">
         <v>12</v>
       </c>
-      <c r="E10" s="17"/>
+      <c r="D10" t="s" s="17">
+        <v>13</v>
+      </c>
+      <c r="E10" s="18"/>
       <c r="F10" s="13"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -2909,12 +2906,12 @@
       <c r="A11" s="5"/>
       <c r="B11" s="14"/>
       <c r="C11" t="s" s="6">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s" s="18">
         <v>14</v>
       </c>
-      <c r="E11" s="17"/>
+      <c r="D11" t="s" s="17">
+        <v>15</v>
+      </c>
+      <c r="E11" s="18"/>
       <c r="F11" s="13"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -2923,12 +2920,12 @@
       <c r="A12" s="5"/>
       <c r="B12" s="14"/>
       <c r="C12" t="s" s="6">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s" s="18">
         <v>16</v>
       </c>
-      <c r="E12" s="17"/>
+      <c r="D12" t="s" s="17">
+        <v>17</v>
+      </c>
+      <c r="E12" s="18"/>
       <c r="F12" s="13"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -2937,12 +2934,12 @@
       <c r="A13" s="5"/>
       <c r="B13" s="14"/>
       <c r="C13" t="s" s="6">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s" s="18">
         <v>18</v>
       </c>
-      <c r="E13" s="17"/>
+      <c r="D13" t="s" s="17">
+        <v>19</v>
+      </c>
+      <c r="E13" s="18"/>
       <c r="F13" s="13"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -2951,12 +2948,12 @@
       <c r="A14" s="5"/>
       <c r="B14" s="14"/>
       <c r="C14" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s" s="18">
         <v>20</v>
       </c>
-      <c r="E14" s="17"/>
+      <c r="D14" t="s" s="17">
+        <v>21</v>
+      </c>
+      <c r="E14" s="18"/>
       <c r="F14" s="13"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -2965,12 +2962,12 @@
       <c r="A15" s="5"/>
       <c r="B15" s="14"/>
       <c r="C15" t="s" s="6">
-        <v>21</v>
-      </c>
-      <c r="D15" t="s" s="18">
         <v>22</v>
       </c>
-      <c r="E15" s="17"/>
+      <c r="D15" t="s" s="17">
+        <v>23</v>
+      </c>
+      <c r="E15" s="18"/>
       <c r="F15" s="13"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -2979,12 +2976,12 @@
       <c r="A16" s="5"/>
       <c r="B16" s="14"/>
       <c r="C16" t="s" s="6">
-        <v>23</v>
-      </c>
-      <c r="D16" t="s" s="18">
         <v>24</v>
       </c>
-      <c r="E16" s="17"/>
+      <c r="D16" t="s" s="17">
+        <v>25</v>
+      </c>
+      <c r="E16" s="18"/>
       <c r="F16" s="13"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -2993,12 +2990,12 @@
       <c r="A17" s="5"/>
       <c r="B17" s="14"/>
       <c r="C17" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s" s="18">
         <v>26</v>
       </c>
-      <c r="E17" s="17"/>
+      <c r="D17" t="s" s="17">
+        <v>27</v>
+      </c>
+      <c r="E17" s="18"/>
       <c r="F17" s="13"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -3007,12 +3004,12 @@
       <c r="A18" s="5"/>
       <c r="B18" s="14"/>
       <c r="C18" t="s" s="6">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s" s="18">
         <v>28</v>
       </c>
-      <c r="E18" s="17"/>
+      <c r="D18" t="s" s="17">
+        <v>29</v>
+      </c>
+      <c r="E18" s="18"/>
       <c r="F18" s="13"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -3021,12 +3018,12 @@
       <c r="A19" s="5"/>
       <c r="B19" s="14"/>
       <c r="C19" t="s" s="6">
-        <v>29</v>
-      </c>
-      <c r="D19" t="s" s="18">
         <v>30</v>
       </c>
-      <c r="E19" s="17"/>
+      <c r="D19" s="19">
+        <v>41298</v>
+      </c>
+      <c r="E19" s="18"/>
       <c r="F19" s="13"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -3038,9 +3035,9 @@
         <v>31</v>
       </c>
       <c r="D20" s="19">
-        <v>41298</v>
-      </c>
-      <c r="E20" s="17"/>
+        <v>41275</v>
+      </c>
+      <c r="E20" s="18"/>
       <c r="F20" s="13"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -3052,9 +3049,9 @@
         <v>32</v>
       </c>
       <c r="D21" s="19">
-        <v>41275</v>
-      </c>
-      <c r="E21" s="17"/>
+        <v>41670</v>
+      </c>
+      <c r="E21" s="18"/>
       <c r="F21" s="13"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -3066,9 +3063,9 @@
         <v>33</v>
       </c>
       <c r="D22" s="19">
-        <v>41670</v>
-      </c>
-      <c r="E22" s="17"/>
+        <v>41646</v>
+      </c>
+      <c r="E22" s="18"/>
       <c r="F22" s="13"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -3079,10 +3076,10 @@
       <c r="C23" t="s" s="6">
         <v>34</v>
       </c>
-      <c r="D23" s="19">
-        <v>41646</v>
-      </c>
-      <c r="E23" s="17"/>
+      <c r="D23" t="s" s="17">
+        <v>35</v>
+      </c>
+      <c r="E23" s="18"/>
       <c r="F23" s="13"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -3091,12 +3088,12 @@
       <c r="A24" s="5"/>
       <c r="B24" s="14"/>
       <c r="C24" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D24" t="s" s="18">
         <v>36</v>
       </c>
-      <c r="E24" s="17"/>
+      <c r="D24" t="s" s="17">
+        <v>37</v>
+      </c>
+      <c r="E24" s="18"/>
       <c r="F24" s="13"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -3105,12 +3102,12 @@
       <c r="A25" s="5"/>
       <c r="B25" s="14"/>
       <c r="C25" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D25" t="s" s="18">
         <v>38</v>
       </c>
-      <c r="E25" s="17"/>
+      <c r="D25" t="s" s="17">
+        <v>39</v>
+      </c>
+      <c r="E25" s="18"/>
       <c r="F25" s="13"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -3119,12 +3116,12 @@
       <c r="A26" s="5"/>
       <c r="B26" s="14"/>
       <c r="C26" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D26" t="s" s="18">
         <v>40</v>
       </c>
-      <c r="E26" s="17"/>
+      <c r="D26" t="s" s="17">
+        <v>41</v>
+      </c>
+      <c r="E26" s="18"/>
       <c r="F26" s="13"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -3132,55 +3129,57 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="5"/>
       <c r="B27" s="14"/>
-      <c r="C27" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D27" t="s" s="18">
+      <c r="C27" t="s" s="20">
         <v>42</v>
       </c>
-      <c r="E27" s="17"/>
+      <c r="D27" t="s" s="17">
+        <v>43</v>
+      </c>
+      <c r="E27" s="18"/>
       <c r="F27" s="13"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="5"/>
-      <c r="B28" s="14"/>
-      <c r="C28" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D28" t="s" s="18">
+      <c r="B28" s="21"/>
+      <c r="C28" t="s" s="6">
         <v>44</v>
       </c>
-      <c r="E28" s="17"/>
+      <c r="D28" s="19">
+        <v>41648</v>
+      </c>
+      <c r="E28" s="18"/>
       <c r="F28" s="13"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="9" customHeight="1" hidden="1">
       <c r="A29" s="5"/>
-      <c r="B29" s="21"/>
-      <c r="C29" t="s" s="6">
+      <c r="B29" t="s" s="22">
         <v>45</v>
       </c>
-      <c r="D29" s="19">
-        <v>41648</v>
-      </c>
-      <c r="E29" s="17"/>
-      <c r="F29" s="13"/>
+      <c r="C29" t="s" s="23">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s" s="23">
+        <v>47</v>
+      </c>
+      <c r="E29" s="24"/>
+      <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
     <row r="30" ht="9" customHeight="1" hidden="1">
       <c r="A30" s="5"/>
-      <c r="B30" t="s" s="22">
-        <v>46</v>
-      </c>
-      <c r="C30" t="s" s="23">
-        <v>47</v>
-      </c>
-      <c r="D30" t="s" s="23">
+      <c r="B30" t="s" s="25">
         <v>48</v>
+      </c>
+      <c r="C30" t="s" s="26">
+        <v>49</v>
+      </c>
+      <c r="D30" s="27">
+        <v>200</v>
       </c>
       <c r="E30" s="24"/>
       <c r="F30" s="2"/>
@@ -3190,13 +3189,13 @@
     <row r="31" ht="9" customHeight="1" hidden="1">
       <c r="A31" s="5"/>
       <c r="B31" t="s" s="25">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s" s="26">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D31" s="27">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E31" s="24"/>
       <c r="F31" s="2"/>
@@ -3206,13 +3205,13 @@
     <row r="32" ht="9" customHeight="1" hidden="1">
       <c r="A32" s="5"/>
       <c r="B32" t="s" s="25">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C32" t="s" s="26">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D32" s="27">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E32" s="24"/>
       <c r="F32" s="2"/>
@@ -3222,13 +3221,13 @@
     <row r="33" ht="9" customHeight="1" hidden="1">
       <c r="A33" s="5"/>
       <c r="B33" t="s" s="25">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s" s="26">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D33" s="27">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E33" s="24"/>
       <c r="F33" s="2"/>
@@ -3238,13 +3237,13 @@
     <row r="34" ht="9" customHeight="1" hidden="1">
       <c r="A34" s="5"/>
       <c r="B34" t="s" s="25">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s" s="26">
-        <v>56</v>
-      </c>
-      <c r="D34" s="27">
-        <v>500</v>
+        <v>57</v>
+      </c>
+      <c r="D34" t="s" s="26">
+        <v>58</v>
       </c>
       <c r="E34" s="24"/>
       <c r="F34" s="2"/>
@@ -3254,13 +3253,13 @@
     <row r="35" ht="9" customHeight="1" hidden="1">
       <c r="A35" s="5"/>
       <c r="B35" t="s" s="25">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C35" t="s" s="26">
-        <v>58</v>
-      </c>
-      <c r="D35" t="s" s="26">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="D35" s="27">
+        <v>700</v>
       </c>
       <c r="E35" s="24"/>
       <c r="F35" s="2"/>
@@ -3270,51 +3269,47 @@
     <row r="36" ht="9" customHeight="1" hidden="1">
       <c r="A36" s="5"/>
       <c r="B36" t="s" s="25">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s" s="26">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D36" s="27">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E36" s="24"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" ht="9" customHeight="1" hidden="1">
-      <c r="A37" s="5"/>
-      <c r="B37" t="s" s="25">
-        <v>62</v>
-      </c>
-      <c r="C37" t="s" s="26">
-        <v>63</v>
-      </c>
-      <c r="D37" s="27">
-        <v>800</v>
-      </c>
-      <c r="E37" s="24"/>
+    <row r="37" ht="13.65" customHeight="1">
+      <c r="A37" s="2"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
     <row r="38" ht="13.65" customHeight="1">
       <c r="A38" s="2"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" ht="13.65" customHeight="1">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="2"/>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="5"/>
+      <c r="B39" t="s" s="6">
+        <v>63</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="29"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -3322,22 +3317,24 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="5"/>
       <c r="B40" t="s" s="6">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s" s="6">
         <v>64</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="2"/>
+      <c r="D40" t="b" s="30">
+        <v>1</v>
+      </c>
+      <c r="E40" s="31"/>
+      <c r="F40" s="9"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="5"/>
-      <c r="B41" t="s" s="6">
-        <v>1</v>
-      </c>
+      <c r="B41" s="7"/>
       <c r="C41" t="s" s="6">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D41" t="b" s="30">
         <v>1</v>
@@ -3351,40 +3348,40 @@
       <c r="A42" s="5"/>
       <c r="B42" s="7"/>
       <c r="C42" t="s" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="b" s="30">
         <v>1</v>
       </c>
-      <c r="E42" s="31"/>
+      <c r="E42" s="32"/>
       <c r="F42" s="9"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="5"/>
-      <c r="B43" s="7"/>
+      <c r="B43" s="33"/>
       <c r="C43" t="s" s="6">
-        <v>3</v>
-      </c>
-      <c r="D43" t="b" s="30">
-        <v>1</v>
-      </c>
-      <c r="E43" s="32"/>
-      <c r="F43" s="9"/>
+        <v>65</v>
+      </c>
+      <c r="D43" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="E43" s="35"/>
+      <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="5"/>
-      <c r="B44" s="33"/>
+      <c r="B44" s="7"/>
       <c r="C44" t="s" s="6">
         <v>4</v>
       </c>
-      <c r="D44" t="b" s="30">
-        <v>1</v>
-      </c>
-      <c r="E44" s="34"/>
+      <c r="D44" t="s" s="34">
+        <v>5</v>
+      </c>
+      <c r="E44" s="13"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -3393,9 +3390,9 @@
       <c r="A45" s="5"/>
       <c r="B45" s="7"/>
       <c r="C45" t="s" s="6">
-        <v>66</v>
-      </c>
-      <c r="D45" t="s" s="35">
+        <v>6</v>
+      </c>
+      <c r="D45" t="s" s="34">
         <v>67</v>
       </c>
       <c r="E45" s="13"/>
@@ -3407,10 +3404,10 @@
       <c r="A46" s="5"/>
       <c r="B46" s="7"/>
       <c r="C46" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D46" t="s" s="35">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="D46" t="s" s="34">
+        <v>9</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="2"/>
@@ -3421,10 +3418,10 @@
       <c r="A47" s="5"/>
       <c r="B47" s="7"/>
       <c r="C47" t="s" s="6">
-        <v>7</v>
-      </c>
-      <c r="D47" t="s" s="35">
-        <v>68</v>
+        <v>10</v>
+      </c>
+      <c r="D47" t="s" s="34">
+        <v>11</v>
       </c>
       <c r="E47" s="13"/>
       <c r="F47" s="2"/>
@@ -3435,10 +3432,10 @@
       <c r="A48" s="5"/>
       <c r="B48" s="7"/>
       <c r="C48" t="s" s="6">
-        <v>9</v>
-      </c>
-      <c r="D48" t="s" s="35">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="D48" t="s" s="34">
+        <v>13</v>
       </c>
       <c r="E48" s="13"/>
       <c r="F48" s="2"/>
@@ -3449,10 +3446,10 @@
       <c r="A49" s="5"/>
       <c r="B49" s="7"/>
       <c r="C49" t="s" s="6">
-        <v>11</v>
-      </c>
-      <c r="D49" t="s" s="35">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="D49" t="s" s="34">
+        <v>15</v>
       </c>
       <c r="E49" s="13"/>
       <c r="F49" s="2"/>
@@ -3463,10 +3460,10 @@
       <c r="A50" s="5"/>
       <c r="B50" s="7"/>
       <c r="C50" t="s" s="6">
-        <v>13</v>
-      </c>
-      <c r="D50" t="s" s="35">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="D50" t="s" s="34">
+        <v>17</v>
       </c>
       <c r="E50" s="13"/>
       <c r="F50" s="2"/>
@@ -3477,10 +3474,10 @@
       <c r="A51" s="5"/>
       <c r="B51" s="7"/>
       <c r="C51" t="s" s="6">
-        <v>15</v>
-      </c>
-      <c r="D51" t="s" s="35">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="D51" t="s" s="34">
+        <v>19</v>
       </c>
       <c r="E51" s="13"/>
       <c r="F51" s="2"/>
@@ -3491,10 +3488,10 @@
       <c r="A52" s="5"/>
       <c r="B52" s="7"/>
       <c r="C52" t="s" s="6">
-        <v>17</v>
-      </c>
-      <c r="D52" t="s" s="35">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="D52" t="s" s="34">
+        <v>21</v>
       </c>
       <c r="E52" s="13"/>
       <c r="F52" s="2"/>
@@ -3505,10 +3502,10 @@
       <c r="A53" s="5"/>
       <c r="B53" s="7"/>
       <c r="C53" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="D53" t="s" s="35">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="D53" t="s" s="34">
+        <v>23</v>
       </c>
       <c r="E53" s="13"/>
       <c r="F53" s="2"/>
@@ -3519,10 +3516,10 @@
       <c r="A54" s="5"/>
       <c r="B54" s="7"/>
       <c r="C54" t="s" s="6">
-        <v>21</v>
-      </c>
-      <c r="D54" t="s" s="35">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="D54" t="s" s="34">
+        <v>25</v>
       </c>
       <c r="E54" s="13"/>
       <c r="F54" s="2"/>
@@ -3533,10 +3530,10 @@
       <c r="A55" s="5"/>
       <c r="B55" s="7"/>
       <c r="C55" t="s" s="6">
-        <v>23</v>
-      </c>
-      <c r="D55" t="s" s="35">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="D55" t="s" s="34">
+        <v>27</v>
       </c>
       <c r="E55" s="13"/>
       <c r="F55" s="2"/>
@@ -3547,10 +3544,10 @@
       <c r="A56" s="5"/>
       <c r="B56" s="7"/>
       <c r="C56" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="D56" t="s" s="35">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="D56" t="s" s="34">
+        <v>29</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="2"/>
@@ -3561,10 +3558,10 @@
       <c r="A57" s="5"/>
       <c r="B57" s="7"/>
       <c r="C57" t="s" s="6">
-        <v>27</v>
-      </c>
-      <c r="D57" t="s" s="35">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="D57" s="36">
+        <v>41298</v>
       </c>
       <c r="E57" s="13"/>
       <c r="F57" s="2"/>
@@ -3575,10 +3572,10 @@
       <c r="A58" s="5"/>
       <c r="B58" s="7"/>
       <c r="C58" t="s" s="6">
-        <v>29</v>
-      </c>
-      <c r="D58" t="s" s="35">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="D58" s="36">
+        <v>41275</v>
       </c>
       <c r="E58" s="13"/>
       <c r="F58" s="2"/>
@@ -3589,10 +3586,10 @@
       <c r="A59" s="5"/>
       <c r="B59" s="7"/>
       <c r="C59" t="s" s="6">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D59" s="36">
-        <v>41298</v>
+        <v>41670</v>
       </c>
       <c r="E59" s="13"/>
       <c r="F59" s="2"/>
@@ -3603,10 +3600,10 @@
       <c r="A60" s="5"/>
       <c r="B60" s="7"/>
       <c r="C60" t="s" s="6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D60" s="36">
-        <v>41275</v>
+        <v>41646</v>
       </c>
       <c r="E60" s="13"/>
       <c r="F60" s="2"/>
@@ -3617,10 +3614,10 @@
       <c r="A61" s="5"/>
       <c r="B61" s="7"/>
       <c r="C61" t="s" s="6">
-        <v>33</v>
-      </c>
-      <c r="D61" s="36">
-        <v>41670</v>
+        <v>34</v>
+      </c>
+      <c r="D61" t="s" s="34">
+        <v>35</v>
       </c>
       <c r="E61" s="13"/>
       <c r="F61" s="2"/>
@@ -3631,10 +3628,10 @@
       <c r="A62" s="5"/>
       <c r="B62" s="7"/>
       <c r="C62" t="s" s="6">
-        <v>34</v>
-      </c>
-      <c r="D62" s="36">
-        <v>41646</v>
+        <v>36</v>
+      </c>
+      <c r="D62" t="s" s="34">
+        <v>37</v>
       </c>
       <c r="E62" s="13"/>
       <c r="F62" s="2"/>
@@ -3645,10 +3642,10 @@
       <c r="A63" s="5"/>
       <c r="B63" s="7"/>
       <c r="C63" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D63" t="s" s="35">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="D63" t="s" s="34">
+        <v>39</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="2"/>
@@ -3659,10 +3656,10 @@
       <c r="A64" s="5"/>
       <c r="B64" s="7"/>
       <c r="C64" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D64" t="s" s="35">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="D64" t="s" s="34">
+        <v>41</v>
       </c>
       <c r="E64" s="13"/>
       <c r="F64" s="2"/>
@@ -3672,11 +3669,11 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="5"/>
       <c r="B65" s="7"/>
-      <c r="C65" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D65" t="s" s="35">
-        <v>40</v>
+      <c r="C65" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D65" t="s" s="34">
+        <v>43</v>
       </c>
       <c r="E65" s="13"/>
       <c r="F65" s="2"/>
@@ -3687,10 +3684,10 @@
       <c r="A66" s="5"/>
       <c r="B66" s="7"/>
       <c r="C66" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D66" t="s" s="35">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="D66" s="36">
+        <v>41648</v>
       </c>
       <c r="E66" s="13"/>
       <c r="F66" s="2"/>
@@ -3700,115 +3697,115 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="5"/>
       <c r="B67" s="7"/>
-      <c r="C67" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D67" t="s" s="35">
-        <v>44</v>
+      <c r="C67" t="s" s="6">
+        <v>68</v>
+      </c>
+      <c r="D67" s="36">
+        <v>40919</v>
       </c>
       <c r="E67" s="13"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" ht="15" customHeight="1">
+    <row r="68" ht="9" customHeight="1" hidden="1">
       <c r="A68" s="5"/>
-      <c r="B68" s="7"/>
+      <c r="B68" t="s" s="6">
+        <v>69</v>
+      </c>
       <c r="C68" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D68" s="36">
-        <v>41648</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D68" s="7"/>
       <c r="E68" s="13"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" ht="15" customHeight="1">
+    <row r="69" ht="9" customHeight="1" hidden="1">
       <c r="A69" s="5"/>
-      <c r="B69" s="7"/>
+      <c r="B69" t="s" s="6">
+        <v>71</v>
+      </c>
       <c r="C69" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D69" s="36">
-        <v>40919</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="D69" s="7"/>
       <c r="E69" s="13"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" ht="9" customHeight="1" hidden="1">
-      <c r="A70" s="5"/>
-      <c r="B70" t="s" s="6">
-        <v>70</v>
-      </c>
-      <c r="C70" t="s" s="6">
-        <v>71</v>
-      </c>
-      <c r="D70" s="7"/>
-      <c r="E70" s="13"/>
+    <row r="70" ht="13.65" customHeight="1">
+      <c r="A70" s="2"/>
+      <c r="B70" s="37"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" ht="9" customHeight="1" hidden="1">
-      <c r="A71" s="5"/>
-      <c r="B71" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="C71" t="s" s="6">
-        <v>73</v>
-      </c>
-      <c r="D71" s="7"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="2"/>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="38"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" ht="13.65" customHeight="1">
-      <c r="A72" s="2"/>
-      <c r="B72" s="37"/>
-      <c r="C72" s="28"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
+    <row r="72" ht="13.5" customHeight="1">
+      <c r="A72" s="5"/>
+      <c r="B72" t="s" s="41">
+        <v>73</v>
+      </c>
+      <c r="C72" s="42"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="13"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="38"/>
-      <c r="B73" s="39"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="2"/>
+    <row r="73" ht="13.5" customHeight="1">
+      <c r="A73" s="5"/>
+      <c r="B73" t="s" s="10">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s" s="6">
+        <v>2</v>
+      </c>
+      <c r="D73" t="b" s="43">
+        <v>1</v>
+      </c>
+      <c r="E73" s="44"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="13"/>
       <c r="H73" s="2"/>
     </row>
     <row r="74" ht="13.5" customHeight="1">
       <c r="A74" s="5"/>
-      <c r="B74" t="s" s="41">
-        <v>74</v>
-      </c>
-      <c r="C74" s="42"/>
-      <c r="D74" s="42"/>
-      <c r="E74" s="42"/>
-      <c r="F74" s="42"/>
+      <c r="B74" s="14"/>
+      <c r="C74" t="s" s="6">
+        <v>3</v>
+      </c>
+      <c r="D74" t="b" s="43">
+        <v>1</v>
+      </c>
+      <c r="E74" s="44"/>
+      <c r="F74" s="45"/>
       <c r="G74" s="13"/>
       <c r="H74" s="2"/>
     </row>
     <row r="75" ht="13.5" customHeight="1">
       <c r="A75" s="5"/>
-      <c r="B75" t="s" s="10">
-        <v>1</v>
-      </c>
+      <c r="B75" s="16"/>
       <c r="C75" t="s" s="6">
-        <v>2</v>
-      </c>
-      <c r="D75" t="b" s="43">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D75" t="s" s="46">
+        <v>5</v>
       </c>
       <c r="E75" s="44"/>
       <c r="F75" s="45"/>
@@ -3819,10 +3816,10 @@
       <c r="A76" s="5"/>
       <c r="B76" s="14"/>
       <c r="C76" t="s" s="6">
-        <v>3</v>
-      </c>
-      <c r="D76" t="b" s="43">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D76" t="s" s="46">
+        <v>74</v>
       </c>
       <c r="E76" s="44"/>
       <c r="F76" s="45"/>
@@ -3831,12 +3828,12 @@
     </row>
     <row r="77" ht="13.5" customHeight="1">
       <c r="A77" s="5"/>
-      <c r="B77" s="16"/>
+      <c r="B77" s="14"/>
       <c r="C77" t="s" s="6">
-        <v>4</v>
-      </c>
-      <c r="D77" t="b" s="43">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D77" t="s" s="46">
+        <v>9</v>
       </c>
       <c r="E77" s="44"/>
       <c r="F77" s="45"/>
@@ -3847,10 +3844,10 @@
       <c r="A78" s="5"/>
       <c r="B78" s="14"/>
       <c r="C78" t="s" s="6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D78" t="s" s="46">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E78" s="44"/>
       <c r="F78" s="45"/>
@@ -3861,10 +3858,10 @@
       <c r="A79" s="5"/>
       <c r="B79" s="14"/>
       <c r="C79" t="s" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s" s="46">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="E79" s="44"/>
       <c r="F79" s="45"/>
@@ -3875,10 +3872,10 @@
       <c r="A80" s="5"/>
       <c r="B80" s="14"/>
       <c r="C80" t="s" s="6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s" s="46">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E80" s="44"/>
       <c r="F80" s="45"/>
@@ -3889,10 +3886,10 @@
       <c r="A81" s="5"/>
       <c r="B81" s="14"/>
       <c r="C81" t="s" s="6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D81" t="s" s="46">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E81" s="44"/>
       <c r="F81" s="45"/>
@@ -3903,10 +3900,10 @@
       <c r="A82" s="5"/>
       <c r="B82" s="14"/>
       <c r="C82" t="s" s="6">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D82" t="s" s="46">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E82" s="44"/>
       <c r="F82" s="45"/>
@@ -3917,10 +3914,10 @@
       <c r="A83" s="5"/>
       <c r="B83" s="14"/>
       <c r="C83" t="s" s="6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D83" t="s" s="46">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E83" s="44"/>
       <c r="F83" s="45"/>
@@ -3931,10 +3928,10 @@
       <c r="A84" s="5"/>
       <c r="B84" s="14"/>
       <c r="C84" t="s" s="6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D84" t="s" s="46">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E84" s="44"/>
       <c r="F84" s="45"/>
@@ -3945,10 +3942,10 @@
       <c r="A85" s="5"/>
       <c r="B85" s="14"/>
       <c r="C85" t="s" s="6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D85" t="s" s="46">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E85" s="44"/>
       <c r="F85" s="45"/>
@@ -3959,10 +3956,10 @@
       <c r="A86" s="5"/>
       <c r="B86" s="14"/>
       <c r="C86" t="s" s="6">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D86" t="s" s="46">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E86" s="44"/>
       <c r="F86" s="45"/>
@@ -3973,10 +3970,10 @@
       <c r="A87" s="5"/>
       <c r="B87" s="14"/>
       <c r="C87" t="s" s="6">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D87" t="s" s="46">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E87" s="44"/>
       <c r="F87" s="45"/>
@@ -3987,10 +3984,10 @@
       <c r="A88" s="5"/>
       <c r="B88" s="14"/>
       <c r="C88" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="D88" t="s" s="46">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="D88" s="47">
+        <v>41298</v>
       </c>
       <c r="E88" s="44"/>
       <c r="F88" s="45"/>
@@ -4001,10 +3998,10 @@
       <c r="A89" s="5"/>
       <c r="B89" s="14"/>
       <c r="C89" t="s" s="6">
-        <v>27</v>
-      </c>
-      <c r="D89" t="s" s="46">
-        <v>28</v>
+        <v>31</v>
+      </c>
+      <c r="D89" s="47">
+        <v>41275</v>
       </c>
       <c r="E89" s="44"/>
       <c r="F89" s="45"/>
@@ -4015,10 +4012,10 @@
       <c r="A90" s="5"/>
       <c r="B90" s="14"/>
       <c r="C90" t="s" s="6">
-        <v>29</v>
-      </c>
-      <c r="D90" t="s" s="46">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="D90" s="47">
+        <v>41670</v>
       </c>
       <c r="E90" s="44"/>
       <c r="F90" s="45"/>
@@ -4029,10 +4026,10 @@
       <c r="A91" s="5"/>
       <c r="B91" s="14"/>
       <c r="C91" t="s" s="6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D91" s="47">
-        <v>41298</v>
+        <v>41646</v>
       </c>
       <c r="E91" s="44"/>
       <c r="F91" s="45"/>
@@ -4043,13 +4040,13 @@
       <c r="A92" s="5"/>
       <c r="B92" s="14"/>
       <c r="C92" t="s" s="6">
-        <v>32</v>
-      </c>
-      <c r="D92" s="47">
-        <v>41275</v>
-      </c>
-      <c r="E92" s="44"/>
-      <c r="F92" s="45"/>
+        <v>34</v>
+      </c>
+      <c r="D92" t="s" s="46">
+        <v>35</v>
+      </c>
+      <c r="E92" s="48"/>
+      <c r="F92" s="49"/>
       <c r="G92" s="13"/>
       <c r="H92" s="2"/>
     </row>
@@ -4057,13 +4054,13 @@
       <c r="A93" s="5"/>
       <c r="B93" s="14"/>
       <c r="C93" t="s" s="6">
-        <v>33</v>
-      </c>
-      <c r="D93" s="47">
-        <v>41670</v>
-      </c>
-      <c r="E93" s="44"/>
-      <c r="F93" s="45"/>
+        <v>36</v>
+      </c>
+      <c r="D93" t="s" s="46">
+        <v>37</v>
+      </c>
+      <c r="E93" s="48"/>
+      <c r="F93" s="49"/>
       <c r="G93" s="13"/>
       <c r="H93" s="2"/>
     </row>
@@ -4071,13 +4068,13 @@
       <c r="A94" s="5"/>
       <c r="B94" s="14"/>
       <c r="C94" t="s" s="6">
-        <v>34</v>
-      </c>
-      <c r="D94" s="47">
-        <v>41646</v>
-      </c>
-      <c r="E94" s="44"/>
-      <c r="F94" s="45"/>
+        <v>38</v>
+      </c>
+      <c r="D94" t="s" s="46">
+        <v>39</v>
+      </c>
+      <c r="E94" s="48"/>
+      <c r="F94" s="49"/>
       <c r="G94" s="13"/>
       <c r="H94" s="2"/>
     </row>
@@ -4085,10 +4082,10 @@
       <c r="A95" s="5"/>
       <c r="B95" s="14"/>
       <c r="C95" t="s" s="6">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D95" t="s" s="46">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E95" s="48"/>
       <c r="F95" s="49"/>
@@ -4098,11 +4095,11 @@
     <row r="96" ht="13.5" customHeight="1">
       <c r="A96" s="5"/>
       <c r="B96" s="14"/>
-      <c r="C96" t="s" s="6">
-        <v>37</v>
+      <c r="C96" t="s" s="20">
+        <v>42</v>
       </c>
       <c r="D96" t="s" s="46">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E96" s="48"/>
       <c r="F96" s="49"/>
@@ -4113,175 +4110,177 @@
       <c r="A97" s="5"/>
       <c r="B97" s="14"/>
       <c r="C97" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D97" t="s" s="46">
-        <v>40</v>
-      </c>
-      <c r="E97" s="48"/>
-      <c r="F97" s="49"/>
+        <v>44</v>
+      </c>
+      <c r="D97" s="47">
+        <v>41648</v>
+      </c>
+      <c r="E97" s="44"/>
+      <c r="F97" s="45"/>
       <c r="G97" s="13"/>
       <c r="H97" s="2"/>
     </row>
     <row r="98" ht="13.5" customHeight="1">
       <c r="A98" s="5"/>
-      <c r="B98" s="14"/>
+      <c r="B98" s="21"/>
       <c r="C98" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D98" t="s" s="46">
-        <v>42</v>
-      </c>
-      <c r="E98" s="48"/>
-      <c r="F98" s="49"/>
+        <v>68</v>
+      </c>
+      <c r="D98" s="47">
+        <v>40919</v>
+      </c>
+      <c r="E98" s="44"/>
+      <c r="F98" s="45"/>
       <c r="G98" s="13"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" ht="13.5" customHeight="1">
+    <row r="99" ht="13.5" customHeight="1" hidden="1">
       <c r="A99" s="5"/>
-      <c r="B99" s="14"/>
-      <c r="C99" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D99" t="s" s="46">
-        <v>44</v>
-      </c>
-      <c r="E99" s="48"/>
-      <c r="F99" s="49"/>
+      <c r="B99" t="s" s="50">
+        <v>75</v>
+      </c>
+      <c r="C99" t="s" s="50">
+        <v>76</v>
+      </c>
+      <c r="D99" t="s" s="50">
+        <v>77</v>
+      </c>
+      <c r="E99" t="s" s="50">
+        <v>78</v>
+      </c>
+      <c r="F99" t="s" s="50">
+        <v>79</v>
+      </c>
       <c r="G99" s="13"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" ht="13.5" customHeight="1">
+    <row r="100" ht="27" customHeight="1" hidden="1">
       <c r="A100" s="5"/>
-      <c r="B100" s="14"/>
-      <c r="C100" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D100" s="47">
-        <v>41648</v>
-      </c>
-      <c r="E100" s="44"/>
-      <c r="F100" s="45"/>
+      <c r="B100" t="s" s="51">
+        <v>80</v>
+      </c>
+      <c r="C100" t="s" s="51">
+        <v>76</v>
+      </c>
+      <c r="D100" t="s" s="51">
+        <v>77</v>
+      </c>
+      <c r="E100" t="s" s="51">
+        <v>78</v>
+      </c>
+      <c r="F100" t="s" s="52">
+        <v>79</v>
+      </c>
       <c r="G100" s="13"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" ht="13.5" customHeight="1">
+    <row r="101" ht="13.5" customHeight="1" hidden="1">
       <c r="A101" s="5"/>
-      <c r="B101" s="21"/>
-      <c r="C101" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D101" s="47">
-        <v>40919</v>
-      </c>
-      <c r="E101" s="44"/>
-      <c r="F101" s="45"/>
+      <c r="B101" s="53"/>
+      <c r="C101" t="s" s="54">
+        <v>81</v>
+      </c>
+      <c r="D101" t="s" s="55">
+        <v>82</v>
+      </c>
+      <c r="E101" t="s" s="55">
+        <v>83</v>
+      </c>
+      <c r="F101" s="56">
+        <v>1</v>
+      </c>
       <c r="G101" s="13"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" ht="13.5" customHeight="1">
+    <row r="102" ht="13.5" customHeight="1" hidden="1">
       <c r="A102" s="5"/>
-      <c r="B102" t="s" s="50">
-        <v>76</v>
-      </c>
-      <c r="C102" t="s" s="50">
-        <v>77</v>
-      </c>
-      <c r="D102" t="s" s="50">
-        <v>78</v>
-      </c>
-      <c r="E102" t="s" s="50">
-        <v>79</v>
-      </c>
-      <c r="F102" t="s" s="50">
-        <v>80</v>
+      <c r="B102" s="53"/>
+      <c r="C102" t="s" s="54">
+        <v>84</v>
+      </c>
+      <c r="D102" t="s" s="55">
+        <v>82</v>
+      </c>
+      <c r="E102" t="s" s="55">
+        <v>85</v>
+      </c>
+      <c r="F102" s="56">
+        <v>1</v>
       </c>
       <c r="G102" s="13"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" ht="27" customHeight="1">
-      <c r="A103" s="5"/>
-      <c r="B103" t="s" s="51">
-        <v>81</v>
-      </c>
-      <c r="C103" t="s" s="51">
-        <v>77</v>
-      </c>
-      <c r="D103" t="s" s="51">
-        <v>78</v>
-      </c>
-      <c r="E103" t="s" s="51">
-        <v>79</v>
-      </c>
-      <c r="F103" t="s" s="52">
-        <v>80</v>
-      </c>
-      <c r="G103" s="13"/>
+    <row r="103" ht="13.65" customHeight="1">
+      <c r="A103" s="2"/>
+      <c r="B103" s="28"/>
+      <c r="C103" s="28"/>
+      <c r="D103" s="28"/>
+      <c r="E103" s="28"/>
+      <c r="F103" s="28"/>
+      <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" ht="13.5" customHeight="1">
-      <c r="A104" s="5"/>
-      <c r="B104" s="53"/>
-      <c r="C104" t="s" s="54">
-        <v>82</v>
-      </c>
-      <c r="D104" t="s" s="55">
-        <v>83</v>
-      </c>
-      <c r="E104" t="s" s="55">
-        <v>84</v>
-      </c>
-      <c r="F104" s="56">
+    <row r="104" ht="13.65" customHeight="1">
+      <c r="A104" s="2"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="5"/>
+      <c r="B105" t="s" s="57">
+        <v>86</v>
+      </c>
+      <c r="C105" s="58"/>
+      <c r="D105" s="58"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="5"/>
+      <c r="B106" t="s" s="10">
         <v>1</v>
       </c>
-      <c r="G104" s="13"/>
-      <c r="H104" s="2"/>
-    </row>
-    <row r="105" ht="13.5" customHeight="1">
-      <c r="A105" s="5"/>
-      <c r="B105" s="53"/>
-      <c r="C105" t="s" s="54">
-        <v>85</v>
-      </c>
-      <c r="D105" t="s" s="55">
-        <v>83</v>
-      </c>
-      <c r="E105" t="s" s="55">
-        <v>86</v>
-      </c>
-      <c r="F105" s="56">
+      <c r="C106" t="s" s="6">
+        <v>2</v>
+      </c>
+      <c r="D106" t="b" s="30">
         <v>1</v>
       </c>
-      <c r="G105" s="13"/>
-      <c r="H105" s="2"/>
-    </row>
-    <row r="106" ht="13.65" customHeight="1">
-      <c r="A106" s="2"/>
-      <c r="B106" s="28"/>
-      <c r="C106" s="28"/>
-      <c r="D106" s="28"/>
-      <c r="E106" s="28"/>
-      <c r="F106" s="28"/>
+      <c r="E106" s="13"/>
+      <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" ht="13.65" customHeight="1">
-      <c r="A107" s="2"/>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="2"/>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="5"/>
+      <c r="B107" s="14"/>
+      <c r="C107" t="s" s="6">
+        <v>3</v>
+      </c>
+      <c r="D107" t="b" s="30">
+        <v>1</v>
+      </c>
+      <c r="E107" s="13"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="5"/>
-      <c r="B108" t="s" s="57">
-        <v>87</v>
-      </c>
-      <c r="C108" s="58"/>
-      <c r="D108" s="58"/>
+      <c r="B108" s="16"/>
+      <c r="C108" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D108" t="s" s="34">
+        <v>5</v>
+      </c>
       <c r="E108" s="13"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -4289,14 +4288,12 @@
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" s="5"/>
-      <c r="B109" t="s" s="10">
-        <v>1</v>
-      </c>
+      <c r="B109" s="14"/>
       <c r="C109" t="s" s="6">
-        <v>2</v>
-      </c>
-      <c r="D109" t="b" s="30">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="D109" t="s" s="34">
+        <v>87</v>
       </c>
       <c r="E109" s="13"/>
       <c r="F109" s="2"/>
@@ -4307,10 +4304,10 @@
       <c r="A110" s="5"/>
       <c r="B110" s="14"/>
       <c r="C110" t="s" s="6">
-        <v>3</v>
-      </c>
-      <c r="D110" t="b" s="30">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D110" t="s" s="34">
+        <v>9</v>
       </c>
       <c r="E110" s="13"/>
       <c r="F110" s="2"/>
@@ -4319,12 +4316,12 @@
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" s="5"/>
-      <c r="B111" s="16"/>
+      <c r="B111" s="14"/>
       <c r="C111" t="s" s="6">
-        <v>4</v>
-      </c>
-      <c r="D111" t="b" s="30">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D111" t="s" s="34">
+        <v>11</v>
       </c>
       <c r="E111" s="13"/>
       <c r="F111" s="2"/>
@@ -4335,10 +4332,10 @@
       <c r="A112" s="5"/>
       <c r="B112" s="14"/>
       <c r="C112" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D112" t="s" s="35">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="D112" t="s" s="34">
+        <v>13</v>
       </c>
       <c r="E112" s="13"/>
       <c r="F112" s="2"/>
@@ -4349,10 +4346,10 @@
       <c r="A113" s="5"/>
       <c r="B113" s="14"/>
       <c r="C113" t="s" s="6">
-        <v>7</v>
-      </c>
-      <c r="D113" t="s" s="35">
-        <v>88</v>
+        <v>14</v>
+      </c>
+      <c r="D113" t="s" s="34">
+        <v>15</v>
       </c>
       <c r="E113" s="13"/>
       <c r="F113" s="2"/>
@@ -4363,10 +4360,10 @@
       <c r="A114" s="5"/>
       <c r="B114" s="14"/>
       <c r="C114" t="s" s="6">
-        <v>9</v>
-      </c>
-      <c r="D114" t="s" s="35">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="D114" t="s" s="34">
+        <v>17</v>
       </c>
       <c r="E114" s="13"/>
       <c r="F114" s="2"/>
@@ -4377,10 +4374,10 @@
       <c r="A115" s="5"/>
       <c r="B115" s="14"/>
       <c r="C115" t="s" s="6">
-        <v>11</v>
-      </c>
-      <c r="D115" t="s" s="35">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="D115" t="s" s="34">
+        <v>19</v>
       </c>
       <c r="E115" s="13"/>
       <c r="F115" s="2"/>
@@ -4391,10 +4388,10 @@
       <c r="A116" s="5"/>
       <c r="B116" s="14"/>
       <c r="C116" t="s" s="6">
-        <v>13</v>
-      </c>
-      <c r="D116" t="s" s="35">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="D116" t="s" s="34">
+        <v>21</v>
       </c>
       <c r="E116" s="13"/>
       <c r="F116" s="2"/>
@@ -4405,10 +4402,10 @@
       <c r="A117" s="5"/>
       <c r="B117" s="14"/>
       <c r="C117" t="s" s="6">
-        <v>15</v>
-      </c>
-      <c r="D117" t="s" s="35">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="D117" t="s" s="34">
+        <v>23</v>
       </c>
       <c r="E117" s="13"/>
       <c r="F117" s="2"/>
@@ -4419,10 +4416,10 @@
       <c r="A118" s="5"/>
       <c r="B118" s="14"/>
       <c r="C118" t="s" s="6">
-        <v>17</v>
-      </c>
-      <c r="D118" t="s" s="35">
-        <v>18</v>
+        <v>24</v>
+      </c>
+      <c r="D118" t="s" s="34">
+        <v>25</v>
       </c>
       <c r="E118" s="13"/>
       <c r="F118" s="2"/>
@@ -4433,10 +4430,10 @@
       <c r="A119" s="5"/>
       <c r="B119" s="14"/>
       <c r="C119" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="D119" t="s" s="35">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="D119" t="s" s="34">
+        <v>27</v>
       </c>
       <c r="E119" s="13"/>
       <c r="F119" s="2"/>
@@ -4447,10 +4444,10 @@
       <c r="A120" s="5"/>
       <c r="B120" s="14"/>
       <c r="C120" t="s" s="6">
-        <v>21</v>
-      </c>
-      <c r="D120" t="s" s="35">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="D120" t="s" s="34">
+        <v>29</v>
       </c>
       <c r="E120" s="13"/>
       <c r="F120" s="2"/>
@@ -4461,10 +4458,10 @@
       <c r="A121" s="5"/>
       <c r="B121" s="14"/>
       <c r="C121" t="s" s="6">
-        <v>23</v>
-      </c>
-      <c r="D121" t="s" s="35">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="D121" s="36">
+        <v>41298</v>
       </c>
       <c r="E121" s="13"/>
       <c r="F121" s="2"/>
@@ -4475,10 +4472,10 @@
       <c r="A122" s="5"/>
       <c r="B122" s="14"/>
       <c r="C122" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="D122" t="s" s="35">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="D122" s="36">
+        <v>41275</v>
       </c>
       <c r="E122" s="13"/>
       <c r="F122" s="2"/>
@@ -4489,10 +4486,10 @@
       <c r="A123" s="5"/>
       <c r="B123" s="14"/>
       <c r="C123" t="s" s="6">
-        <v>27</v>
-      </c>
-      <c r="D123" t="s" s="35">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="D123" s="36">
+        <v>41670</v>
       </c>
       <c r="E123" s="13"/>
       <c r="F123" s="2"/>
@@ -4503,10 +4500,10 @@
       <c r="A124" s="5"/>
       <c r="B124" s="14"/>
       <c r="C124" t="s" s="6">
-        <v>29</v>
-      </c>
-      <c r="D124" t="s" s="35">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="D124" s="36">
+        <v>41646</v>
       </c>
       <c r="E124" s="13"/>
       <c r="F124" s="2"/>
@@ -4517,10 +4514,10 @@
       <c r="A125" s="5"/>
       <c r="B125" s="14"/>
       <c r="C125" t="s" s="6">
-        <v>31</v>
-      </c>
-      <c r="D125" s="36">
-        <v>41298</v>
+        <v>34</v>
+      </c>
+      <c r="D125" t="s" s="34">
+        <v>35</v>
       </c>
       <c r="E125" s="13"/>
       <c r="F125" s="2"/>
@@ -4531,10 +4528,10 @@
       <c r="A126" s="5"/>
       <c r="B126" s="14"/>
       <c r="C126" t="s" s="6">
-        <v>32</v>
-      </c>
-      <c r="D126" s="36">
-        <v>41275</v>
+        <v>36</v>
+      </c>
+      <c r="D126" t="s" s="34">
+        <v>37</v>
       </c>
       <c r="E126" s="13"/>
       <c r="F126" s="2"/>
@@ -4545,10 +4542,10 @@
       <c r="A127" s="5"/>
       <c r="B127" s="14"/>
       <c r="C127" t="s" s="6">
-        <v>33</v>
-      </c>
-      <c r="D127" s="36">
-        <v>41670</v>
+        <v>38</v>
+      </c>
+      <c r="D127" t="s" s="34">
+        <v>39</v>
       </c>
       <c r="E127" s="13"/>
       <c r="F127" s="2"/>
@@ -4559,10 +4556,10 @@
       <c r="A128" s="5"/>
       <c r="B128" s="14"/>
       <c r="C128" t="s" s="6">
-        <v>34</v>
-      </c>
-      <c r="D128" s="36">
-        <v>41646</v>
+        <v>40</v>
+      </c>
+      <c r="D128" t="s" s="34">
+        <v>41</v>
       </c>
       <c r="E128" s="13"/>
       <c r="F128" s="2"/>
@@ -4572,11 +4569,11 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="5"/>
       <c r="B129" s="14"/>
-      <c r="C129" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D129" t="s" s="35">
-        <v>36</v>
+      <c r="C129" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D129" t="s" s="34">
+        <v>43</v>
       </c>
       <c r="E129" s="13"/>
       <c r="F129" s="2"/>
@@ -4587,10 +4584,10 @@
       <c r="A130" s="5"/>
       <c r="B130" s="14"/>
       <c r="C130" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D130" t="s" s="35">
-        <v>38</v>
+        <v>44</v>
+      </c>
+      <c r="D130" s="36">
+        <v>41648</v>
       </c>
       <c r="E130" s="13"/>
       <c r="F130" s="2"/>
@@ -4599,55 +4596,47 @@
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="5"/>
-      <c r="B131" s="14"/>
+      <c r="B131" s="21"/>
       <c r="C131" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D131" t="s" s="35">
-        <v>40</v>
+        <v>68</v>
+      </c>
+      <c r="D131" s="36">
+        <v>40919</v>
       </c>
       <c r="E131" s="13"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" ht="15" customHeight="1">
+    <row r="132" ht="9" customHeight="1" hidden="1">
       <c r="A132" s="5"/>
-      <c r="B132" s="14"/>
-      <c r="C132" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D132" t="s" s="35">
-        <v>42</v>
-      </c>
+      <c r="B132" t="s" s="59">
+        <v>88</v>
+      </c>
+      <c r="C132" s="33"/>
+      <c r="D132" s="33"/>
       <c r="E132" s="13"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="5"/>
-      <c r="B133" s="14"/>
-      <c r="C133" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D133" t="s" s="35">
-        <v>44</v>
-      </c>
-      <c r="E133" s="13"/>
+    <row r="133" ht="13.65" customHeight="1">
+      <c r="A133" s="2"/>
+      <c r="B133" s="60"/>
+      <c r="C133" s="60"/>
+      <c r="D133" s="60"/>
+      <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="5"/>
-      <c r="B134" s="14"/>
-      <c r="C134" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D134" s="36">
-        <v>41648</v>
-      </c>
+      <c r="B134" t="s" s="6">
+        <v>89</v>
+      </c>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
       <c r="E134" s="13"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
@@ -4655,47 +4644,57 @@
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="5"/>
-      <c r="B135" s="21"/>
+      <c r="B135" t="s" s="6">
+        <v>1</v>
+      </c>
       <c r="C135" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D135" s="36">
-        <v>40919</v>
+        <v>4</v>
+      </c>
+      <c r="D135" t="s" s="34">
+        <v>5</v>
       </c>
       <c r="E135" s="13"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" ht="9" customHeight="1" hidden="1">
+    <row r="136" ht="15" customHeight="1">
       <c r="A136" s="5"/>
-      <c r="B136" t="s" s="59">
-        <v>89</v>
-      </c>
-      <c r="C136" s="33"/>
-      <c r="D136" s="33"/>
+      <c r="B136" s="7"/>
+      <c r="C136" t="s" s="6">
+        <v>34</v>
+      </c>
+      <c r="D136" t="s" s="34">
+        <v>35</v>
+      </c>
       <c r="E136" s="13"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" ht="13.65" customHeight="1">
-      <c r="A137" s="2"/>
-      <c r="B137" s="60"/>
-      <c r="C137" s="60"/>
-      <c r="D137" s="60"/>
-      <c r="E137" s="2"/>
+    <row r="137" ht="15" customHeight="1">
+      <c r="A137" s="5"/>
+      <c r="B137" s="7"/>
+      <c r="C137" t="s" s="6">
+        <v>36</v>
+      </c>
+      <c r="D137" t="s" s="34">
+        <v>37</v>
+      </c>
+      <c r="E137" s="13"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="5"/>
-      <c r="B138" t="s" s="6">
-        <v>90</v>
-      </c>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
+      <c r="B138" s="7"/>
+      <c r="C138" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="D138" t="s" s="34">
+        <v>39</v>
+      </c>
       <c r="E138" s="13"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
@@ -4703,14 +4702,12 @@
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="5"/>
-      <c r="B139" t="s" s="6">
-        <v>1</v>
-      </c>
+      <c r="B139" s="7"/>
       <c r="C139" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D139" t="s" s="35">
-        <v>6</v>
+        <v>40</v>
+      </c>
+      <c r="D139" t="s" s="34">
+        <v>41</v>
       </c>
       <c r="E139" s="13"/>
       <c r="F139" s="2"/>
@@ -4720,11 +4717,11 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="5"/>
       <c r="B140" s="7"/>
-      <c r="C140" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D140" t="s" s="35">
-        <v>36</v>
+      <c r="C140" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D140" t="s" s="34">
+        <v>43</v>
       </c>
       <c r="E140" s="13"/>
       <c r="F140" s="2"/>
@@ -4735,10 +4732,10 @@
       <c r="A141" s="5"/>
       <c r="B141" s="7"/>
       <c r="C141" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D141" t="s" s="35">
-        <v>38</v>
+        <v>44</v>
+      </c>
+      <c r="D141" s="36">
+        <v>41648</v>
       </c>
       <c r="E141" s="13"/>
       <c r="F141" s="2"/>
@@ -4749,150 +4746,150 @@
       <c r="A142" s="5"/>
       <c r="B142" s="7"/>
       <c r="C142" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D142" t="s" s="35">
-        <v>40</v>
+        <v>68</v>
+      </c>
+      <c r="D142" s="36">
+        <v>40919</v>
       </c>
       <c r="E142" s="13"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" ht="15" customHeight="1">
+    <row r="143" ht="9" customHeight="1" hidden="1">
       <c r="A143" s="5"/>
-      <c r="B143" s="7"/>
-      <c r="C143" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D143" t="s" s="35">
-        <v>42</v>
-      </c>
+      <c r="B143" t="s" s="26">
+        <v>90</v>
+      </c>
+      <c r="C143" s="61"/>
+      <c r="D143" s="61"/>
       <c r="E143" s="13"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" ht="15" customHeight="1">
+    <row r="144" ht="9" customHeight="1" hidden="1">
       <c r="A144" s="5"/>
-      <c r="B144" s="7"/>
-      <c r="C144" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D144" t="s" s="35">
-        <v>44</v>
-      </c>
+      <c r="B144" t="s" s="26">
+        <v>91</v>
+      </c>
+      <c r="C144" s="61"/>
+      <c r="D144" s="61"/>
       <c r="E144" s="13"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" ht="15" customHeight="1">
+    <row r="145" ht="9" customHeight="1" hidden="1">
       <c r="A145" s="5"/>
-      <c r="B145" s="7"/>
-      <c r="C145" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D145" s="36">
-        <v>41648</v>
-      </c>
+      <c r="B145" t="s" s="26">
+        <v>92</v>
+      </c>
+      <c r="C145" s="61"/>
+      <c r="D145" s="61"/>
       <c r="E145" s="13"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="5"/>
-      <c r="B146" s="7"/>
-      <c r="C146" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D146" s="36">
-        <v>40919</v>
-      </c>
-      <c r="E146" s="13"/>
+    <row r="146" ht="13.65" customHeight="1">
+      <c r="A146" s="2"/>
+      <c r="B146" s="28"/>
+      <c r="C146" s="28"/>
+      <c r="D146" s="28"/>
+      <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" ht="9" customHeight="1" hidden="1">
-      <c r="A147" s="5"/>
-      <c r="B147" t="s" s="26">
-        <v>91</v>
-      </c>
-      <c r="C147" s="61"/>
-      <c r="D147" s="61"/>
-      <c r="E147" s="13"/>
+    <row r="147" ht="13.65" customHeight="1">
+      <c r="A147" s="2"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="3"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" ht="9" customHeight="1" hidden="1">
+    <row r="148" ht="15" customHeight="1">
       <c r="A148" s="5"/>
-      <c r="B148" t="s" s="26">
-        <v>92</v>
-      </c>
-      <c r="C148" s="61"/>
-      <c r="D148" s="61"/>
-      <c r="E148" s="13"/>
-      <c r="F148" s="2"/>
+      <c r="B148" t="s" s="6">
+        <v>93</v>
+      </c>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="13"/>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" ht="9" customHeight="1" hidden="1">
+    <row r="149" ht="15" customHeight="1">
       <c r="A149" s="5"/>
-      <c r="B149" t="s" s="26">
-        <v>93</v>
-      </c>
-      <c r="C149" s="61"/>
-      <c r="D149" s="61"/>
-      <c r="E149" s="13"/>
-      <c r="F149" s="2"/>
+      <c r="B149" t="s" s="6">
+        <v>1</v>
+      </c>
+      <c r="C149" t="s" s="6">
+        <v>2</v>
+      </c>
+      <c r="D149" t="b" s="43">
+        <v>1</v>
+      </c>
+      <c r="E149" s="45"/>
+      <c r="F149" s="13"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" ht="13.65" customHeight="1">
-      <c r="A150" s="2"/>
-      <c r="B150" s="28"/>
-      <c r="C150" s="28"/>
-      <c r="D150" s="28"/>
-      <c r="E150" s="2"/>
-      <c r="F150" s="2"/>
+    <row r="150" ht="15" customHeight="1">
+      <c r="A150" s="5"/>
+      <c r="B150" s="7"/>
+      <c r="C150" t="s" s="6">
+        <v>3</v>
+      </c>
+      <c r="D150" t="b" s="43">
+        <v>1</v>
+      </c>
+      <c r="E150" s="45"/>
+      <c r="F150" s="13"/>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" ht="13.65" customHeight="1">
-      <c r="A151" s="2"/>
-      <c r="B151" s="3"/>
-      <c r="C151" s="3"/>
-      <c r="D151" s="3"/>
-      <c r="E151" s="3"/>
-      <c r="F151" s="2"/>
+    <row r="151" ht="15" customHeight="1">
+      <c r="A151" s="5"/>
+      <c r="B151" s="33"/>
+      <c r="C151" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D151" t="s" s="46">
+        <v>5</v>
+      </c>
+      <c r="E151" s="45"/>
+      <c r="F151" s="13"/>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
     <row r="152" ht="15" customHeight="1">
       <c r="A152" s="5"/>
-      <c r="B152" t="s" s="6">
+      <c r="B152" s="7"/>
+      <c r="C152" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="D152" t="s" s="46">
         <v>94</v>
       </c>
-      <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
+      <c r="E152" s="45"/>
       <c r="F152" s="13"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
     </row>
     <row r="153" ht="15" customHeight="1">
       <c r="A153" s="5"/>
-      <c r="B153" t="s" s="6">
-        <v>1</v>
-      </c>
+      <c r="B153" s="7"/>
       <c r="C153" t="s" s="6">
-        <v>2</v>
-      </c>
-      <c r="D153" t="b" s="43">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="D153" t="s" s="46">
+        <v>9</v>
       </c>
       <c r="E153" s="45"/>
       <c r="F153" s="13"/>
@@ -4903,10 +4900,10 @@
       <c r="A154" s="5"/>
       <c r="B154" s="7"/>
       <c r="C154" t="s" s="6">
-        <v>3</v>
-      </c>
-      <c r="D154" t="b" s="43">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="D154" t="s" s="46">
+        <v>11</v>
       </c>
       <c r="E154" s="45"/>
       <c r="F154" s="13"/>
@@ -4915,12 +4912,12 @@
     </row>
     <row r="155" ht="15" customHeight="1">
       <c r="A155" s="5"/>
-      <c r="B155" s="33"/>
+      <c r="B155" s="7"/>
       <c r="C155" t="s" s="6">
-        <v>4</v>
-      </c>
-      <c r="D155" t="b" s="43">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D155" t="s" s="46">
+        <v>13</v>
       </c>
       <c r="E155" s="45"/>
       <c r="F155" s="13"/>
@@ -4931,10 +4928,10 @@
       <c r="A156" s="5"/>
       <c r="B156" s="7"/>
       <c r="C156" t="s" s="6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D156" t="s" s="46">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E156" s="45"/>
       <c r="F156" s="13"/>
@@ -4945,10 +4942,10 @@
       <c r="A157" s="5"/>
       <c r="B157" s="7"/>
       <c r="C157" t="s" s="6">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D157" t="s" s="46">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="E157" s="45"/>
       <c r="F157" s="13"/>
@@ -4959,10 +4956,10 @@
       <c r="A158" s="5"/>
       <c r="B158" s="7"/>
       <c r="C158" t="s" s="6">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D158" t="s" s="46">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E158" s="45"/>
       <c r="F158" s="13"/>
@@ -4973,10 +4970,10 @@
       <c r="A159" s="5"/>
       <c r="B159" s="7"/>
       <c r="C159" t="s" s="6">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D159" t="s" s="46">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E159" s="45"/>
       <c r="F159" s="13"/>
@@ -4987,10 +4984,10 @@
       <c r="A160" s="5"/>
       <c r="B160" s="7"/>
       <c r="C160" t="s" s="6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D160" t="s" s="46">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E160" s="45"/>
       <c r="F160" s="13"/>
@@ -5001,10 +4998,10 @@
       <c r="A161" s="5"/>
       <c r="B161" s="7"/>
       <c r="C161" t="s" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D161" t="s" s="46">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E161" s="45"/>
       <c r="F161" s="13"/>
@@ -5015,10 +5012,10 @@
       <c r="A162" s="5"/>
       <c r="B162" s="7"/>
       <c r="C162" t="s" s="6">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D162" t="s" s="46">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E162" s="45"/>
       <c r="F162" s="13"/>
@@ -5029,10 +5026,10 @@
       <c r="A163" s="5"/>
       <c r="B163" s="7"/>
       <c r="C163" t="s" s="6">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D163" t="s" s="46">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E163" s="45"/>
       <c r="F163" s="13"/>
@@ -5043,10 +5040,10 @@
       <c r="A164" s="5"/>
       <c r="B164" s="7"/>
       <c r="C164" t="s" s="6">
-        <v>21</v>
-      </c>
-      <c r="D164" t="s" s="46">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="D164" s="47">
+        <v>41298</v>
       </c>
       <c r="E164" s="45"/>
       <c r="F164" s="13"/>
@@ -5057,10 +5054,10 @@
       <c r="A165" s="5"/>
       <c r="B165" s="7"/>
       <c r="C165" t="s" s="6">
-        <v>23</v>
-      </c>
-      <c r="D165" t="s" s="46">
-        <v>24</v>
+        <v>31</v>
+      </c>
+      <c r="D165" s="47">
+        <v>41275</v>
       </c>
       <c r="E165" s="45"/>
       <c r="F165" s="13"/>
@@ -5071,10 +5068,10 @@
       <c r="A166" s="5"/>
       <c r="B166" s="7"/>
       <c r="C166" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="D166" t="s" s="46">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="D166" s="47">
+        <v>41670</v>
       </c>
       <c r="E166" s="45"/>
       <c r="F166" s="13"/>
@@ -5085,10 +5082,10 @@
       <c r="A167" s="5"/>
       <c r="B167" s="7"/>
       <c r="C167" t="s" s="6">
-        <v>27</v>
-      </c>
-      <c r="D167" t="s" s="46">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="D167" s="47">
+        <v>41646</v>
       </c>
       <c r="E167" s="45"/>
       <c r="F167" s="13"/>
@@ -5099,12 +5096,12 @@
       <c r="A168" s="5"/>
       <c r="B168" s="7"/>
       <c r="C168" t="s" s="6">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D168" t="s" s="46">
-        <v>30</v>
-      </c>
-      <c r="E168" s="45"/>
+        <v>35</v>
+      </c>
+      <c r="E168" s="49"/>
       <c r="F168" s="13"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
@@ -5113,12 +5110,12 @@
       <c r="A169" s="5"/>
       <c r="B169" s="7"/>
       <c r="C169" t="s" s="6">
-        <v>31</v>
-      </c>
-      <c r="D169" s="47">
-        <v>41298</v>
-      </c>
-      <c r="E169" s="45"/>
+        <v>36</v>
+      </c>
+      <c r="D169" t="s" s="46">
+        <v>37</v>
+      </c>
+      <c r="E169" s="49"/>
       <c r="F169" s="13"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
@@ -5127,12 +5124,12 @@
       <c r="A170" s="5"/>
       <c r="B170" s="7"/>
       <c r="C170" t="s" s="6">
-        <v>32</v>
-      </c>
-      <c r="D170" s="47">
-        <v>41275</v>
-      </c>
-      <c r="E170" s="45"/>
+        <v>38</v>
+      </c>
+      <c r="D170" t="s" s="46">
+        <v>39</v>
+      </c>
+      <c r="E170" s="49"/>
       <c r="F170" s="13"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
@@ -5141,12 +5138,12 @@
       <c r="A171" s="5"/>
       <c r="B171" s="7"/>
       <c r="C171" t="s" s="6">
-        <v>33</v>
-      </c>
-      <c r="D171" s="47">
-        <v>41670</v>
-      </c>
-      <c r="E171" s="45"/>
+        <v>40</v>
+      </c>
+      <c r="D171" t="s" s="46">
+        <v>41</v>
+      </c>
+      <c r="E171" s="49"/>
       <c r="F171" s="13"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
@@ -5154,13 +5151,13 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" s="5"/>
       <c r="B172" s="7"/>
-      <c r="C172" t="s" s="6">
-        <v>34</v>
-      </c>
-      <c r="D172" s="47">
-        <v>41646</v>
-      </c>
-      <c r="E172" s="45"/>
+      <c r="C172" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D172" t="s" s="46">
+        <v>43</v>
+      </c>
+      <c r="E172" s="49"/>
       <c r="F172" s="13"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
@@ -5169,12 +5166,12 @@
       <c r="A173" s="5"/>
       <c r="B173" s="7"/>
       <c r="C173" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D173" t="s" s="46">
-        <v>36</v>
-      </c>
-      <c r="E173" s="49"/>
+        <v>44</v>
+      </c>
+      <c r="D173" s="47">
+        <v>41648</v>
+      </c>
+      <c r="E173" s="45"/>
       <c r="F173" s="13"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
@@ -5183,179 +5180,181 @@
       <c r="A174" s="5"/>
       <c r="B174" s="7"/>
       <c r="C174" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D174" t="s" s="46">
-        <v>38</v>
-      </c>
-      <c r="E174" s="49"/>
+        <v>68</v>
+      </c>
+      <c r="D174" s="47">
+        <v>40919</v>
+      </c>
+      <c r="E174" s="45"/>
       <c r="F174" s="13"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
     </row>
-    <row r="175" ht="15" customHeight="1">
+    <row r="175" ht="9" customHeight="1" hidden="1">
       <c r="A175" s="5"/>
-      <c r="B175" s="7"/>
-      <c r="C175" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D175" t="s" s="46">
-        <v>40</v>
-      </c>
-      <c r="E175" s="49"/>
+      <c r="B175" t="s" s="22">
+        <v>95</v>
+      </c>
+      <c r="C175" t="s" s="22">
+        <v>96</v>
+      </c>
+      <c r="D175" t="s" s="23">
+        <v>97</v>
+      </c>
+      <c r="E175" t="s" s="23">
+        <v>98</v>
+      </c>
       <c r="F175" s="13"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
     </row>
-    <row r="176" ht="15" customHeight="1">
+    <row r="176" ht="9" customHeight="1" hidden="1">
       <c r="A176" s="5"/>
-      <c r="B176" s="7"/>
-      <c r="C176" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D176" t="s" s="46">
-        <v>42</v>
-      </c>
-      <c r="E176" s="49"/>
+      <c r="B176" t="s" s="22">
+        <v>99</v>
+      </c>
+      <c r="C176" s="62"/>
+      <c r="D176" t="s" s="23">
+        <v>100</v>
+      </c>
+      <c r="E176" t="s" s="23">
+        <v>47</v>
+      </c>
       <c r="F176" s="13"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
     </row>
-    <row r="177" ht="15" customHeight="1">
+    <row r="177" ht="9" customHeight="1" hidden="1">
       <c r="A177" s="5"/>
-      <c r="B177" s="7"/>
-      <c r="C177" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D177" t="s" s="46">
-        <v>44</v>
-      </c>
-      <c r="E177" s="49"/>
+      <c r="B177" t="s" s="22">
+        <v>101</v>
+      </c>
+      <c r="C177" s="62"/>
+      <c r="D177" s="63"/>
+      <c r="E177" t="s" s="23">
+        <v>102</v>
+      </c>
       <c r="F177" s="13"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
     </row>
-    <row r="178" ht="15" customHeight="1">
+    <row r="178" ht="9" customHeight="1" hidden="1">
       <c r="A178" s="5"/>
-      <c r="B178" s="7"/>
-      <c r="C178" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D178" s="47">
-        <v>41648</v>
-      </c>
-      <c r="E178" s="45"/>
+      <c r="B178" t="s" s="25">
+        <v>103</v>
+      </c>
+      <c r="C178" t="s" s="25">
+        <v>104</v>
+      </c>
+      <c r="D178" s="27">
+        <v>2</v>
+      </c>
+      <c r="E178" t="s" s="26">
+        <v>105</v>
+      </c>
       <c r="F178" s="13"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
     </row>
-    <row r="179" ht="15" customHeight="1">
-      <c r="A179" s="5"/>
-      <c r="B179" s="7"/>
-      <c r="C179" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D179" s="47">
-        <v>40919</v>
-      </c>
-      <c r="E179" s="45"/>
-      <c r="F179" s="13"/>
+    <row r="179" ht="13.65" customHeight="1">
+      <c r="A179" s="2"/>
+      <c r="B179" s="28"/>
+      <c r="C179" s="28"/>
+      <c r="D179" s="28"/>
+      <c r="E179" s="28"/>
+      <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
     </row>
-    <row r="180" ht="9" customHeight="1" hidden="1">
-      <c r="A180" s="5"/>
-      <c r="B180" t="s" s="22">
-        <v>96</v>
-      </c>
-      <c r="C180" t="s" s="22">
-        <v>97</v>
-      </c>
-      <c r="D180" t="s" s="23">
-        <v>98</v>
-      </c>
-      <c r="E180" t="s" s="23">
-        <v>99</v>
-      </c>
-      <c r="F180" s="13"/>
+    <row r="180" ht="13.65" customHeight="1">
+      <c r="A180" s="2"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="2"/>
+      <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
     </row>
-    <row r="181" ht="9" customHeight="1" hidden="1">
+    <row r="181" ht="13.65" customHeight="1">
       <c r="A181" s="5"/>
-      <c r="B181" t="s" s="22">
-        <v>100</v>
-      </c>
-      <c r="C181" s="62"/>
-      <c r="D181" t="s" s="23">
-        <v>101</v>
-      </c>
-      <c r="E181" t="s" s="23">
-        <v>48</v>
-      </c>
-      <c r="F181" s="13"/>
+      <c r="B181" t="s" s="64">
+        <v>106</v>
+      </c>
+      <c r="C181" s="65"/>
+      <c r="D181" s="66"/>
+      <c r="E181" s="13"/>
+      <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
     </row>
-    <row r="182" ht="9" customHeight="1" hidden="1">
+    <row r="182" ht="15" customHeight="1">
       <c r="A182" s="5"/>
-      <c r="B182" t="s" s="22">
-        <v>102</v>
-      </c>
-      <c r="C182" s="62"/>
-      <c r="D182" s="63"/>
-      <c r="E182" t="s" s="23">
-        <v>103</v>
-      </c>
-      <c r="F182" s="13"/>
+      <c r="B182" t="s" s="6">
+        <v>1</v>
+      </c>
+      <c r="C182" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D182" t="s" s="34">
+        <v>5</v>
+      </c>
+      <c r="E182" s="13"/>
+      <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
     </row>
-    <row r="183" ht="9" customHeight="1" hidden="1">
+    <row r="183" ht="15" customHeight="1">
       <c r="A183" s="5"/>
-      <c r="B183" t="s" s="25">
-        <v>104</v>
-      </c>
-      <c r="C183" t="s" s="25">
-        <v>105</v>
-      </c>
-      <c r="D183" s="27">
-        <v>2</v>
-      </c>
-      <c r="E183" t="s" s="26">
-        <v>106</v>
-      </c>
-      <c r="F183" s="13"/>
+      <c r="B183" s="7"/>
+      <c r="C183" t="s" s="6">
+        <v>34</v>
+      </c>
+      <c r="D183" t="s" s="34">
+        <v>35</v>
+      </c>
+      <c r="E183" s="13"/>
+      <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
     </row>
-    <row r="184" ht="13.65" customHeight="1">
-      <c r="A184" s="2"/>
-      <c r="B184" s="28"/>
-      <c r="C184" s="28"/>
-      <c r="D184" s="28"/>
-      <c r="E184" s="28"/>
+    <row r="184" ht="15" customHeight="1">
+      <c r="A184" s="5"/>
+      <c r="B184" s="7"/>
+      <c r="C184" t="s" s="6">
+        <v>36</v>
+      </c>
+      <c r="D184" t="s" s="34">
+        <v>37</v>
+      </c>
+      <c r="E184" s="13"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
     </row>
-    <row r="185" ht="13.65" customHeight="1">
-      <c r="A185" s="2"/>
-      <c r="B185" s="3"/>
-      <c r="C185" s="3"/>
-      <c r="D185" s="3"/>
-      <c r="E185" s="2"/>
+    <row r="185" ht="15" customHeight="1">
+      <c r="A185" s="5"/>
+      <c r="B185" s="7"/>
+      <c r="C185" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="D185" t="s" s="34">
+        <v>39</v>
+      </c>
+      <c r="E185" s="13"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
     </row>
-    <row r="186" ht="13.65" customHeight="1">
+    <row r="186" ht="15" customHeight="1">
       <c r="A186" s="5"/>
-      <c r="B186" t="s" s="64">
-        <v>107</v>
-      </c>
-      <c r="C186" s="65"/>
-      <c r="D186" s="66"/>
+      <c r="B186" s="7"/>
+      <c r="C186" t="s" s="6">
+        <v>40</v>
+      </c>
+      <c r="D186" t="s" s="34">
+        <v>41</v>
+      </c>
       <c r="E186" s="13"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
@@ -5363,14 +5362,12 @@
     </row>
     <row r="187" ht="15" customHeight="1">
       <c r="A187" s="5"/>
-      <c r="B187" t="s" s="6">
-        <v>1</v>
-      </c>
-      <c r="C187" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D187" t="s" s="35">
-        <v>6</v>
+      <c r="B187" s="7"/>
+      <c r="C187" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D187" t="s" s="34">
+        <v>43</v>
       </c>
       <c r="E187" s="13"/>
       <c r="F187" s="2"/>
@@ -5381,10 +5378,10 @@
       <c r="A188" s="5"/>
       <c r="B188" s="7"/>
       <c r="C188" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D188" t="s" s="35">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="D188" s="36">
+        <v>41648</v>
       </c>
       <c r="E188" s="13"/>
       <c r="F188" s="2"/>
@@ -5395,10 +5392,10 @@
       <c r="A189" s="5"/>
       <c r="B189" s="7"/>
       <c r="C189" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D189" t="s" s="35">
-        <v>38</v>
+        <v>68</v>
+      </c>
+      <c r="D189" s="36">
+        <v>40919</v>
       </c>
       <c r="E189" s="13"/>
       <c r="F189" s="2"/>
@@ -5409,155 +5406,157 @@
       <c r="A190" s="5"/>
       <c r="B190" s="7"/>
       <c r="C190" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D190" t="s" s="35">
-        <v>40</v>
+        <v>107</v>
+      </c>
+      <c r="D190" s="67">
+        <v>2</v>
       </c>
       <c r="E190" s="13"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
     </row>
-    <row r="191" ht="15" customHeight="1">
+    <row r="191" ht="9" customHeight="1" hidden="1">
       <c r="A191" s="5"/>
-      <c r="B191" s="7"/>
-      <c r="C191" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D191" t="s" s="35">
-        <v>42</v>
-      </c>
+      <c r="B191" t="s" s="20">
+        <v>90</v>
+      </c>
+      <c r="C191" t="s" s="68">
+        <v>108</v>
+      </c>
+      <c r="D191" s="69"/>
       <c r="E191" s="13"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
     </row>
-    <row r="192" ht="15" customHeight="1">
+    <row r="192" ht="9" customHeight="1" hidden="1">
       <c r="A192" s="5"/>
-      <c r="B192" s="7"/>
-      <c r="C192" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D192" t="s" s="35">
-        <v>44</v>
-      </c>
+      <c r="B192" t="s" s="20">
+        <v>109</v>
+      </c>
+      <c r="C192" t="s" s="68">
+        <v>110</v>
+      </c>
+      <c r="D192" s="69"/>
       <c r="E192" s="13"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
     </row>
-    <row r="193" ht="15" customHeight="1">
+    <row r="193" ht="9" customHeight="1" hidden="1">
       <c r="A193" s="5"/>
-      <c r="B193" s="7"/>
-      <c r="C193" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D193" s="36">
-        <v>41648</v>
-      </c>
+      <c r="B193" s="70">
+        <v>3</v>
+      </c>
+      <c r="C193" s="71">
+        <v>400</v>
+      </c>
+      <c r="D193" s="69"/>
       <c r="E193" s="13"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
     </row>
-    <row r="194" ht="15" customHeight="1">
-      <c r="A194" s="5"/>
-      <c r="B194" s="7"/>
-      <c r="C194" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D194" s="36">
-        <v>40919</v>
-      </c>
-      <c r="E194" s="13"/>
+    <row r="194" ht="13.65" customHeight="1">
+      <c r="A194" s="2"/>
+      <c r="B194" s="28"/>
+      <c r="C194" s="28"/>
+      <c r="D194" s="28"/>
+      <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
     </row>
-    <row r="195" ht="15" customHeight="1">
-      <c r="A195" s="5"/>
-      <c r="B195" s="7"/>
-      <c r="C195" t="s" s="6">
-        <v>108</v>
-      </c>
-      <c r="D195" s="67">
-        <v>2</v>
-      </c>
-      <c r="E195" s="13"/>
+    <row r="195" ht="13.65" customHeight="1">
+      <c r="A195" s="2"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+      <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
     </row>
-    <row r="196" ht="9" customHeight="1" hidden="1">
+    <row r="196" ht="13.65" customHeight="1">
       <c r="A196" s="5"/>
-      <c r="B196" t="s" s="20">
-        <v>91</v>
-      </c>
-      <c r="C196" t="s" s="68">
-        <v>109</v>
-      </c>
+      <c r="B196" t="s" s="68">
+        <v>111</v>
+      </c>
+      <c r="C196" s="69"/>
       <c r="D196" s="69"/>
       <c r="E196" s="13"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
     </row>
-    <row r="197" ht="9" customHeight="1" hidden="1">
+    <row r="197" ht="15" customHeight="1">
       <c r="A197" s="5"/>
-      <c r="B197" t="s" s="20">
-        <v>110</v>
-      </c>
-      <c r="C197" t="s" s="68">
-        <v>111</v>
-      </c>
-      <c r="D197" s="69"/>
+      <c r="B197" t="s" s="6">
+        <v>1</v>
+      </c>
+      <c r="C197" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D197" t="s" s="34">
+        <v>5</v>
+      </c>
       <c r="E197" s="13"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
     </row>
-    <row r="198" ht="9" customHeight="1" hidden="1">
+    <row r="198" ht="15" customHeight="1">
       <c r="A198" s="5"/>
-      <c r="B198" s="70">
-        <v>3</v>
-      </c>
-      <c r="C198" s="71">
-        <v>400</v>
-      </c>
-      <c r="D198" s="69"/>
+      <c r="B198" s="7"/>
+      <c r="C198" t="s" s="6">
+        <v>34</v>
+      </c>
+      <c r="D198" t="s" s="34">
+        <v>35</v>
+      </c>
       <c r="E198" s="13"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
     </row>
-    <row r="199" ht="13.65" customHeight="1">
-      <c r="A199" s="2"/>
-      <c r="B199" s="28"/>
-      <c r="C199" s="28"/>
-      <c r="D199" s="28"/>
-      <c r="E199" s="2"/>
+    <row r="199" ht="15" customHeight="1">
+      <c r="A199" s="5"/>
+      <c r="B199" s="7"/>
+      <c r="C199" t="s" s="6">
+        <v>36</v>
+      </c>
+      <c r="D199" t="s" s="34">
+        <v>37</v>
+      </c>
+      <c r="E199" s="13"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
     </row>
-    <row r="200" ht="13.65" customHeight="1">
-      <c r="A200" s="2"/>
-      <c r="B200" s="3"/>
-      <c r="C200" s="3"/>
-      <c r="D200" s="3"/>
-      <c r="E200" s="2"/>
+    <row r="200" ht="15" customHeight="1">
+      <c r="A200" s="5"/>
+      <c r="B200" s="7"/>
+      <c r="C200" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="D200" t="s" s="34">
+        <v>39</v>
+      </c>
+      <c r="E200" s="13"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" ht="13.65" customHeight="1">
+    <row r="201" ht="15" customHeight="1">
       <c r="A201" s="5"/>
-      <c r="B201" t="s" s="68">
-        <v>112</v>
-      </c>
-      <c r="C201" s="69"/>
-      <c r="D201" s="69"/>
+      <c r="B201" s="7"/>
+      <c r="C201" t="s" s="6">
+        <v>40</v>
+      </c>
+      <c r="D201" t="s" s="34">
+        <v>41</v>
+      </c>
       <c r="E201" s="13"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
@@ -5565,14 +5564,12 @@
     </row>
     <row r="202" ht="15" customHeight="1">
       <c r="A202" s="5"/>
-      <c r="B202" t="s" s="6">
-        <v>1</v>
-      </c>
-      <c r="C202" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D202" t="s" s="35">
-        <v>6</v>
+      <c r="B202" s="7"/>
+      <c r="C202" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D202" t="s" s="34">
+        <v>43</v>
       </c>
       <c r="E202" s="13"/>
       <c r="F202" s="2"/>
@@ -5583,10 +5580,10 @@
       <c r="A203" s="5"/>
       <c r="B203" s="7"/>
       <c r="C203" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D203" t="s" s="35">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="D203" s="36">
+        <v>41648</v>
       </c>
       <c r="E203" s="13"/>
       <c r="F203" s="2"/>
@@ -5597,10 +5594,10 @@
       <c r="A204" s="5"/>
       <c r="B204" s="7"/>
       <c r="C204" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D204" t="s" s="35">
-        <v>38</v>
+        <v>68</v>
+      </c>
+      <c r="D204" s="36">
+        <v>40919</v>
       </c>
       <c r="E204" s="13"/>
       <c r="F204" s="2"/>
@@ -5611,67 +5608,61 @@
       <c r="A205" s="5"/>
       <c r="B205" s="7"/>
       <c r="C205" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D205" t="s" s="35">
-        <v>40</v>
+        <v>112</v>
+      </c>
+      <c r="D205" t="s" s="6">
+        <v>113</v>
       </c>
       <c r="E205" s="13"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
     </row>
-    <row r="206" ht="15" customHeight="1">
+    <row r="206" ht="9" customHeight="1" hidden="1">
       <c r="A206" s="5"/>
-      <c r="B206" s="7"/>
-      <c r="C206" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D206" t="s" s="35">
-        <v>42</v>
-      </c>
+      <c r="B206" t="s" s="20">
+        <v>114</v>
+      </c>
+      <c r="C206" t="s" s="68">
+        <v>115</v>
+      </c>
+      <c r="D206" s="69"/>
       <c r="E206" s="13"/>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
     </row>
-    <row r="207" ht="15" customHeight="1">
+    <row r="207" ht="9" customHeight="1" hidden="1">
       <c r="A207" s="5"/>
-      <c r="B207" s="7"/>
-      <c r="C207" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D207" t="s" s="35">
-        <v>44</v>
-      </c>
+      <c r="B207" t="s" s="20">
+        <v>114</v>
+      </c>
+      <c r="C207" t="s" s="68">
+        <v>116</v>
+      </c>
+      <c r="D207" s="69"/>
       <c r="E207" s="13"/>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
     </row>
-    <row r="208" ht="15" customHeight="1">
-      <c r="A208" s="5"/>
-      <c r="B208" s="7"/>
-      <c r="C208" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D208" s="36">
-        <v>41648</v>
-      </c>
-      <c r="E208" s="13"/>
+    <row r="208" ht="13.65" customHeight="1">
+      <c r="A208" s="2"/>
+      <c r="B208" s="60"/>
+      <c r="C208" s="60"/>
+      <c r="D208" s="60"/>
+      <c r="E208" s="2"/>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
     </row>
-    <row r="209" ht="15" customHeight="1">
+    <row r="209" ht="13.65" customHeight="1">
       <c r="A209" s="5"/>
-      <c r="B209" s="7"/>
-      <c r="C209" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D209" s="36">
-        <v>40919</v>
-      </c>
+      <c r="B209" t="s" s="68">
+        <v>117</v>
+      </c>
+      <c r="C209" s="69"/>
+      <c r="D209" s="69"/>
       <c r="E209" s="13"/>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
@@ -5679,63 +5670,71 @@
     </row>
     <row r="210" ht="15" customHeight="1">
       <c r="A210" s="5"/>
-      <c r="B210" s="7"/>
+      <c r="B210" t="s" s="6">
+        <v>1</v>
+      </c>
       <c r="C210" t="s" s="6">
-        <v>113</v>
-      </c>
-      <c r="D210" t="s" s="6">
-        <v>114</v>
+        <v>4</v>
+      </c>
+      <c r="D210" t="s" s="34">
+        <v>5</v>
       </c>
       <c r="E210" s="13"/>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
     </row>
-    <row r="211" ht="9" customHeight="1" hidden="1">
+    <row r="211" ht="15" customHeight="1">
       <c r="A211" s="5"/>
-      <c r="B211" t="s" s="20">
-        <v>115</v>
-      </c>
-      <c r="C211" t="s" s="68">
-        <v>116</v>
-      </c>
-      <c r="D211" s="69"/>
+      <c r="B211" s="7"/>
+      <c r="C211" t="s" s="6">
+        <v>34</v>
+      </c>
+      <c r="D211" t="s" s="34">
+        <v>35</v>
+      </c>
       <c r="E211" s="13"/>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
     </row>
-    <row r="212" ht="9" customHeight="1" hidden="1">
+    <row r="212" ht="15" customHeight="1">
       <c r="A212" s="5"/>
-      <c r="B212" t="s" s="20">
-        <v>115</v>
-      </c>
-      <c r="C212" t="s" s="68">
-        <v>117</v>
-      </c>
-      <c r="D212" s="69"/>
+      <c r="B212" s="7"/>
+      <c r="C212" t="s" s="6">
+        <v>36</v>
+      </c>
+      <c r="D212" t="s" s="34">
+        <v>37</v>
+      </c>
       <c r="E212" s="13"/>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
     </row>
-    <row r="213" ht="13.65" customHeight="1">
-      <c r="A213" s="2"/>
-      <c r="B213" s="60"/>
-      <c r="C213" s="60"/>
-      <c r="D213" s="60"/>
-      <c r="E213" s="2"/>
+    <row r="213" ht="15" customHeight="1">
+      <c r="A213" s="5"/>
+      <c r="B213" s="7"/>
+      <c r="C213" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="D213" t="s" s="34">
+        <v>39</v>
+      </c>
+      <c r="E213" s="13"/>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" ht="13.65" customHeight="1">
+    <row r="214" ht="15" customHeight="1">
       <c r="A214" s="5"/>
-      <c r="B214" t="s" s="68">
-        <v>118</v>
-      </c>
-      <c r="C214" s="69"/>
-      <c r="D214" s="69"/>
+      <c r="B214" s="7"/>
+      <c r="C214" t="s" s="6">
+        <v>40</v>
+      </c>
+      <c r="D214" t="s" s="34">
+        <v>41</v>
+      </c>
       <c r="E214" s="13"/>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
@@ -5743,14 +5742,12 @@
     </row>
     <row r="215" ht="15" customHeight="1">
       <c r="A215" s="5"/>
-      <c r="B215" t="s" s="6">
-        <v>1</v>
-      </c>
-      <c r="C215" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D215" t="s" s="35">
-        <v>6</v>
+      <c r="B215" s="7"/>
+      <c r="C215" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D215" t="s" s="34">
+        <v>43</v>
       </c>
       <c r="E215" s="13"/>
       <c r="F215" s="2"/>
@@ -5761,10 +5758,10 @@
       <c r="A216" s="5"/>
       <c r="B216" s="7"/>
       <c r="C216" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D216" t="s" s="35">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="D216" s="36">
+        <v>41648</v>
       </c>
       <c r="E216" s="13"/>
       <c r="F216" s="2"/>
@@ -5775,10 +5772,10 @@
       <c r="A217" s="5"/>
       <c r="B217" s="7"/>
       <c r="C217" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D217" t="s" s="35">
-        <v>38</v>
+        <v>68</v>
+      </c>
+      <c r="D217" s="36">
+        <v>40919</v>
       </c>
       <c r="E217" s="13"/>
       <c r="F217" s="2"/>
@@ -5789,155 +5786,155 @@
       <c r="A218" s="5"/>
       <c r="B218" s="7"/>
       <c r="C218" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D218" t="s" s="35">
-        <v>40</v>
+        <v>112</v>
+      </c>
+      <c r="D218" t="s" s="6">
+        <v>113</v>
       </c>
       <c r="E218" s="13"/>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
     </row>
-    <row r="219" ht="15" customHeight="1">
+    <row r="219" ht="9" customHeight="1" hidden="1">
       <c r="A219" s="5"/>
-      <c r="B219" s="7"/>
-      <c r="C219" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D219" t="s" s="35">
-        <v>42</v>
-      </c>
+      <c r="B219" t="s" s="68">
+        <v>118</v>
+      </c>
+      <c r="C219" s="69"/>
+      <c r="D219" s="69"/>
       <c r="E219" s="13"/>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
     </row>
-    <row r="220" ht="15" customHeight="1">
+    <row r="220" ht="9" customHeight="1" hidden="1">
       <c r="A220" s="5"/>
-      <c r="B220" s="7"/>
-      <c r="C220" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D220" t="s" s="35">
-        <v>44</v>
-      </c>
+      <c r="B220" t="s" s="68">
+        <v>119</v>
+      </c>
+      <c r="C220" s="69"/>
+      <c r="D220" s="69"/>
       <c r="E220" s="13"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
     </row>
-    <row r="221" ht="15" customHeight="1">
-      <c r="A221" s="5"/>
-      <c r="B221" s="7"/>
-      <c r="C221" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D221" s="36">
-        <v>41648</v>
-      </c>
-      <c r="E221" s="13"/>
+    <row r="221" ht="13.65" customHeight="1">
+      <c r="A221" s="2"/>
+      <c r="B221" s="28"/>
+      <c r="C221" s="28"/>
+      <c r="D221" s="28"/>
+      <c r="E221" s="2"/>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
     </row>
-    <row r="222" ht="15" customHeight="1">
-      <c r="A222" s="5"/>
-      <c r="B222" s="7"/>
-      <c r="C222" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D222" s="36">
-        <v>40919</v>
-      </c>
-      <c r="E222" s="13"/>
+    <row r="222" ht="13.65" customHeight="1">
+      <c r="A222" s="2"/>
+      <c r="B222" s="72"/>
+      <c r="C222" s="72"/>
+      <c r="D222" s="72"/>
+      <c r="E222" s="72"/>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
     </row>
-    <row r="223" ht="15" customHeight="1">
-      <c r="A223" s="5"/>
-      <c r="B223" s="7"/>
-      <c r="C223" t="s" s="6">
-        <v>113</v>
-      </c>
-      <c r="D223" t="s" s="6">
-        <v>114</v>
-      </c>
-      <c r="E223" s="13"/>
-      <c r="F223" s="2"/>
+    <row r="223" ht="13.65" customHeight="1">
+      <c r="A223" s="38"/>
+      <c r="B223" t="s" s="73">
+        <v>120</v>
+      </c>
+      <c r="C223" s="74"/>
+      <c r="D223" s="74"/>
+      <c r="E223" s="74"/>
+      <c r="F223" s="9"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
     </row>
-    <row r="224" ht="9" customHeight="1" hidden="1">
+    <row r="224" ht="15" customHeight="1">
       <c r="A224" s="5"/>
-      <c r="B224" t="s" s="68">
-        <v>119</v>
-      </c>
-      <c r="C224" s="69"/>
-      <c r="D224" s="69"/>
-      <c r="E224" s="13"/>
+      <c r="B224" t="s" s="10">
+        <v>1</v>
+      </c>
+      <c r="C224" t="s" s="6">
+        <v>64</v>
+      </c>
+      <c r="D224" t="b" s="67">
+        <v>1</v>
+      </c>
+      <c r="E224" s="75"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
     </row>
-    <row r="225" ht="9" customHeight="1" hidden="1">
+    <row r="225" ht="15" customHeight="1">
       <c r="A225" s="5"/>
-      <c r="B225" t="s" s="68">
-        <v>120</v>
-      </c>
-      <c r="C225" s="69"/>
-      <c r="D225" s="69"/>
-      <c r="E225" s="13"/>
+      <c r="B225" s="14"/>
+      <c r="C225" t="s" s="6">
+        <v>2</v>
+      </c>
+      <c r="D225" t="b" s="67">
+        <v>1</v>
+      </c>
+      <c r="E225" s="76"/>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
     </row>
-    <row r="226" ht="13.65" customHeight="1">
-      <c r="A226" s="2"/>
-      <c r="B226" s="28"/>
-      <c r="C226" s="28"/>
-      <c r="D226" s="28"/>
-      <c r="E226" s="2"/>
-      <c r="F226" s="2"/>
+    <row r="226" ht="15" customHeight="1">
+      <c r="A226" s="5"/>
+      <c r="B226" s="14"/>
+      <c r="C226" t="s" s="6">
+        <v>3</v>
+      </c>
+      <c r="D226" t="b" s="67">
+        <v>1</v>
+      </c>
+      <c r="E226" s="77"/>
+      <c r="F226" s="13"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
     </row>
-    <row r="227" ht="13.65" customHeight="1">
-      <c r="A227" s="2"/>
-      <c r="B227" s="72"/>
-      <c r="C227" s="72"/>
-      <c r="D227" s="72"/>
-      <c r="E227" s="72"/>
-      <c r="F227" s="2"/>
+    <row r="227" ht="15" customHeight="1">
+      <c r="A227" s="5"/>
+      <c r="B227" s="16"/>
+      <c r="C227" t="s" s="6">
+        <v>65</v>
+      </c>
+      <c r="D227" t="s" s="6">
+        <v>66</v>
+      </c>
+      <c r="E227" s="33"/>
+      <c r="F227" s="13"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
     </row>
-    <row r="228" ht="13.65" customHeight="1">
-      <c r="A228" s="38"/>
-      <c r="B228" t="s" s="73">
-        <v>121</v>
-      </c>
-      <c r="C228" s="74"/>
-      <c r="D228" s="74"/>
-      <c r="E228" s="74"/>
-      <c r="F228" s="9"/>
+    <row r="228" ht="15" customHeight="1">
+      <c r="A228" s="5"/>
+      <c r="B228" s="14"/>
+      <c r="C228" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D228" t="s" s="6">
+        <v>5</v>
+      </c>
+      <c r="E228" s="33"/>
+      <c r="F228" s="13"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
     <row r="229" ht="15" customHeight="1">
       <c r="A229" s="5"/>
-      <c r="B229" t="s" s="10">
-        <v>1</v>
-      </c>
+      <c r="B229" s="14"/>
       <c r="C229" t="s" s="6">
-        <v>65</v>
-      </c>
-      <c r="D229" t="b" s="67">
-        <v>1</v>
-      </c>
-      <c r="E229" s="75"/>
-      <c r="F229" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="D229" t="s" s="6">
+        <v>121</v>
+      </c>
+      <c r="E229" s="33"/>
+      <c r="F229" s="13"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
     </row>
@@ -5945,13 +5942,13 @@
       <c r="A230" s="5"/>
       <c r="B230" s="14"/>
       <c r="C230" t="s" s="6">
-        <v>2</v>
-      </c>
-      <c r="D230" t="b" s="67">
-        <v>1</v>
-      </c>
-      <c r="E230" s="76"/>
-      <c r="F230" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="D230" t="s" s="6">
+        <v>9</v>
+      </c>
+      <c r="E230" s="33"/>
+      <c r="F230" s="13"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
     </row>
@@ -5959,24 +5956,24 @@
       <c r="A231" s="5"/>
       <c r="B231" s="14"/>
       <c r="C231" t="s" s="6">
-        <v>3</v>
-      </c>
-      <c r="D231" t="b" s="67">
-        <v>1</v>
-      </c>
-      <c r="E231" s="77"/>
+        <v>10</v>
+      </c>
+      <c r="D231" t="s" s="6">
+        <v>11</v>
+      </c>
+      <c r="E231" s="33"/>
       <c r="F231" s="13"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
     </row>
     <row r="232" ht="15" customHeight="1">
       <c r="A232" s="5"/>
-      <c r="B232" s="16"/>
+      <c r="B232" s="14"/>
       <c r="C232" t="s" s="6">
-        <v>4</v>
-      </c>
-      <c r="D232" t="b" s="67">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D232" t="s" s="6">
+        <v>13</v>
       </c>
       <c r="E232" s="33"/>
       <c r="F232" s="13"/>
@@ -5987,10 +5984,10 @@
       <c r="A233" s="5"/>
       <c r="B233" s="14"/>
       <c r="C233" t="s" s="6">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="D233" t="s" s="6">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="E233" s="33"/>
       <c r="F233" s="13"/>
@@ -6001,10 +5998,10 @@
       <c r="A234" s="5"/>
       <c r="B234" s="14"/>
       <c r="C234" t="s" s="6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D234" t="s" s="6">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E234" s="33"/>
       <c r="F234" s="13"/>
@@ -6015,10 +6012,10 @@
       <c r="A235" s="5"/>
       <c r="B235" s="14"/>
       <c r="C235" t="s" s="6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D235" t="s" s="6">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="E235" s="33"/>
       <c r="F235" s="13"/>
@@ -6029,10 +6026,10 @@
       <c r="A236" s="5"/>
       <c r="B236" s="14"/>
       <c r="C236" t="s" s="6">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D236" t="s" s="6">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E236" s="33"/>
       <c r="F236" s="13"/>
@@ -6043,10 +6040,10 @@
       <c r="A237" s="5"/>
       <c r="B237" s="14"/>
       <c r="C237" t="s" s="6">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D237" t="s" s="6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E237" s="33"/>
       <c r="F237" s="13"/>
@@ -6057,10 +6054,10 @@
       <c r="A238" s="5"/>
       <c r="B238" s="14"/>
       <c r="C238" t="s" s="6">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D238" t="s" s="6">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E238" s="33"/>
       <c r="F238" s="13"/>
@@ -6071,10 +6068,10 @@
       <c r="A239" s="5"/>
       <c r="B239" s="14"/>
       <c r="C239" t="s" s="6">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D239" t="s" s="6">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E239" s="33"/>
       <c r="F239" s="13"/>
@@ -6085,10 +6082,10 @@
       <c r="A240" s="5"/>
       <c r="B240" s="14"/>
       <c r="C240" t="s" s="6">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D240" t="s" s="6">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E240" s="33"/>
       <c r="F240" s="13"/>
@@ -6099,10 +6096,10 @@
       <c r="A241" s="5"/>
       <c r="B241" s="14"/>
       <c r="C241" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="D241" t="s" s="6">
-        <v>20</v>
+        <v>30</v>
+      </c>
+      <c r="D241" s="77">
+        <v>41298</v>
       </c>
       <c r="E241" s="33"/>
       <c r="F241" s="13"/>
@@ -6113,10 +6110,10 @@
       <c r="A242" s="5"/>
       <c r="B242" s="14"/>
       <c r="C242" t="s" s="6">
-        <v>21</v>
-      </c>
-      <c r="D242" t="s" s="6">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="D242" s="77">
+        <v>41275</v>
       </c>
       <c r="E242" s="33"/>
       <c r="F242" s="13"/>
@@ -6127,10 +6124,10 @@
       <c r="A243" s="5"/>
       <c r="B243" s="14"/>
       <c r="C243" t="s" s="6">
-        <v>23</v>
-      </c>
-      <c r="D243" t="s" s="6">
-        <v>24</v>
+        <v>32</v>
+      </c>
+      <c r="D243" s="77">
+        <v>41670</v>
       </c>
       <c r="E243" s="33"/>
       <c r="F243" s="13"/>
@@ -6141,10 +6138,10 @@
       <c r="A244" s="5"/>
       <c r="B244" s="14"/>
       <c r="C244" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="D244" t="s" s="6">
-        <v>26</v>
+        <v>33</v>
+      </c>
+      <c r="D244" s="77">
+        <v>41646</v>
       </c>
       <c r="E244" s="33"/>
       <c r="F244" s="13"/>
@@ -6155,10 +6152,10 @@
       <c r="A245" s="5"/>
       <c r="B245" s="14"/>
       <c r="C245" t="s" s="6">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D245" t="s" s="6">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E245" s="33"/>
       <c r="F245" s="13"/>
@@ -6169,10 +6166,10 @@
       <c r="A246" s="5"/>
       <c r="B246" s="14"/>
       <c r="C246" t="s" s="6">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D246" t="s" s="6">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E246" s="33"/>
       <c r="F246" s="13"/>
@@ -6183,10 +6180,10 @@
       <c r="A247" s="5"/>
       <c r="B247" s="14"/>
       <c r="C247" t="s" s="6">
-        <v>31</v>
-      </c>
-      <c r="D247" s="77">
-        <v>41298</v>
+        <v>38</v>
+      </c>
+      <c r="D247" t="s" s="6">
+        <v>39</v>
       </c>
       <c r="E247" s="33"/>
       <c r="F247" s="13"/>
@@ -6197,10 +6194,10 @@
       <c r="A248" s="5"/>
       <c r="B248" s="14"/>
       <c r="C248" t="s" s="6">
-        <v>32</v>
-      </c>
-      <c r="D248" s="77">
-        <v>41275</v>
+        <v>40</v>
+      </c>
+      <c r="D248" t="s" s="6">
+        <v>41</v>
       </c>
       <c r="E248" s="33"/>
       <c r="F248" s="13"/>
@@ -6210,11 +6207,11 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" s="5"/>
       <c r="B249" s="14"/>
-      <c r="C249" t="s" s="6">
-        <v>33</v>
-      </c>
-      <c r="D249" s="77">
-        <v>41670</v>
+      <c r="C249" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D249" t="s" s="6">
+        <v>43</v>
       </c>
       <c r="E249" s="33"/>
       <c r="F249" s="13"/>
@@ -6225,10 +6222,10 @@
       <c r="A250" s="5"/>
       <c r="B250" s="14"/>
       <c r="C250" t="s" s="6">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D250" s="77">
-        <v>41646</v>
+        <v>41648</v>
       </c>
       <c r="E250" s="33"/>
       <c r="F250" s="13"/>
@@ -6239,299 +6236,299 @@
       <c r="A251" s="5"/>
       <c r="B251" s="14"/>
       <c r="C251" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D251" t="s" s="6">
-        <v>36</v>
+        <v>68</v>
+      </c>
+      <c r="D251" s="77">
+        <v>40919</v>
       </c>
       <c r="E251" s="33"/>
       <c r="F251" s="13"/>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
     </row>
-    <row r="252" ht="15" customHeight="1">
-      <c r="A252" s="5"/>
-      <c r="B252" s="14"/>
-      <c r="C252" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D252" t="s" s="6">
-        <v>38</v>
-      </c>
-      <c r="E252" s="33"/>
-      <c r="F252" s="13"/>
+    <row r="252" ht="9" customHeight="1" hidden="1">
+      <c r="A252" s="38"/>
+      <c r="B252" t="s" s="78">
+        <v>122</v>
+      </c>
+      <c r="C252" t="s" s="79">
+        <v>123</v>
+      </c>
+      <c r="D252" t="s" s="79">
+        <v>124</v>
+      </c>
+      <c r="E252" t="s" s="79">
+        <v>125</v>
+      </c>
+      <c r="F252" s="9"/>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
     </row>
-    <row r="253" ht="15" customHeight="1">
-      <c r="A253" s="5"/>
-      <c r="B253" s="14"/>
-      <c r="C253" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D253" t="s" s="6">
-        <v>40</v>
-      </c>
-      <c r="E253" s="33"/>
-      <c r="F253" s="13"/>
+    <row r="253" ht="9" customHeight="1" hidden="1">
+      <c r="A253" s="38"/>
+      <c r="B253" s="80">
+        <v>1</v>
+      </c>
+      <c r="C253" t="s" s="81">
+        <v>126</v>
+      </c>
+      <c r="D253" t="s" s="81">
+        <v>127</v>
+      </c>
+      <c r="E253" t="s" s="81">
+        <v>128</v>
+      </c>
+      <c r="F253" s="9"/>
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
     </row>
-    <row r="254" ht="15" customHeight="1">
-      <c r="A254" s="5"/>
-      <c r="B254" s="14"/>
-      <c r="C254" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D254" t="s" s="6">
-        <v>42</v>
-      </c>
-      <c r="E254" s="33"/>
-      <c r="F254" s="13"/>
+    <row r="254" ht="9" customHeight="1" hidden="1">
+      <c r="A254" s="38"/>
+      <c r="B254" s="80">
+        <v>2</v>
+      </c>
+      <c r="C254" t="s" s="81">
+        <v>129</v>
+      </c>
+      <c r="D254" t="s" s="81">
+        <v>130</v>
+      </c>
+      <c r="E254" t="s" s="81">
+        <v>131</v>
+      </c>
+      <c r="F254" s="9"/>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
     </row>
-    <row r="255" ht="15" customHeight="1">
-      <c r="A255" s="5"/>
-      <c r="B255" s="14"/>
-      <c r="C255" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D255" t="s" s="6">
-        <v>44</v>
-      </c>
-      <c r="E255" s="33"/>
-      <c r="F255" s="13"/>
+    <row r="255" ht="9" customHeight="1" hidden="1">
+      <c r="A255" s="38"/>
+      <c r="B255" s="80">
+        <v>3</v>
+      </c>
+      <c r="C255" t="s" s="81">
+        <v>132</v>
+      </c>
+      <c r="D255" t="s" s="81">
+        <v>133</v>
+      </c>
+      <c r="E255" t="s" s="81">
+        <v>134</v>
+      </c>
+      <c r="F255" s="9"/>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
     </row>
-    <row r="256" ht="15" customHeight="1">
-      <c r="A256" s="5"/>
-      <c r="B256" s="14"/>
-      <c r="C256" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D256" s="77">
-        <v>41648</v>
-      </c>
-      <c r="E256" s="33"/>
-      <c r="F256" s="13"/>
+    <row r="256" ht="9" customHeight="1" hidden="1">
+      <c r="A256" s="38"/>
+      <c r="B256" s="80">
+        <v>4</v>
+      </c>
+      <c r="C256" t="s" s="81">
+        <v>135</v>
+      </c>
+      <c r="D256" t="s" s="81">
+        <v>136</v>
+      </c>
+      <c r="E256" t="s" s="81">
+        <v>137</v>
+      </c>
+      <c r="F256" s="9"/>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" ht="15" customHeight="1">
-      <c r="A257" s="5"/>
-      <c r="B257" s="14"/>
-      <c r="C257" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D257" s="77">
-        <v>40919</v>
-      </c>
-      <c r="E257" s="33"/>
-      <c r="F257" s="13"/>
+    <row r="257" ht="9" customHeight="1" hidden="1">
+      <c r="A257" s="38"/>
+      <c r="B257" s="80">
+        <v>5</v>
+      </c>
+      <c r="C257" t="s" s="81">
+        <v>138</v>
+      </c>
+      <c r="D257" t="s" s="81">
+        <v>139</v>
+      </c>
+      <c r="E257" t="s" s="81">
+        <v>140</v>
+      </c>
+      <c r="F257" s="9"/>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
     </row>
     <row r="258" ht="9" customHeight="1" hidden="1">
       <c r="A258" s="38"/>
-      <c r="B258" t="s" s="78">
-        <v>123</v>
-      </c>
-      <c r="C258" t="s" s="79">
-        <v>124</v>
-      </c>
-      <c r="D258" t="s" s="79">
-        <v>125</v>
-      </c>
-      <c r="E258" t="s" s="79">
-        <v>126</v>
+      <c r="B258" s="80">
+        <v>6</v>
+      </c>
+      <c r="C258" t="s" s="81">
+        <v>141</v>
+      </c>
+      <c r="D258" t="s" s="81">
+        <v>142</v>
+      </c>
+      <c r="E258" t="s" s="81">
+        <v>143</v>
       </c>
       <c r="F258" s="9"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
     </row>
-    <row r="259" ht="9" customHeight="1" hidden="1">
-      <c r="A259" s="38"/>
-      <c r="B259" s="80">
-        <v>1</v>
-      </c>
-      <c r="C259" t="s" s="81">
-        <v>127</v>
-      </c>
-      <c r="D259" t="s" s="81">
-        <v>128</v>
-      </c>
-      <c r="E259" t="s" s="81">
-        <v>129</v>
-      </c>
-      <c r="F259" s="9"/>
+    <row r="259" ht="13.65" customHeight="1">
+      <c r="A259" s="2"/>
+      <c r="B259" s="82"/>
+      <c r="C259" s="28"/>
+      <c r="D259" s="28"/>
+      <c r="E259" s="28"/>
+      <c r="F259" s="2"/>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
     </row>
-    <row r="260" ht="9" customHeight="1" hidden="1">
-      <c r="A260" s="38"/>
-      <c r="B260" s="80">
-        <v>2</v>
-      </c>
-      <c r="C260" t="s" s="81">
-        <v>130</v>
-      </c>
-      <c r="D260" t="s" s="81">
-        <v>131</v>
-      </c>
-      <c r="E260" t="s" s="81">
-        <v>132</v>
-      </c>
-      <c r="F260" s="9"/>
+    <row r="260" ht="13.65" customHeight="1">
+      <c r="A260" s="2"/>
+      <c r="B260" s="3"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="2"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
     </row>
-    <row r="261" ht="9" customHeight="1" hidden="1">
-      <c r="A261" s="38"/>
-      <c r="B261" s="80">
-        <v>3</v>
-      </c>
-      <c r="C261" t="s" s="81">
-        <v>133</v>
-      </c>
-      <c r="D261" t="s" s="81">
-        <v>134</v>
-      </c>
-      <c r="E261" t="s" s="81">
-        <v>135</v>
-      </c>
-      <c r="F261" s="9"/>
+    <row r="261" ht="13.65" customHeight="1">
+      <c r="A261" s="5"/>
+      <c r="B261" t="s" s="83">
+        <v>144</v>
+      </c>
+      <c r="C261" s="40"/>
+      <c r="D261" s="84"/>
+      <c r="E261" s="29"/>
+      <c r="F261" s="2"/>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
     </row>
-    <row r="262" ht="9" customHeight="1" hidden="1">
-      <c r="A262" s="38"/>
-      <c r="B262" s="80">
-        <v>4</v>
-      </c>
-      <c r="C262" t="s" s="81">
-        <v>136</v>
-      </c>
-      <c r="D262" t="s" s="81">
-        <v>137</v>
-      </c>
-      <c r="E262" t="s" s="81">
-        <v>138</v>
-      </c>
+    <row r="262" ht="15" customHeight="1">
+      <c r="A262" s="5"/>
+      <c r="B262" t="s" s="6">
+        <v>1</v>
+      </c>
+      <c r="C262" t="s" s="6">
+        <v>64</v>
+      </c>
+      <c r="D262" t="b" s="30">
+        <v>1</v>
+      </c>
+      <c r="E262" s="31"/>
       <c r="F262" s="9"/>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
     </row>
-    <row r="263" ht="9" customHeight="1" hidden="1">
-      <c r="A263" s="38"/>
-      <c r="B263" s="80">
-        <v>5</v>
-      </c>
-      <c r="C263" t="s" s="81">
-        <v>139</v>
-      </c>
-      <c r="D263" t="s" s="81">
-        <v>140</v>
-      </c>
-      <c r="E263" t="s" s="81">
-        <v>141</v>
-      </c>
+    <row r="263" ht="15" customHeight="1">
+      <c r="A263" s="5"/>
+      <c r="B263" s="7"/>
+      <c r="C263" t="s" s="6">
+        <v>2</v>
+      </c>
+      <c r="D263" t="b" s="30">
+        <v>1</v>
+      </c>
+      <c r="E263" s="32"/>
       <c r="F263" s="9"/>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
     </row>
-    <row r="264" ht="9" customHeight="1" hidden="1">
-      <c r="A264" s="38"/>
-      <c r="B264" s="80">
-        <v>6</v>
-      </c>
-      <c r="C264" t="s" s="81">
-        <v>142</v>
-      </c>
-      <c r="D264" t="s" s="81">
-        <v>143</v>
-      </c>
-      <c r="E264" t="s" s="81">
-        <v>144</v>
-      </c>
+    <row r="264" ht="15" customHeight="1">
+      <c r="A264" s="5"/>
+      <c r="B264" s="7"/>
+      <c r="C264" t="s" s="6">
+        <v>3</v>
+      </c>
+      <c r="D264" t="b" s="30">
+        <v>1</v>
+      </c>
+      <c r="E264" s="32"/>
       <c r="F264" s="9"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
     </row>
-    <row r="265" ht="13.65" customHeight="1">
-      <c r="A265" s="2"/>
-      <c r="B265" s="82"/>
-      <c r="C265" s="28"/>
-      <c r="D265" s="28"/>
-      <c r="E265" s="28"/>
+    <row r="265" ht="15" customHeight="1">
+      <c r="A265" s="5"/>
+      <c r="B265" s="33"/>
+      <c r="C265" t="s" s="6">
+        <v>65</v>
+      </c>
+      <c r="D265" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="E265" s="35"/>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
     </row>
-    <row r="266" ht="13.65" customHeight="1">
-      <c r="A266" s="2"/>
-      <c r="B266" s="3"/>
-      <c r="C266" s="2"/>
-      <c r="D266" s="2"/>
-      <c r="E266" s="2"/>
+    <row r="266" ht="15" customHeight="1">
+      <c r="A266" s="5"/>
+      <c r="B266" s="33"/>
+      <c r="C266" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D266" t="s" s="34">
+        <v>5</v>
+      </c>
+      <c r="E266" s="13"/>
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
     </row>
-    <row r="267" ht="13.65" customHeight="1">
+    <row r="267" ht="15" customHeight="1">
       <c r="A267" s="5"/>
-      <c r="B267" t="s" s="83">
+      <c r="B267" s="33"/>
+      <c r="C267" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="D267" t="s" s="34">
         <v>145</v>
       </c>
-      <c r="C267" s="40"/>
-      <c r="D267" s="84"/>
-      <c r="E267" s="29"/>
+      <c r="E267" s="13"/>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
     </row>
     <row r="268" ht="15" customHeight="1">
       <c r="A268" s="5"/>
-      <c r="B268" t="s" s="6">
-        <v>1</v>
-      </c>
+      <c r="B268" s="33"/>
       <c r="C268" t="s" s="6">
-        <v>65</v>
-      </c>
-      <c r="D268" t="b" s="30">
-        <v>1</v>
-      </c>
-      <c r="E268" s="31"/>
-      <c r="F268" s="9"/>
+        <v>8</v>
+      </c>
+      <c r="D268" t="s" s="34">
+        <v>9</v>
+      </c>
+      <c r="E268" s="13"/>
+      <c r="F268" s="2"/>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
     </row>
     <row r="269" ht="15" customHeight="1">
       <c r="A269" s="5"/>
-      <c r="B269" s="7"/>
+      <c r="B269" s="33"/>
       <c r="C269" t="s" s="6">
-        <v>2</v>
-      </c>
-      <c r="D269" t="b" s="30">
-        <v>1</v>
-      </c>
-      <c r="E269" s="32"/>
-      <c r="F269" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="D269" t="s" s="34">
+        <v>11</v>
+      </c>
+      <c r="E269" s="13"/>
+      <c r="F269" s="2"/>
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c r="A270" s="5"/>
-      <c r="B270" s="7"/>
+      <c r="B270" s="33"/>
       <c r="C270" t="s" s="6">
-        <v>3</v>
-      </c>
-      <c r="D270" t="b" s="30">
-        <v>1</v>
-      </c>
-      <c r="E270" s="32"/>
-      <c r="F270" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="D270" t="s" s="34">
+        <v>13</v>
+      </c>
+      <c r="E270" s="13"/>
+      <c r="F270" s="2"/>
       <c r="G270" s="2"/>
       <c r="H270" s="2"/>
     </row>
@@ -6539,12 +6536,12 @@
       <c r="A271" s="5"/>
       <c r="B271" s="33"/>
       <c r="C271" t="s" s="6">
-        <v>4</v>
-      </c>
-      <c r="D271" t="b" s="30">
-        <v>1</v>
-      </c>
-      <c r="E271" s="34"/>
+        <v>14</v>
+      </c>
+      <c r="D271" t="s" s="34">
+        <v>15</v>
+      </c>
+      <c r="E271" s="13"/>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
@@ -6553,10 +6550,10 @@
       <c r="A272" s="5"/>
       <c r="B272" s="33"/>
       <c r="C272" t="s" s="6">
-        <v>66</v>
-      </c>
-      <c r="D272" t="s" s="35">
-        <v>67</v>
+        <v>16</v>
+      </c>
+      <c r="D272" t="s" s="34">
+        <v>17</v>
       </c>
       <c r="E272" s="13"/>
       <c r="F272" s="2"/>
@@ -6567,10 +6564,10 @@
       <c r="A273" s="5"/>
       <c r="B273" s="33"/>
       <c r="C273" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D273" t="s" s="35">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D273" t="s" s="34">
+        <v>19</v>
       </c>
       <c r="E273" s="13"/>
       <c r="F273" s="2"/>
@@ -6581,10 +6578,10 @@
       <c r="A274" s="5"/>
       <c r="B274" s="33"/>
       <c r="C274" t="s" s="6">
-        <v>7</v>
-      </c>
-      <c r="D274" t="s" s="35">
-        <v>146</v>
+        <v>20</v>
+      </c>
+      <c r="D274" t="s" s="34">
+        <v>21</v>
       </c>
       <c r="E274" s="13"/>
       <c r="F274" s="2"/>
@@ -6595,10 +6592,10 @@
       <c r="A275" s="5"/>
       <c r="B275" s="33"/>
       <c r="C275" t="s" s="6">
-        <v>9</v>
-      </c>
-      <c r="D275" t="s" s="35">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="D275" t="s" s="34">
+        <v>23</v>
       </c>
       <c r="E275" s="13"/>
       <c r="F275" s="2"/>
@@ -6609,10 +6606,10 @@
       <c r="A276" s="5"/>
       <c r="B276" s="33"/>
       <c r="C276" t="s" s="6">
-        <v>11</v>
-      </c>
-      <c r="D276" t="s" s="35">
-        <v>12</v>
+        <v>24</v>
+      </c>
+      <c r="D276" t="s" s="34">
+        <v>25</v>
       </c>
       <c r="E276" s="13"/>
       <c r="F276" s="2"/>
@@ -6623,10 +6620,10 @@
       <c r="A277" s="5"/>
       <c r="B277" s="33"/>
       <c r="C277" t="s" s="6">
-        <v>13</v>
-      </c>
-      <c r="D277" t="s" s="35">
-        <v>14</v>
+        <v>26</v>
+      </c>
+      <c r="D277" t="s" s="34">
+        <v>27</v>
       </c>
       <c r="E277" s="13"/>
       <c r="F277" s="2"/>
@@ -6637,10 +6634,10 @@
       <c r="A278" s="5"/>
       <c r="B278" s="33"/>
       <c r="C278" t="s" s="6">
-        <v>15</v>
-      </c>
-      <c r="D278" t="s" s="35">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="D278" t="s" s="34">
+        <v>29</v>
       </c>
       <c r="E278" s="13"/>
       <c r="F278" s="2"/>
@@ -6651,10 +6648,10 @@
       <c r="A279" s="5"/>
       <c r="B279" s="33"/>
       <c r="C279" t="s" s="6">
-        <v>17</v>
-      </c>
-      <c r="D279" t="s" s="35">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="D279" s="36">
+        <v>41298</v>
       </c>
       <c r="E279" s="13"/>
       <c r="F279" s="2"/>
@@ -6665,10 +6662,10 @@
       <c r="A280" s="5"/>
       <c r="B280" s="33"/>
       <c r="C280" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="D280" t="s" s="35">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="D280" s="36">
+        <v>41275</v>
       </c>
       <c r="E280" s="13"/>
       <c r="F280" s="2"/>
@@ -6679,10 +6676,10 @@
       <c r="A281" s="5"/>
       <c r="B281" s="33"/>
       <c r="C281" t="s" s="6">
-        <v>21</v>
-      </c>
-      <c r="D281" t="s" s="35">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="D281" s="36">
+        <v>41670</v>
       </c>
       <c r="E281" s="13"/>
       <c r="F281" s="2"/>
@@ -6693,10 +6690,10 @@
       <c r="A282" s="5"/>
       <c r="B282" s="33"/>
       <c r="C282" t="s" s="6">
-        <v>23</v>
-      </c>
-      <c r="D282" t="s" s="35">
-        <v>24</v>
+        <v>33</v>
+      </c>
+      <c r="D282" s="36">
+        <v>41646</v>
       </c>
       <c r="E282" s="13"/>
       <c r="F282" s="2"/>
@@ -6707,10 +6704,10 @@
       <c r="A283" s="5"/>
       <c r="B283" s="33"/>
       <c r="C283" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="D283" t="s" s="35">
-        <v>26</v>
+        <v>34</v>
+      </c>
+      <c r="D283" t="s" s="34">
+        <v>35</v>
       </c>
       <c r="E283" s="13"/>
       <c r="F283" s="2"/>
@@ -6721,10 +6718,10 @@
       <c r="A284" s="5"/>
       <c r="B284" s="33"/>
       <c r="C284" t="s" s="6">
-        <v>27</v>
-      </c>
-      <c r="D284" t="s" s="35">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="D284" t="s" s="34">
+        <v>37</v>
       </c>
       <c r="E284" s="13"/>
       <c r="F284" s="2"/>
@@ -6735,10 +6732,10 @@
       <c r="A285" s="5"/>
       <c r="B285" s="33"/>
       <c r="C285" t="s" s="6">
-        <v>29</v>
-      </c>
-      <c r="D285" t="s" s="35">
-        <v>30</v>
+        <v>38</v>
+      </c>
+      <c r="D285" t="s" s="34">
+        <v>39</v>
       </c>
       <c r="E285" s="13"/>
       <c r="F285" s="2"/>
@@ -6749,10 +6746,10 @@
       <c r="A286" s="5"/>
       <c r="B286" s="33"/>
       <c r="C286" t="s" s="6">
-        <v>31</v>
-      </c>
-      <c r="D286" s="36">
-        <v>41298</v>
+        <v>40</v>
+      </c>
+      <c r="D286" t="s" s="34">
+        <v>41</v>
       </c>
       <c r="E286" s="13"/>
       <c r="F286" s="2"/>
@@ -6762,11 +6759,11 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" s="5"/>
       <c r="B287" s="33"/>
-      <c r="C287" t="s" s="6">
-        <v>32</v>
-      </c>
-      <c r="D287" s="36">
-        <v>41275</v>
+      <c r="C287" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D287" t="s" s="34">
+        <v>43</v>
       </c>
       <c r="E287" s="13"/>
       <c r="F287" s="2"/>
@@ -6777,10 +6774,10 @@
       <c r="A288" s="5"/>
       <c r="B288" s="33"/>
       <c r="C288" t="s" s="6">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D288" s="36">
-        <v>41670</v>
+        <v>41648</v>
       </c>
       <c r="E288" s="13"/>
       <c r="F288" s="2"/>
@@ -6791,289 +6788,289 @@
       <c r="A289" s="5"/>
       <c r="B289" s="33"/>
       <c r="C289" t="s" s="6">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D289" s="36">
-        <v>41646</v>
+        <v>40919</v>
       </c>
       <c r="E289" s="13"/>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
     </row>
-    <row r="290" ht="15" customHeight="1">
+    <row r="290" ht="9" customHeight="1" hidden="1">
       <c r="A290" s="5"/>
-      <c r="B290" s="33"/>
-      <c r="C290" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D290" t="s" s="35">
-        <v>36</v>
+      <c r="B290" t="s" s="85">
+        <v>146</v>
+      </c>
+      <c r="C290" t="s" s="79">
+        <v>147</v>
+      </c>
+      <c r="D290" t="s" s="86">
+        <v>70</v>
       </c>
       <c r="E290" s="13"/>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
     </row>
-    <row r="291" ht="15" customHeight="1">
+    <row r="291" ht="9" customHeight="1" hidden="1">
       <c r="A291" s="5"/>
-      <c r="B291" s="33"/>
-      <c r="C291" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D291" t="s" s="35">
-        <v>38</v>
+      <c r="B291" s="87">
+        <v>1</v>
+      </c>
+      <c r="C291" t="s" s="79">
+        <v>123</v>
+      </c>
+      <c r="D291" t="s" s="86">
+        <v>126</v>
       </c>
       <c r="E291" s="13"/>
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
     </row>
-    <row r="292" ht="15" customHeight="1">
+    <row r="292" ht="9" customHeight="1" hidden="1">
       <c r="A292" s="5"/>
-      <c r="B292" s="33"/>
-      <c r="C292" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D292" t="s" s="35">
-        <v>40</v>
+      <c r="B292" s="87">
+        <v>2</v>
+      </c>
+      <c r="C292" t="s" s="79">
+        <v>124</v>
+      </c>
+      <c r="D292" t="s" s="86">
+        <v>129</v>
       </c>
       <c r="E292" s="13"/>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
     </row>
-    <row r="293" ht="15" customHeight="1">
+    <row r="293" ht="9" customHeight="1" hidden="1">
       <c r="A293" s="5"/>
-      <c r="B293" s="33"/>
-      <c r="C293" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D293" t="s" s="35">
-        <v>42</v>
+      <c r="B293" s="87">
+        <v>3</v>
+      </c>
+      <c r="C293" t="s" s="79">
+        <v>125</v>
+      </c>
+      <c r="D293" t="s" s="86">
+        <v>132</v>
       </c>
       <c r="E293" s="13"/>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
     </row>
-    <row r="294" ht="15" customHeight="1">
+    <row r="294" ht="9" customHeight="1" hidden="1">
       <c r="A294" s="5"/>
-      <c r="B294" s="33"/>
-      <c r="C294" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D294" t="s" s="35">
-        <v>44</v>
+      <c r="B294" s="87">
+        <v>4</v>
+      </c>
+      <c r="C294" t="s" s="79">
+        <v>148</v>
+      </c>
+      <c r="D294" t="s" s="86">
+        <v>135</v>
       </c>
       <c r="E294" s="13"/>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
     </row>
-    <row r="295" ht="15" customHeight="1">
+    <row r="295" ht="9" customHeight="1" hidden="1">
       <c r="A295" s="5"/>
-      <c r="B295" s="33"/>
-      <c r="C295" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D295" s="36">
-        <v>41648</v>
+      <c r="B295" s="87">
+        <v>5</v>
+      </c>
+      <c r="C295" t="s" s="79">
+        <v>149</v>
+      </c>
+      <c r="D295" t="s" s="86">
+        <v>138</v>
       </c>
       <c r="E295" s="13"/>
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
     </row>
-    <row r="296" ht="15" customHeight="1">
+    <row r="296" ht="9" customHeight="1" hidden="1">
       <c r="A296" s="5"/>
-      <c r="B296" s="33"/>
-      <c r="C296" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D296" s="36">
-        <v>40919</v>
+      <c r="B296" s="87">
+        <v>6</v>
+      </c>
+      <c r="C296" t="s" s="79">
+        <v>150</v>
+      </c>
+      <c r="D296" t="s" s="86">
+        <v>141</v>
       </c>
       <c r="E296" s="13"/>
       <c r="F296" s="2"/>
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
     </row>
-    <row r="297" ht="9" customHeight="1" hidden="1">
-      <c r="A297" s="5"/>
-      <c r="B297" t="s" s="85">
-        <v>147</v>
-      </c>
-      <c r="C297" t="s" s="79">
-        <v>148</v>
-      </c>
-      <c r="D297" t="s" s="86">
-        <v>71</v>
-      </c>
-      <c r="E297" s="13"/>
+    <row r="297" ht="13.65" customHeight="1">
+      <c r="A297" s="2"/>
+      <c r="B297" s="60"/>
+      <c r="C297" s="28"/>
+      <c r="D297" s="28"/>
+      <c r="E297" s="2"/>
       <c r="F297" s="2"/>
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
     </row>
-    <row r="298" ht="9" customHeight="1" hidden="1">
+    <row r="298" ht="15" customHeight="1">
       <c r="A298" s="5"/>
-      <c r="B298" s="87">
-        <v>1</v>
-      </c>
-      <c r="C298" t="s" s="79">
-        <v>124</v>
-      </c>
-      <c r="D298" t="s" s="86">
-        <v>127</v>
-      </c>
-      <c r="E298" s="13"/>
+      <c r="B298" t="s" s="6">
+        <v>151</v>
+      </c>
+      <c r="C298" s="76"/>
+      <c r="D298" s="84"/>
+      <c r="E298" s="29"/>
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
       <c r="H298" s="2"/>
     </row>
-    <row r="299" ht="9" customHeight="1" hidden="1">
+    <row r="299" ht="15" customHeight="1">
       <c r="A299" s="5"/>
-      <c r="B299" s="87">
-        <v>2</v>
-      </c>
-      <c r="C299" t="s" s="79">
-        <v>125</v>
-      </c>
-      <c r="D299" t="s" s="86">
-        <v>130</v>
-      </c>
-      <c r="E299" s="13"/>
-      <c r="F299" s="2"/>
+      <c r="B299" t="s" s="6">
+        <v>1</v>
+      </c>
+      <c r="C299" t="s" s="6">
+        <v>64</v>
+      </c>
+      <c r="D299" t="b" s="30">
+        <v>1</v>
+      </c>
+      <c r="E299" s="31"/>
+      <c r="F299" s="9"/>
       <c r="G299" s="2"/>
       <c r="H299" s="2"/>
     </row>
-    <row r="300" ht="9" customHeight="1" hidden="1">
+    <row r="300" ht="15" customHeight="1">
       <c r="A300" s="5"/>
-      <c r="B300" s="87">
-        <v>3</v>
-      </c>
-      <c r="C300" t="s" s="79">
-        <v>126</v>
-      </c>
-      <c r="D300" t="s" s="86">
-        <v>133</v>
-      </c>
-      <c r="E300" s="13"/>
-      <c r="F300" s="2"/>
+      <c r="B300" s="7"/>
+      <c r="C300" t="s" s="6">
+        <v>2</v>
+      </c>
+      <c r="D300" t="b" s="30">
+        <v>1</v>
+      </c>
+      <c r="E300" s="32"/>
+      <c r="F300" s="9"/>
       <c r="G300" s="2"/>
       <c r="H300" s="2"/>
     </row>
-    <row r="301" ht="9" customHeight="1" hidden="1">
+    <row r="301" ht="15" customHeight="1">
       <c r="A301" s="5"/>
-      <c r="B301" s="87">
-        <v>4</v>
-      </c>
-      <c r="C301" t="s" s="79">
-        <v>149</v>
-      </c>
-      <c r="D301" t="s" s="86">
-        <v>136</v>
-      </c>
-      <c r="E301" s="13"/>
-      <c r="F301" s="2"/>
+      <c r="B301" s="7"/>
+      <c r="C301" t="s" s="6">
+        <v>3</v>
+      </c>
+      <c r="D301" t="b" s="30">
+        <v>1</v>
+      </c>
+      <c r="E301" s="32"/>
+      <c r="F301" s="9"/>
       <c r="G301" s="2"/>
       <c r="H301" s="2"/>
     </row>
-    <row r="302" ht="9" customHeight="1" hidden="1">
+    <row r="302" ht="15" customHeight="1">
       <c r="A302" s="5"/>
-      <c r="B302" s="87">
-        <v>5</v>
-      </c>
-      <c r="C302" t="s" s="79">
-        <v>150</v>
-      </c>
-      <c r="D302" t="s" s="86">
-        <v>139</v>
-      </c>
-      <c r="E302" s="13"/>
+      <c r="B302" s="33"/>
+      <c r="C302" t="s" s="6">
+        <v>65</v>
+      </c>
+      <c r="D302" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="E302" s="35"/>
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
       <c r="H302" s="2"/>
     </row>
-    <row r="303" ht="9" customHeight="1" hidden="1">
+    <row r="303" ht="15" customHeight="1">
       <c r="A303" s="5"/>
-      <c r="B303" s="87">
-        <v>6</v>
-      </c>
-      <c r="C303" t="s" s="79">
-        <v>151</v>
-      </c>
-      <c r="D303" t="s" s="86">
-        <v>142</v>
+      <c r="B303" s="33"/>
+      <c r="C303" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D303" t="s" s="34">
+        <v>5</v>
       </c>
       <c r="E303" s="13"/>
       <c r="F303" s="2"/>
       <c r="G303" s="2"/>
       <c r="H303" s="2"/>
     </row>
-    <row r="304" ht="13.65" customHeight="1">
-      <c r="A304" s="2"/>
-      <c r="B304" s="60"/>
-      <c r="C304" s="28"/>
-      <c r="D304" s="28"/>
-      <c r="E304" s="2"/>
+    <row r="304" ht="15" customHeight="1">
+      <c r="A304" s="5"/>
+      <c r="B304" s="33"/>
+      <c r="C304" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="D304" t="s" s="34">
+        <v>152</v>
+      </c>
+      <c r="E304" s="13"/>
       <c r="F304" s="2"/>
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
     </row>
     <row r="305" ht="15" customHeight="1">
       <c r="A305" s="5"/>
-      <c r="B305" t="s" s="6">
-        <v>152</v>
-      </c>
-      <c r="C305" s="76"/>
-      <c r="D305" s="84"/>
-      <c r="E305" s="29"/>
+      <c r="B305" s="33"/>
+      <c r="C305" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="D305" t="s" s="34">
+        <v>9</v>
+      </c>
+      <c r="E305" s="13"/>
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
       <c r="H305" s="2"/>
     </row>
     <row r="306" ht="15" customHeight="1">
       <c r="A306" s="5"/>
-      <c r="B306" t="s" s="6">
-        <v>1</v>
-      </c>
+      <c r="B306" s="33"/>
       <c r="C306" t="s" s="6">
-        <v>65</v>
-      </c>
-      <c r="D306" t="b" s="30">
-        <v>1</v>
-      </c>
-      <c r="E306" s="31"/>
-      <c r="F306" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="D306" t="s" s="34">
+        <v>11</v>
+      </c>
+      <c r="E306" s="13"/>
+      <c r="F306" s="2"/>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
     </row>
     <row r="307" ht="15" customHeight="1">
       <c r="A307" s="5"/>
-      <c r="B307" s="7"/>
+      <c r="B307" s="33"/>
       <c r="C307" t="s" s="6">
-        <v>2</v>
-      </c>
-      <c r="D307" t="b" s="30">
-        <v>1</v>
-      </c>
-      <c r="E307" s="32"/>
-      <c r="F307" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="D307" t="s" s="34">
+        <v>13</v>
+      </c>
+      <c r="E307" s="13"/>
+      <c r="F307" s="2"/>
       <c r="G307" s="2"/>
       <c r="H307" s="2"/>
     </row>
     <row r="308" ht="15" customHeight="1">
       <c r="A308" s="5"/>
-      <c r="B308" s="7"/>
+      <c r="B308" s="33"/>
       <c r="C308" t="s" s="6">
-        <v>3</v>
-      </c>
-      <c r="D308" t="b" s="30">
-        <v>1</v>
-      </c>
-      <c r="E308" s="32"/>
-      <c r="F308" s="9"/>
+        <v>14</v>
+      </c>
+      <c r="D308" t="s" s="34">
+        <v>15</v>
+      </c>
+      <c r="E308" s="13"/>
+      <c r="F308" s="2"/>
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
     </row>
@@ -7081,12 +7078,12 @@
       <c r="A309" s="5"/>
       <c r="B309" s="33"/>
       <c r="C309" t="s" s="6">
-        <v>4</v>
-      </c>
-      <c r="D309" t="b" s="30">
-        <v>1</v>
-      </c>
-      <c r="E309" s="34"/>
+        <v>16</v>
+      </c>
+      <c r="D309" t="s" s="34">
+        <v>17</v>
+      </c>
+      <c r="E309" s="13"/>
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
@@ -7095,10 +7092,10 @@
       <c r="A310" s="5"/>
       <c r="B310" s="33"/>
       <c r="C310" t="s" s="6">
-        <v>66</v>
-      </c>
-      <c r="D310" t="s" s="35">
-        <v>67</v>
+        <v>18</v>
+      </c>
+      <c r="D310" t="s" s="34">
+        <v>19</v>
       </c>
       <c r="E310" s="13"/>
       <c r="F310" s="2"/>
@@ -7109,10 +7106,10 @@
       <c r="A311" s="5"/>
       <c r="B311" s="33"/>
       <c r="C311" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D311" t="s" s="35">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="D311" t="s" s="34">
+        <v>21</v>
       </c>
       <c r="E311" s="13"/>
       <c r="F311" s="2"/>
@@ -7123,10 +7120,10 @@
       <c r="A312" s="5"/>
       <c r="B312" s="33"/>
       <c r="C312" t="s" s="6">
-        <v>7</v>
-      </c>
-      <c r="D312" t="s" s="35">
-        <v>153</v>
+        <v>22</v>
+      </c>
+      <c r="D312" t="s" s="34">
+        <v>23</v>
       </c>
       <c r="E312" s="13"/>
       <c r="F312" s="2"/>
@@ -7137,10 +7134,10 @@
       <c r="A313" s="5"/>
       <c r="B313" s="33"/>
       <c r="C313" t="s" s="6">
-        <v>9</v>
-      </c>
-      <c r="D313" t="s" s="35">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="D313" t="s" s="34">
+        <v>25</v>
       </c>
       <c r="E313" s="13"/>
       <c r="F313" s="2"/>
@@ -7151,10 +7148,10 @@
       <c r="A314" s="5"/>
       <c r="B314" s="33"/>
       <c r="C314" t="s" s="6">
-        <v>11</v>
-      </c>
-      <c r="D314" t="s" s="35">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="D314" t="s" s="34">
+        <v>27</v>
       </c>
       <c r="E314" s="13"/>
       <c r="F314" s="2"/>
@@ -7165,10 +7162,10 @@
       <c r="A315" s="5"/>
       <c r="B315" s="33"/>
       <c r="C315" t="s" s="6">
-        <v>13</v>
-      </c>
-      <c r="D315" t="s" s="35">
-        <v>14</v>
+        <v>28</v>
+      </c>
+      <c r="D315" t="s" s="34">
+        <v>29</v>
       </c>
       <c r="E315" s="13"/>
       <c r="F315" s="2"/>
@@ -7179,10 +7176,10 @@
       <c r="A316" s="5"/>
       <c r="B316" s="33"/>
       <c r="C316" t="s" s="6">
-        <v>15</v>
-      </c>
-      <c r="D316" t="s" s="35">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="D316" s="36">
+        <v>41298</v>
       </c>
       <c r="E316" s="13"/>
       <c r="F316" s="2"/>
@@ -7193,10 +7190,10 @@
       <c r="A317" s="5"/>
       <c r="B317" s="33"/>
       <c r="C317" t="s" s="6">
-        <v>17</v>
-      </c>
-      <c r="D317" t="s" s="35">
-        <v>18</v>
+        <v>31</v>
+      </c>
+      <c r="D317" s="36">
+        <v>41275</v>
       </c>
       <c r="E317" s="13"/>
       <c r="F317" s="2"/>
@@ -7207,10 +7204,10 @@
       <c r="A318" s="5"/>
       <c r="B318" s="33"/>
       <c r="C318" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="D318" t="s" s="35">
-        <v>20</v>
+        <v>32</v>
+      </c>
+      <c r="D318" s="36">
+        <v>41670</v>
       </c>
       <c r="E318" s="13"/>
       <c r="F318" s="2"/>
@@ -7221,10 +7218,10 @@
       <c r="A319" s="5"/>
       <c r="B319" s="33"/>
       <c r="C319" t="s" s="6">
-        <v>21</v>
-      </c>
-      <c r="D319" t="s" s="35">
-        <v>22</v>
+        <v>33</v>
+      </c>
+      <c r="D319" s="36">
+        <v>41646</v>
       </c>
       <c r="E319" s="13"/>
       <c r="F319" s="2"/>
@@ -7235,10 +7232,10 @@
       <c r="A320" s="5"/>
       <c r="B320" s="33"/>
       <c r="C320" t="s" s="6">
-        <v>23</v>
-      </c>
-      <c r="D320" t="s" s="35">
-        <v>24</v>
+        <v>34</v>
+      </c>
+      <c r="D320" t="s" s="34">
+        <v>35</v>
       </c>
       <c r="E320" s="13"/>
       <c r="F320" s="2"/>
@@ -7249,10 +7246,10 @@
       <c r="A321" s="5"/>
       <c r="B321" s="33"/>
       <c r="C321" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="D321" t="s" s="35">
-        <v>26</v>
+        <v>36</v>
+      </c>
+      <c r="D321" t="s" s="34">
+        <v>37</v>
       </c>
       <c r="E321" s="13"/>
       <c r="F321" s="2"/>
@@ -7263,10 +7260,10 @@
       <c r="A322" s="5"/>
       <c r="B322" s="33"/>
       <c r="C322" t="s" s="6">
-        <v>27</v>
-      </c>
-      <c r="D322" t="s" s="35">
-        <v>28</v>
+        <v>38</v>
+      </c>
+      <c r="D322" t="s" s="34">
+        <v>39</v>
       </c>
       <c r="E322" s="13"/>
       <c r="F322" s="2"/>
@@ -7277,10 +7274,10 @@
       <c r="A323" s="5"/>
       <c r="B323" s="33"/>
       <c r="C323" t="s" s="6">
-        <v>29</v>
-      </c>
-      <c r="D323" t="s" s="35">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="D323" t="s" s="34">
+        <v>41</v>
       </c>
       <c r="E323" s="13"/>
       <c r="F323" s="2"/>
@@ -7290,11 +7287,11 @@
     <row r="324" ht="15" customHeight="1">
       <c r="A324" s="5"/>
       <c r="B324" s="33"/>
-      <c r="C324" t="s" s="6">
-        <v>31</v>
-      </c>
-      <c r="D324" s="36">
-        <v>41298</v>
+      <c r="C324" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D324" t="s" s="34">
+        <v>43</v>
       </c>
       <c r="E324" s="13"/>
       <c r="F324" s="2"/>
@@ -7305,10 +7302,10 @@
       <c r="A325" s="5"/>
       <c r="B325" s="33"/>
       <c r="C325" t="s" s="6">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D325" s="36">
-        <v>41275</v>
+        <v>41648</v>
       </c>
       <c r="E325" s="13"/>
       <c r="F325" s="2"/>
@@ -7319,109 +7316,107 @@
       <c r="A326" s="5"/>
       <c r="B326" s="33"/>
       <c r="C326" t="s" s="6">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D326" s="36">
-        <v>41670</v>
+        <v>40919</v>
       </c>
       <c r="E326" s="13"/>
       <c r="F326" s="2"/>
       <c r="G326" s="2"/>
       <c r="H326" s="2"/>
     </row>
-    <row r="327" ht="15" customHeight="1">
+    <row r="327" ht="9" customHeight="1" hidden="1">
       <c r="A327" s="5"/>
-      <c r="B327" s="33"/>
+      <c r="B327" t="s" s="6">
+        <v>153</v>
+      </c>
       <c r="C327" t="s" s="6">
-        <v>34</v>
-      </c>
-      <c r="D327" s="36">
-        <v>41646</v>
+        <v>154</v>
+      </c>
+      <c r="D327" t="s" s="6">
+        <v>71</v>
       </c>
       <c r="E327" s="13"/>
       <c r="F327" s="2"/>
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
     </row>
-    <row r="328" ht="15" customHeight="1">
+    <row r="328" ht="9" customHeight="1" hidden="1">
       <c r="A328" s="5"/>
-      <c r="B328" s="33"/>
+      <c r="B328" t="s" s="6">
+        <v>153</v>
+      </c>
       <c r="C328" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D328" t="s" s="35">
-        <v>36</v>
+        <v>155</v>
+      </c>
+      <c r="D328" t="s" s="6">
+        <v>72</v>
       </c>
       <c r="E328" s="13"/>
       <c r="F328" s="2"/>
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
     </row>
-    <row r="329" ht="15" customHeight="1">
+    <row r="329" ht="9" customHeight="1" hidden="1">
       <c r="A329" s="5"/>
-      <c r="B329" s="33"/>
+      <c r="B329" t="s" s="6">
+        <v>156</v>
+      </c>
       <c r="C329" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D329" t="s" s="35">
-        <v>38</v>
+        <v>157</v>
+      </c>
+      <c r="D329" s="67">
+        <v>3</v>
       </c>
       <c r="E329" s="13"/>
       <c r="F329" s="2"/>
       <c r="G329" s="2"/>
       <c r="H329" s="2"/>
     </row>
-    <row r="330" ht="15" customHeight="1">
+    <row r="330" ht="9" customHeight="1" hidden="1">
       <c r="A330" s="5"/>
-      <c r="B330" s="33"/>
+      <c r="B330" t="s" s="6">
+        <v>158</v>
+      </c>
       <c r="C330" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D330" t="s" s="35">
-        <v>40</v>
+        <v>92</v>
+      </c>
+      <c r="D330" s="67">
+        <v>23</v>
       </c>
       <c r="E330" s="13"/>
       <c r="F330" s="2"/>
       <c r="G330" s="2"/>
       <c r="H330" s="2"/>
     </row>
-    <row r="331" ht="15" customHeight="1">
-      <c r="A331" s="5"/>
-      <c r="B331" s="33"/>
-      <c r="C331" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D331" t="s" s="35">
-        <v>42</v>
-      </c>
-      <c r="E331" s="13"/>
+    <row r="331" ht="13.65" customHeight="1">
+      <c r="A331" s="2"/>
+      <c r="B331" s="28"/>
+      <c r="C331" s="28"/>
+      <c r="D331" s="28"/>
+      <c r="E331" s="2"/>
       <c r="F331" s="2"/>
       <c r="G331" s="2"/>
       <c r="H331" s="2"/>
     </row>
-    <row r="332" ht="15" customHeight="1">
-      <c r="A332" s="5"/>
-      <c r="B332" s="33"/>
-      <c r="C332" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D332" t="s" s="35">
-        <v>44</v>
-      </c>
-      <c r="E332" s="13"/>
+    <row r="332" ht="13.65" customHeight="1">
+      <c r="A332" s="2"/>
+      <c r="B332" s="3"/>
+      <c r="C332" s="3"/>
+      <c r="D332" s="3"/>
+      <c r="E332" s="2"/>
       <c r="F332" s="2"/>
       <c r="G332" s="2"/>
       <c r="H332" s="2"/>
     </row>
     <row r="333" ht="15" customHeight="1">
       <c r="A333" s="5"/>
-      <c r="B333" s="33"/>
-      <c r="C333" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D333" s="36">
-        <v>41648</v>
-      </c>
+      <c r="B333" t="s" s="6">
+        <v>159</v>
+      </c>
+      <c r="C333" s="7"/>
+      <c r="D333" s="7"/>
       <c r="E333" s="13"/>
       <c r="F333" s="2"/>
       <c r="G333" s="2"/>
@@ -7429,167 +7424,159 @@
     </row>
     <row r="334" ht="15" customHeight="1">
       <c r="A334" s="5"/>
-      <c r="B334" s="33"/>
+      <c r="B334" t="s" s="6">
+        <v>1</v>
+      </c>
       <c r="C334" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D334" s="36">
-        <v>40919</v>
+        <v>4</v>
+      </c>
+      <c r="D334" t="s" s="34">
+        <v>5</v>
       </c>
       <c r="E334" s="13"/>
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
     </row>
-    <row r="335" ht="9" customHeight="1" hidden="1">
+    <row r="335" ht="15" customHeight="1">
       <c r="A335" s="5"/>
-      <c r="B335" t="s" s="6">
-        <v>154</v>
-      </c>
+      <c r="B335" s="7"/>
       <c r="C335" t="s" s="6">
-        <v>155</v>
-      </c>
-      <c r="D335" t="s" s="6">
-        <v>72</v>
+        <v>34</v>
+      </c>
+      <c r="D335" t="s" s="34">
+        <v>35</v>
       </c>
       <c r="E335" s="13"/>
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
     </row>
-    <row r="336" ht="9" customHeight="1" hidden="1">
+    <row r="336" ht="15" customHeight="1">
       <c r="A336" s="5"/>
-      <c r="B336" t="s" s="6">
-        <v>154</v>
-      </c>
+      <c r="B336" s="7"/>
       <c r="C336" t="s" s="6">
-        <v>156</v>
-      </c>
-      <c r="D336" t="s" s="6">
-        <v>73</v>
+        <v>36</v>
+      </c>
+      <c r="D336" t="s" s="34">
+        <v>37</v>
       </c>
       <c r="E336" s="13"/>
       <c r="F336" s="2"/>
       <c r="G336" s="2"/>
       <c r="H336" s="2"/>
     </row>
-    <row r="337" ht="9" customHeight="1" hidden="1">
+    <row r="337" ht="21.75" customHeight="1">
       <c r="A337" s="5"/>
-      <c r="B337" t="s" s="6">
-        <v>157</v>
-      </c>
+      <c r="B337" s="7"/>
       <c r="C337" t="s" s="6">
-        <v>158</v>
-      </c>
-      <c r="D337" s="67">
-        <v>3</v>
+        <v>38</v>
+      </c>
+      <c r="D337" t="s" s="34">
+        <v>39</v>
       </c>
       <c r="E337" s="13"/>
       <c r="F337" s="2"/>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
     </row>
-    <row r="338" ht="9" customHeight="1" hidden="1">
+    <row r="338" ht="15" customHeight="1">
       <c r="A338" s="5"/>
-      <c r="B338" t="s" s="6">
-        <v>159</v>
-      </c>
+      <c r="B338" s="7"/>
       <c r="C338" t="s" s="6">
-        <v>93</v>
-      </c>
-      <c r="D338" s="67">
-        <v>23</v>
+        <v>40</v>
+      </c>
+      <c r="D338" t="s" s="34">
+        <v>41</v>
       </c>
       <c r="E338" s="13"/>
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
     </row>
-    <row r="339" ht="13.65" customHeight="1">
-      <c r="A339" s="2"/>
-      <c r="B339" s="28"/>
-      <c r="C339" s="28"/>
-      <c r="D339" s="28"/>
-      <c r="E339" s="2"/>
+    <row r="339" ht="15" customHeight="1">
+      <c r="A339" s="5"/>
+      <c r="B339" s="7"/>
+      <c r="C339" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D339" t="s" s="34">
+        <v>43</v>
+      </c>
+      <c r="E339" s="13"/>
       <c r="F339" s="2"/>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
     </row>
-    <row r="340" ht="13.65" customHeight="1">
-      <c r="A340" s="2"/>
-      <c r="B340" s="3"/>
-      <c r="C340" s="3"/>
-      <c r="D340" s="3"/>
-      <c r="E340" s="2"/>
+    <row r="340" ht="15" customHeight="1">
+      <c r="A340" s="5"/>
+      <c r="B340" s="7"/>
+      <c r="C340" t="s" s="6">
+        <v>44</v>
+      </c>
+      <c r="D340" s="36">
+        <v>41648</v>
+      </c>
+      <c r="E340" s="13"/>
       <c r="F340" s="2"/>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
     </row>
     <row r="341" ht="15" customHeight="1">
       <c r="A341" s="5"/>
-      <c r="B341" t="s" s="6">
-        <v>160</v>
-      </c>
-      <c r="C341" s="7"/>
-      <c r="D341" s="7"/>
+      <c r="B341" s="7"/>
+      <c r="C341" t="s" s="6">
+        <v>68</v>
+      </c>
+      <c r="D341" s="36">
+        <v>40919</v>
+      </c>
       <c r="E341" s="13"/>
       <c r="F341" s="2"/>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
     </row>
-    <row r="342" ht="15" customHeight="1">
+    <row r="342" ht="9" customHeight="1" hidden="1">
       <c r="A342" s="5"/>
-      <c r="B342" t="s" s="6">
-        <v>1</v>
-      </c>
-      <c r="C342" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D342" t="s" s="35">
-        <v>6</v>
-      </c>
+      <c r="B342" t="s" s="20">
+        <v>160</v>
+      </c>
+      <c r="C342" t="s" s="68">
+        <v>113</v>
+      </c>
+      <c r="D342" s="69"/>
       <c r="E342" s="13"/>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
     </row>
-    <row r="343" ht="15" customHeight="1">
-      <c r="A343" s="5"/>
-      <c r="B343" s="7"/>
-      <c r="C343" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D343" t="s" s="35">
-        <v>36</v>
-      </c>
-      <c r="E343" s="13"/>
+    <row r="343" ht="13.65" customHeight="1">
+      <c r="A343" s="2"/>
+      <c r="B343" s="28"/>
+      <c r="C343" s="28"/>
+      <c r="D343" s="28"/>
+      <c r="E343" s="2"/>
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
       <c r="H343" s="2"/>
     </row>
-    <row r="344" ht="15" customHeight="1">
-      <c r="A344" s="5"/>
-      <c r="B344" s="7"/>
-      <c r="C344" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D344" t="s" s="35">
-        <v>38</v>
-      </c>
-      <c r="E344" s="13"/>
+    <row r="344" ht="13.65" customHeight="1">
+      <c r="A344" s="2"/>
+      <c r="B344" s="3"/>
+      <c r="C344" s="3"/>
+      <c r="D344" s="3"/>
+      <c r="E344" s="2"/>
       <c r="F344" s="2"/>
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
     </row>
-    <row r="345" ht="21.75" customHeight="1">
+    <row r="345" ht="13.65" customHeight="1">
       <c r="A345" s="5"/>
-      <c r="B345" s="7"/>
-      <c r="C345" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D345" t="s" s="35">
-        <v>40</v>
-      </c>
+      <c r="B345" t="s" s="64">
+        <v>161</v>
+      </c>
+      <c r="C345" s="65"/>
+      <c r="D345" s="66"/>
       <c r="E345" s="13"/>
       <c r="F345" s="2"/>
       <c r="G345" s="2"/>
@@ -7597,12 +7584,14 @@
     </row>
     <row r="346" ht="15" customHeight="1">
       <c r="A346" s="5"/>
-      <c r="B346" s="7"/>
+      <c r="B346" t="s" s="20">
+        <v>1</v>
+      </c>
       <c r="C346" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D346" t="s" s="35">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="D346" t="s" s="34">
+        <v>35</v>
       </c>
       <c r="E346" s="13"/>
       <c r="F346" s="2"/>
@@ -7611,12 +7600,12 @@
     </row>
     <row r="347" ht="15" customHeight="1">
       <c r="A347" s="5"/>
-      <c r="B347" s="7"/>
-      <c r="C347" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D347" t="s" s="35">
-        <v>44</v>
+      <c r="B347" s="33"/>
+      <c r="C347" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D347" t="s" s="34">
+        <v>5</v>
       </c>
       <c r="E347" s="13"/>
       <c r="F347" s="2"/>
@@ -7625,12 +7614,12 @@
     </row>
     <row r="348" ht="15" customHeight="1">
       <c r="A348" s="5"/>
-      <c r="B348" s="7"/>
+      <c r="B348" s="33"/>
       <c r="C348" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D348" s="36">
-        <v>41648</v>
+        <v>36</v>
+      </c>
+      <c r="D348" t="s" s="34">
+        <v>37</v>
       </c>
       <c r="E348" s="13"/>
       <c r="F348" s="2"/>
@@ -7639,201 +7628,201 @@
     </row>
     <row r="349" ht="15" customHeight="1">
       <c r="A349" s="5"/>
-      <c r="B349" s="7"/>
+      <c r="B349" s="33"/>
       <c r="C349" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D349" s="36">
-        <v>40919</v>
+        <v>38</v>
+      </c>
+      <c r="D349" t="s" s="34">
+        <v>39</v>
       </c>
       <c r="E349" s="13"/>
       <c r="F349" s="2"/>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
     </row>
-    <row r="350" ht="9" customHeight="1" hidden="1">
+    <row r="350" ht="15" customHeight="1">
       <c r="A350" s="5"/>
-      <c r="B350" t="s" s="20">
-        <v>161</v>
-      </c>
-      <c r="C350" t="s" s="68">
-        <v>114</v>
-      </c>
-      <c r="D350" s="69"/>
+      <c r="B350" s="33"/>
+      <c r="C350" t="s" s="6">
+        <v>40</v>
+      </c>
+      <c r="D350" t="s" s="34">
+        <v>41</v>
+      </c>
       <c r="E350" s="13"/>
       <c r="F350" s="2"/>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
     </row>
-    <row r="351" ht="13.65" customHeight="1">
-      <c r="A351" s="2"/>
-      <c r="B351" s="28"/>
-      <c r="C351" s="28"/>
-      <c r="D351" s="28"/>
-      <c r="E351" s="2"/>
+    <row r="351" ht="15" customHeight="1">
+      <c r="A351" s="5"/>
+      <c r="B351" s="33"/>
+      <c r="C351" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D351" t="s" s="34">
+        <v>43</v>
+      </c>
+      <c r="E351" s="13"/>
       <c r="F351" s="2"/>
       <c r="G351" s="2"/>
       <c r="H351" s="2"/>
     </row>
-    <row r="352" ht="13.65" customHeight="1">
-      <c r="A352" s="2"/>
-      <c r="B352" s="3"/>
-      <c r="C352" s="3"/>
-      <c r="D352" s="3"/>
-      <c r="E352" s="2"/>
+    <row r="352" ht="15" customHeight="1">
+      <c r="A352" s="5"/>
+      <c r="B352" s="33"/>
+      <c r="C352" t="s" s="6">
+        <v>44</v>
+      </c>
+      <c r="D352" s="36">
+        <v>41648</v>
+      </c>
+      <c r="E352" s="13"/>
       <c r="F352" s="2"/>
       <c r="G352" s="2"/>
       <c r="H352" s="2"/>
     </row>
-    <row r="353" ht="13.65" customHeight="1">
+    <row r="353" ht="15" customHeight="1">
       <c r="A353" s="5"/>
-      <c r="B353" t="s" s="64">
-        <v>162</v>
-      </c>
-      <c r="C353" s="65"/>
-      <c r="D353" s="66"/>
+      <c r="B353" s="33"/>
+      <c r="C353" t="s" s="6">
+        <v>68</v>
+      </c>
+      <c r="D353" s="36">
+        <v>40919</v>
+      </c>
       <c r="E353" s="13"/>
       <c r="F353" s="2"/>
       <c r="G353" s="2"/>
       <c r="H353" s="2"/>
     </row>
-    <row r="354" ht="15" customHeight="1">
+    <row r="354" ht="9" customHeight="1" hidden="1">
       <c r="A354" s="5"/>
       <c r="B354" t="s" s="20">
-        <v>1</v>
-      </c>
-      <c r="C354" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D354" t="s" s="35">
-        <v>36</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="C354" t="s" s="20">
+        <v>163</v>
+      </c>
+      <c r="D354" s="33"/>
       <c r="E354" s="13"/>
       <c r="F354" s="2"/>
       <c r="G354" s="2"/>
       <c r="H354" s="2"/>
     </row>
-    <row r="355" ht="15" customHeight="1">
+    <row r="355" ht="9" customHeight="1" hidden="1">
       <c r="A355" s="5"/>
-      <c r="B355" s="33"/>
-      <c r="C355" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D355" t="s" s="35">
-        <v>6</v>
-      </c>
+      <c r="B355" t="s" s="20">
+        <v>164</v>
+      </c>
+      <c r="C355" t="s" s="20">
+        <v>47</v>
+      </c>
+      <c r="D355" s="33"/>
       <c r="E355" s="13"/>
       <c r="F355" s="2"/>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
     </row>
-    <row r="356" ht="15" customHeight="1">
+    <row r="356" ht="9" customHeight="1" hidden="1">
       <c r="A356" s="5"/>
-      <c r="B356" s="33"/>
-      <c r="C356" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D356" t="s" s="35">
-        <v>38</v>
-      </c>
+      <c r="B356" s="70">
+        <v>3</v>
+      </c>
+      <c r="C356" t="s" s="20">
+        <v>92</v>
+      </c>
+      <c r="D356" s="33"/>
       <c r="E356" s="13"/>
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
     </row>
-    <row r="357" ht="15" customHeight="1">
-      <c r="A357" s="5"/>
-      <c r="B357" s="33"/>
-      <c r="C357" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D357" t="s" s="35">
-        <v>40</v>
-      </c>
-      <c r="E357" s="13"/>
+    <row r="357" ht="13.65" customHeight="1">
+      <c r="A357" s="2"/>
+      <c r="B357" s="28"/>
+      <c r="C357" s="28"/>
+      <c r="D357" s="28"/>
+      <c r="E357" s="2"/>
       <c r="F357" s="2"/>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
     </row>
-    <row r="358" ht="15" customHeight="1">
-      <c r="A358" s="5"/>
-      <c r="B358" s="33"/>
-      <c r="C358" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D358" t="s" s="35">
-        <v>42</v>
-      </c>
-      <c r="E358" s="13"/>
+    <row r="358" ht="13.65" customHeight="1">
+      <c r="A358" s="2"/>
+      <c r="B358" s="3"/>
+      <c r="C358" s="2"/>
+      <c r="D358" s="2"/>
+      <c r="E358" s="2"/>
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
       <c r="H358" s="2"/>
     </row>
-    <row r="359" ht="15" customHeight="1">
+    <row r="359" ht="13.65" customHeight="1">
       <c r="A359" s="5"/>
-      <c r="B359" s="33"/>
-      <c r="C359" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D359" t="s" s="35">
-        <v>44</v>
-      </c>
-      <c r="E359" s="13"/>
+      <c r="B359" t="s" s="20">
+        <v>165</v>
+      </c>
+      <c r="C359" s="76"/>
+      <c r="D359" s="3"/>
+      <c r="E359" s="2"/>
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
       <c r="H359" s="2"/>
     </row>
-    <row r="360" ht="15" customHeight="1">
+    <row r="360" ht="13.65" customHeight="1">
       <c r="A360" s="5"/>
-      <c r="B360" s="33"/>
-      <c r="C360" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D360" s="36">
-        <v>41648</v>
+      <c r="B360" t="s" s="88">
+        <v>1</v>
+      </c>
+      <c r="C360" t="s" s="20">
+        <v>34</v>
+      </c>
+      <c r="D360" t="s" s="20">
+        <v>35</v>
       </c>
       <c r="E360" s="13"/>
       <c r="F360" s="2"/>
       <c r="G360" s="2"/>
       <c r="H360" s="2"/>
     </row>
-    <row r="361" ht="15" customHeight="1">
+    <row r="361" ht="13.65" customHeight="1">
       <c r="A361" s="5"/>
-      <c r="B361" s="33"/>
-      <c r="C361" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D361" s="36">
-        <v>40919</v>
+      <c r="B361" s="89"/>
+      <c r="C361" t="s" s="20">
+        <v>36</v>
+      </c>
+      <c r="D361" t="s" s="20">
+        <v>113</v>
       </c>
       <c r="E361" s="13"/>
       <c r="F361" s="2"/>
       <c r="G361" s="2"/>
       <c r="H361" s="2"/>
     </row>
-    <row r="362" ht="9" customHeight="1" hidden="1">
+    <row r="362" ht="15" customHeight="1">
       <c r="A362" s="5"/>
-      <c r="B362" t="s" s="20">
-        <v>163</v>
-      </c>
-      <c r="C362" t="s" s="20">
-        <v>164</v>
-      </c>
-      <c r="D362" s="33"/>
+      <c r="B362" s="89"/>
+      <c r="C362" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D362" t="s" s="34">
+        <v>5</v>
+      </c>
       <c r="E362" s="13"/>
       <c r="F362" s="2"/>
       <c r="G362" s="2"/>
       <c r="H362" s="2"/>
     </row>
-    <row r="363" ht="9" customHeight="1" hidden="1">
+    <row r="363" ht="13.65" customHeight="1">
       <c r="A363" s="5"/>
-      <c r="B363" t="s" s="20">
-        <v>165</v>
-      </c>
+      <c r="B363" s="90"/>
       <c r="C363" t="s" s="20">
-        <v>48</v>
-      </c>
-      <c r="D363" s="33"/>
+        <v>38</v>
+      </c>
+      <c r="D363" t="s" s="20">
+        <v>166</v>
+      </c>
       <c r="E363" s="13"/>
       <c r="F363" s="2"/>
       <c r="G363" s="2"/>
@@ -7841,102 +7830,126 @@
     </row>
     <row r="364" ht="9" customHeight="1" hidden="1">
       <c r="A364" s="5"/>
-      <c r="B364" s="70">
-        <v>3</v>
+      <c r="B364" t="s" s="20">
+        <v>167</v>
       </c>
       <c r="C364" t="s" s="20">
-        <v>93</v>
-      </c>
-      <c r="D364" s="33"/>
+        <v>168</v>
+      </c>
+      <c r="D364" s="70">
+        <v>0.666666666670</v>
+      </c>
       <c r="E364" s="13"/>
       <c r="F364" s="2"/>
       <c r="G364" s="2"/>
       <c r="H364" s="2"/>
     </row>
-    <row r="365" ht="13.65" customHeight="1">
-      <c r="A365" s="2"/>
-      <c r="B365" s="28"/>
-      <c r="C365" s="28"/>
-      <c r="D365" s="28"/>
-      <c r="E365" s="2"/>
+    <row r="365" ht="9" customHeight="1" hidden="1">
+      <c r="A365" s="5"/>
+      <c r="B365" t="s" s="20">
+        <v>169</v>
+      </c>
+      <c r="C365" t="s" s="20">
+        <v>170</v>
+      </c>
+      <c r="D365" s="70">
+        <v>0.555555555570</v>
+      </c>
+      <c r="E365" s="13"/>
       <c r="F365" s="2"/>
       <c r="G365" s="2"/>
       <c r="H365" s="2"/>
     </row>
-    <row r="366" ht="13.65" customHeight="1">
-      <c r="A366" s="2"/>
-      <c r="B366" s="3"/>
-      <c r="C366" s="2"/>
-      <c r="D366" s="2"/>
-      <c r="E366" s="2"/>
+    <row r="366" ht="9" customHeight="1" hidden="1">
+      <c r="A366" s="5"/>
+      <c r="B366" t="s" s="20">
+        <v>171</v>
+      </c>
+      <c r="C366" t="s" s="20">
+        <v>172</v>
+      </c>
+      <c r="D366" s="70">
+        <v>19993</v>
+      </c>
+      <c r="E366" s="13"/>
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
       <c r="H366" s="2"/>
     </row>
-    <row r="367" ht="13.65" customHeight="1">
+    <row r="367" ht="9" customHeight="1" hidden="1">
       <c r="A367" s="5"/>
       <c r="B367" t="s" s="20">
-        <v>166</v>
-      </c>
-      <c r="C367" s="76"/>
-      <c r="D367" s="3"/>
-      <c r="E367" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="C367" t="s" s="20">
+        <v>174</v>
+      </c>
+      <c r="D367" s="70">
+        <v>9847892</v>
+      </c>
+      <c r="E367" s="13"/>
       <c r="F367" s="2"/>
       <c r="G367" s="2"/>
       <c r="H367" s="2"/>
     </row>
-    <row r="368" ht="13.65" customHeight="1">
+    <row r="368" ht="9" customHeight="1" hidden="1">
       <c r="A368" s="5"/>
-      <c r="B368" t="s" s="88">
+      <c r="B368" t="s" s="20">
+        <v>175</v>
+      </c>
+      <c r="C368" t="s" s="20">
+        <v>71</v>
+      </c>
+      <c r="D368" t="b" s="70">
         <v>1</v>
-      </c>
-      <c r="C368" t="s" s="20">
-        <v>35</v>
-      </c>
-      <c r="D368" t="s" s="20">
-        <v>36</v>
       </c>
       <c r="E368" s="13"/>
       <c r="F368" s="2"/>
       <c r="G368" s="2"/>
       <c r="H368" s="2"/>
     </row>
-    <row r="369" ht="13.65" customHeight="1">
+    <row r="369" ht="9" customHeight="1" hidden="1">
       <c r="A369" s="5"/>
-      <c r="B369" s="89"/>
+      <c r="B369" t="s" s="20">
+        <v>176</v>
+      </c>
       <c r="C369" t="s" s="20">
-        <v>37</v>
-      </c>
-      <c r="D369" t="s" s="20">
-        <v>114</v>
+        <v>177</v>
+      </c>
+      <c r="D369" s="70">
+        <v>-128</v>
       </c>
       <c r="E369" s="13"/>
       <c r="F369" s="2"/>
       <c r="G369" s="2"/>
       <c r="H369" s="2"/>
     </row>
-    <row r="370" ht="15" customHeight="1">
+    <row r="370" ht="9" customHeight="1" hidden="1">
       <c r="A370" s="5"/>
-      <c r="B370" s="89"/>
-      <c r="C370" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D370" t="s" s="35">
-        <v>6</v>
+      <c r="B370" t="s" s="20">
+        <v>178</v>
+      </c>
+      <c r="C370" t="s" s="20">
+        <v>179</v>
+      </c>
+      <c r="D370" t="s" s="20">
+        <v>180</v>
       </c>
       <c r="E370" s="13"/>
       <c r="F370" s="2"/>
       <c r="G370" s="2"/>
       <c r="H370" s="2"/>
     </row>
-    <row r="371" ht="13.65" customHeight="1">
+    <row r="371" ht="9" customHeight="1" hidden="1">
       <c r="A371" s="5"/>
-      <c r="B371" s="90"/>
+      <c r="B371" t="s" s="20">
+        <v>181</v>
+      </c>
       <c r="C371" t="s" s="20">
-        <v>39</v>
+        <v>182</v>
       </c>
       <c r="D371" t="s" s="20">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="E371" s="13"/>
       <c r="F371" s="2"/>
@@ -7946,13 +7959,13 @@
     <row r="372" ht="9" customHeight="1" hidden="1">
       <c r="A372" s="5"/>
       <c r="B372" t="s" s="20">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="C372" t="s" s="20">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="D372" s="70">
-        <v>0.666666666670</v>
+        <v>23423.4234</v>
       </c>
       <c r="E372" s="13"/>
       <c r="F372" s="2"/>
@@ -7962,13 +7975,13 @@
     <row r="373" ht="9" customHeight="1" hidden="1">
       <c r="A373" s="5"/>
       <c r="B373" t="s" s="20">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="C373" t="s" s="20">
-        <v>171</v>
-      </c>
-      <c r="D373" s="70">
-        <v>0.555555555570</v>
+        <v>187</v>
+      </c>
+      <c r="D373" t="s" s="20">
+        <v>188</v>
       </c>
       <c r="E373" s="13"/>
       <c r="F373" s="2"/>
@@ -7978,13 +7991,13 @@
     <row r="374" ht="9" customHeight="1" hidden="1">
       <c r="A374" s="5"/>
       <c r="B374" t="s" s="20">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="C374" t="s" s="20">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="D374" s="70">
-        <v>19993</v>
+        <v>5345.234</v>
       </c>
       <c r="E374" s="13"/>
       <c r="F374" s="2"/>
@@ -7994,13 +8007,13 @@
     <row r="375" ht="9" customHeight="1" hidden="1">
       <c r="A375" s="5"/>
       <c r="B375" t="s" s="20">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="C375" t="s" s="20">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="D375" s="70">
-        <v>9847892</v>
+        <v>231.31</v>
       </c>
       <c r="E375" s="13"/>
       <c r="F375" s="2"/>
@@ -8010,13 +8023,13 @@
     <row r="376" ht="9" customHeight="1" hidden="1">
       <c r="A376" s="5"/>
       <c r="B376" t="s" s="20">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C376" t="s" s="20">
-        <v>72</v>
-      </c>
-      <c r="D376" t="b" s="70">
-        <v>1</v>
+        <v>194</v>
+      </c>
+      <c r="D376" s="70">
+        <v>4453.342</v>
       </c>
       <c r="E376" s="13"/>
       <c r="F376" s="2"/>
@@ -8026,13 +8039,13 @@
     <row r="377" ht="9" customHeight="1" hidden="1">
       <c r="A377" s="5"/>
       <c r="B377" t="s" s="20">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="C377" t="s" s="20">
-        <v>178</v>
-      </c>
-      <c r="D377" s="70">
-        <v>-128</v>
+        <v>196</v>
+      </c>
+      <c r="D377" s="91">
+        <v>43393</v>
       </c>
       <c r="E377" s="13"/>
       <c r="F377" s="2"/>
@@ -8042,13 +8055,13 @@
     <row r="378" ht="9" customHeight="1" hidden="1">
       <c r="A378" s="5"/>
       <c r="B378" t="s" s="20">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="C378" t="s" s="20">
-        <v>180</v>
-      </c>
-      <c r="D378" t="s" s="20">
-        <v>181</v>
+        <v>197</v>
+      </c>
+      <c r="D378" s="70">
+        <v>42</v>
       </c>
       <c r="E378" s="13"/>
       <c r="F378" s="2"/>
@@ -8058,13 +8071,13 @@
     <row r="379" ht="9" customHeight="1" hidden="1">
       <c r="A379" s="5"/>
       <c r="B379" t="s" s="20">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="C379" t="s" s="20">
-        <v>183</v>
-      </c>
-      <c r="D379" t="s" s="20">
-        <v>184</v>
+        <v>199</v>
+      </c>
+      <c r="D379" s="70">
+        <v>42</v>
       </c>
       <c r="E379" s="13"/>
       <c r="F379" s="2"/>
@@ -8074,13 +8087,13 @@
     <row r="380" ht="9" customHeight="1" hidden="1">
       <c r="A380" s="5"/>
       <c r="B380" t="s" s="20">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C380" t="s" s="20">
-        <v>186</v>
+        <v>105</v>
       </c>
       <c r="D380" s="70">
-        <v>23423.4234</v>
+        <v>3634</v>
       </c>
       <c r="E380" s="13"/>
       <c r="F380" s="2"/>
@@ -8090,13 +8103,13 @@
     <row r="381" ht="9" customHeight="1" hidden="1">
       <c r="A381" s="5"/>
       <c r="B381" t="s" s="20">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="C381" t="s" s="20">
-        <v>188</v>
-      </c>
-      <c r="D381" t="s" s="20">
-        <v>189</v>
+        <v>202</v>
+      </c>
+      <c r="D381" s="70">
+        <v>265727564</v>
       </c>
       <c r="E381" s="13"/>
       <c r="F381" s="2"/>
@@ -8106,13 +8119,13 @@
     <row r="382" ht="9" customHeight="1" hidden="1">
       <c r="A382" s="5"/>
       <c r="B382" t="s" s="20">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C382" t="s" s="20">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D382" s="70">
-        <v>5345.234</v>
+        <v>23</v>
       </c>
       <c r="E382" s="13"/>
       <c r="F382" s="2"/>
@@ -8122,13 +8135,13 @@
     <row r="383" ht="9" customHeight="1" hidden="1">
       <c r="A383" s="5"/>
       <c r="B383" t="s" s="20">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C383" t="s" s="20">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="D383" s="70">
-        <v>231.31</v>
+        <v>432</v>
       </c>
       <c r="E383" s="13"/>
       <c r="F383" s="2"/>
@@ -8138,13 +8151,13 @@
     <row r="384" ht="9" customHeight="1" hidden="1">
       <c r="A384" s="5"/>
       <c r="B384" t="s" s="20">
-        <v>194</v>
+        <v>114</v>
       </c>
       <c r="C384" t="s" s="20">
-        <v>195</v>
-      </c>
-      <c r="D384" s="70">
-        <v>4453.342</v>
+        <v>207</v>
+      </c>
+      <c r="D384" t="s" s="20">
+        <v>208</v>
       </c>
       <c r="E384" s="13"/>
       <c r="F384" s="2"/>
@@ -8154,13 +8167,13 @@
     <row r="385" ht="9" customHeight="1" hidden="1">
       <c r="A385" s="5"/>
       <c r="B385" t="s" s="20">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="C385" t="s" s="20">
-        <v>197</v>
-      </c>
-      <c r="D385" s="91">
-        <v>43393</v>
+        <v>210</v>
+      </c>
+      <c r="D385" t="s" s="20">
+        <v>211</v>
       </c>
       <c r="E385" s="13"/>
       <c r="F385" s="2"/>
@@ -8170,13 +8183,13 @@
     <row r="386" ht="9" customHeight="1" hidden="1">
       <c r="A386" s="5"/>
       <c r="B386" t="s" s="20">
-        <v>123</v>
+        <v>212</v>
       </c>
       <c r="C386" t="s" s="20">
-        <v>198</v>
+        <v>92</v>
       </c>
       <c r="D386" s="70">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E386" s="13"/>
       <c r="F386" s="2"/>
@@ -8186,13 +8199,13 @@
     <row r="387" ht="9" customHeight="1" hidden="1">
       <c r="A387" s="5"/>
       <c r="B387" t="s" s="20">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C387" t="s" s="20">
-        <v>200</v>
-      </c>
-      <c r="D387" s="70">
-        <v>42</v>
+        <v>214</v>
+      </c>
+      <c r="D387" t="s" s="20">
+        <v>215</v>
       </c>
       <c r="E387" s="13"/>
       <c r="F387" s="2"/>
@@ -8202,13 +8215,13 @@
     <row r="388" ht="9" customHeight="1" hidden="1">
       <c r="A388" s="5"/>
       <c r="B388" t="s" s="20">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="C388" t="s" s="20">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="D388" s="70">
-        <v>3634</v>
+        <v>8972342.432</v>
       </c>
       <c r="E388" s="13"/>
       <c r="F388" s="2"/>
@@ -8218,13 +8231,13 @@
     <row r="389" ht="9" customHeight="1" hidden="1">
       <c r="A389" s="5"/>
       <c r="B389" t="s" s="20">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="C389" t="s" s="20">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D389" s="70">
-        <v>265727564</v>
+        <v>-4234.24</v>
       </c>
       <c r="E389" s="13"/>
       <c r="F389" s="2"/>
@@ -8234,13 +8247,13 @@
     <row r="390" ht="9" customHeight="1" hidden="1">
       <c r="A390" s="5"/>
       <c r="B390" t="s" s="20">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C390" t="s" s="20">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="D390" s="70">
-        <v>23</v>
+        <v>7356</v>
       </c>
       <c r="E390" s="13"/>
       <c r="F390" s="2"/>
@@ -8250,13 +8263,13 @@
     <row r="391" ht="9" customHeight="1" hidden="1">
       <c r="A391" s="5"/>
       <c r="B391" t="s" s="20">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="C391" t="s" s="20">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="D391" s="70">
-        <v>432</v>
+        <v>546245272</v>
       </c>
       <c r="E391" s="13"/>
       <c r="F391" s="2"/>
@@ -8266,13 +8279,13 @@
     <row r="392" ht="9" customHeight="1" hidden="1">
       <c r="A392" s="5"/>
       <c r="B392" t="s" s="20">
-        <v>115</v>
+        <v>224</v>
       </c>
       <c r="C392" t="s" s="20">
-        <v>208</v>
-      </c>
-      <c r="D392" t="s" s="20">
-        <v>209</v>
+        <v>225</v>
+      </c>
+      <c r="D392" s="70">
+        <v>32</v>
       </c>
       <c r="E392" s="13"/>
       <c r="F392" s="2"/>
@@ -8282,174 +8295,160 @@
     <row r="393" ht="9" customHeight="1" hidden="1">
       <c r="A393" s="5"/>
       <c r="B393" t="s" s="20">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="C393" t="s" s="20">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="D393" t="s" s="20">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="E393" s="13"/>
       <c r="F393" s="2"/>
       <c r="G393" s="2"/>
       <c r="H393" s="2"/>
     </row>
-    <row r="394" ht="9" customHeight="1" hidden="1">
-      <c r="A394" s="5"/>
-      <c r="B394" t="s" s="20">
-        <v>213</v>
-      </c>
-      <c r="C394" t="s" s="20">
-        <v>93</v>
-      </c>
-      <c r="D394" s="70">
-        <v>6</v>
-      </c>
-      <c r="E394" s="13"/>
+    <row r="394" ht="13.65" customHeight="1">
+      <c r="A394" s="2"/>
+      <c r="B394" s="28"/>
+      <c r="C394" s="28"/>
+      <c r="D394" s="28"/>
+      <c r="E394" s="2"/>
       <c r="F394" s="2"/>
       <c r="G394" s="2"/>
       <c r="H394" s="2"/>
     </row>
-    <row r="395" ht="9" customHeight="1" hidden="1">
-      <c r="A395" s="5"/>
-      <c r="B395" t="s" s="20">
-        <v>214</v>
-      </c>
-      <c r="C395" t="s" s="20">
-        <v>215</v>
-      </c>
-      <c r="D395" t="s" s="20">
-        <v>216</v>
-      </c>
-      <c r="E395" s="13"/>
+    <row r="395" ht="13.65" customHeight="1">
+      <c r="A395" s="2"/>
+      <c r="B395" s="3"/>
+      <c r="C395" s="3"/>
+      <c r="D395" s="3"/>
+      <c r="E395" s="2"/>
       <c r="F395" s="2"/>
       <c r="G395" s="2"/>
       <c r="H395" s="2"/>
     </row>
-    <row r="396" ht="9" customHeight="1" hidden="1">
+    <row r="396" ht="15" customHeight="1">
       <c r="A396" s="5"/>
-      <c r="B396" t="s" s="20">
-        <v>217</v>
-      </c>
-      <c r="C396" t="s" s="20">
-        <v>218</v>
-      </c>
-      <c r="D396" s="70">
-        <v>8972342.432</v>
-      </c>
+      <c r="B396" t="s" s="6">
+        <v>228</v>
+      </c>
+      <c r="C396" s="7"/>
+      <c r="D396" s="7"/>
       <c r="E396" s="13"/>
       <c r="F396" s="2"/>
       <c r="G396" s="2"/>
       <c r="H396" s="2"/>
     </row>
-    <row r="397" ht="9" customHeight="1" hidden="1">
+    <row r="397" ht="15" customHeight="1">
       <c r="A397" s="5"/>
-      <c r="B397" t="s" s="20">
-        <v>219</v>
-      </c>
-      <c r="C397" t="s" s="20">
-        <v>220</v>
-      </c>
-      <c r="D397" s="70">
-        <v>-4234.24</v>
+      <c r="B397" t="s" s="6">
+        <v>1</v>
+      </c>
+      <c r="C397" t="s" s="6">
+        <v>64</v>
+      </c>
+      <c r="D397" t="b" s="30">
+        <v>1</v>
       </c>
       <c r="E397" s="13"/>
       <c r="F397" s="2"/>
       <c r="G397" s="2"/>
       <c r="H397" s="2"/>
     </row>
-    <row r="398" ht="9" customHeight="1" hidden="1">
+    <row r="398" ht="15" customHeight="1">
       <c r="A398" s="5"/>
-      <c r="B398" t="s" s="20">
-        <v>221</v>
-      </c>
-      <c r="C398" t="s" s="20">
-        <v>222</v>
-      </c>
-      <c r="D398" s="70">
-        <v>7356</v>
+      <c r="B398" s="7"/>
+      <c r="C398" t="s" s="6">
+        <v>2</v>
+      </c>
+      <c r="D398" t="b" s="30">
+        <v>1</v>
       </c>
       <c r="E398" s="13"/>
       <c r="F398" s="2"/>
       <c r="G398" s="2"/>
       <c r="H398" s="2"/>
     </row>
-    <row r="399" ht="9" customHeight="1" hidden="1">
+    <row r="399" ht="15" customHeight="1">
       <c r="A399" s="5"/>
-      <c r="B399" t="s" s="20">
-        <v>223</v>
-      </c>
-      <c r="C399" t="s" s="20">
-        <v>224</v>
-      </c>
-      <c r="D399" s="70">
-        <v>546245272</v>
+      <c r="B399" s="7"/>
+      <c r="C399" t="s" s="6">
+        <v>3</v>
+      </c>
+      <c r="D399" t="b" s="30">
+        <v>1</v>
       </c>
       <c r="E399" s="13"/>
       <c r="F399" s="2"/>
       <c r="G399" s="2"/>
       <c r="H399" s="2"/>
     </row>
-    <row r="400" ht="9" customHeight="1" hidden="1">
+    <row r="400" ht="15" customHeight="1">
       <c r="A400" s="5"/>
-      <c r="B400" t="s" s="20">
-        <v>225</v>
-      </c>
-      <c r="C400" t="s" s="20">
-        <v>226</v>
-      </c>
-      <c r="D400" s="70">
-        <v>32</v>
+      <c r="B400" s="33"/>
+      <c r="C400" t="s" s="6">
+        <v>65</v>
+      </c>
+      <c r="D400" t="s" s="34">
+        <v>66</v>
       </c>
       <c r="E400" s="13"/>
       <c r="F400" s="2"/>
       <c r="G400" s="2"/>
       <c r="H400" s="2"/>
     </row>
-    <row r="401" ht="9" customHeight="1" hidden="1">
+    <row r="401" ht="15" customHeight="1">
       <c r="A401" s="5"/>
-      <c r="B401" t="s" s="20">
-        <v>199</v>
-      </c>
-      <c r="C401" t="s" s="20">
-        <v>227</v>
-      </c>
-      <c r="D401" t="s" s="20">
-        <v>228</v>
+      <c r="B401" s="7"/>
+      <c r="C401" t="s" s="6">
+        <v>4</v>
+      </c>
+      <c r="D401" t="s" s="34">
+        <v>5</v>
       </c>
       <c r="E401" s="13"/>
       <c r="F401" s="2"/>
       <c r="G401" s="2"/>
       <c r="H401" s="2"/>
     </row>
-    <row r="402" ht="13.65" customHeight="1">
-      <c r="A402" s="2"/>
-      <c r="B402" s="28"/>
-      <c r="C402" s="28"/>
-      <c r="D402" s="28"/>
-      <c r="E402" s="2"/>
+    <row r="402" ht="15" customHeight="1">
+      <c r="A402" s="5"/>
+      <c r="B402" s="7"/>
+      <c r="C402" t="s" s="6">
+        <v>6</v>
+      </c>
+      <c r="D402" t="s" s="34">
+        <v>229</v>
+      </c>
+      <c r="E402" s="13"/>
       <c r="F402" s="2"/>
       <c r="G402" s="2"/>
       <c r="H402" s="2"/>
     </row>
-    <row r="403" ht="13.65" customHeight="1">
-      <c r="A403" s="2"/>
-      <c r="B403" s="3"/>
-      <c r="C403" s="3"/>
-      <c r="D403" s="3"/>
-      <c r="E403" s="2"/>
+    <row r="403" ht="15" customHeight="1">
+      <c r="A403" s="5"/>
+      <c r="B403" s="7"/>
+      <c r="C403" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="D403" t="s" s="34">
+        <v>9</v>
+      </c>
+      <c r="E403" s="13"/>
       <c r="F403" s="2"/>
       <c r="G403" s="2"/>
       <c r="H403" s="2"/>
     </row>
     <row r="404" ht="15" customHeight="1">
       <c r="A404" s="5"/>
-      <c r="B404" t="s" s="6">
-        <v>229</v>
-      </c>
-      <c r="C404" s="7"/>
-      <c r="D404" s="7"/>
+      <c r="B404" s="7"/>
+      <c r="C404" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D404" t="s" s="34">
+        <v>11</v>
+      </c>
       <c r="E404" s="13"/>
       <c r="F404" s="2"/>
       <c r="G404" s="2"/>
@@ -8457,14 +8456,12 @@
     </row>
     <row r="405" ht="15" customHeight="1">
       <c r="A405" s="5"/>
-      <c r="B405" t="s" s="6">
-        <v>1</v>
-      </c>
+      <c r="B405" s="7"/>
       <c r="C405" t="s" s="6">
-        <v>65</v>
-      </c>
-      <c r="D405" t="b" s="30">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="D405" t="s" s="34">
+        <v>13</v>
       </c>
       <c r="E405" s="13"/>
       <c r="F405" s="2"/>
@@ -8475,10 +8472,10 @@
       <c r="A406" s="5"/>
       <c r="B406" s="7"/>
       <c r="C406" t="s" s="6">
-        <v>2</v>
-      </c>
-      <c r="D406" t="b" s="30">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="D406" t="s" s="34">
+        <v>15</v>
       </c>
       <c r="E406" s="13"/>
       <c r="F406" s="2"/>
@@ -8489,10 +8486,10 @@
       <c r="A407" s="5"/>
       <c r="B407" s="7"/>
       <c r="C407" t="s" s="6">
-        <v>3</v>
-      </c>
-      <c r="D407" t="b" s="30">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="D407" t="s" s="34">
+        <v>17</v>
       </c>
       <c r="E407" s="13"/>
       <c r="F407" s="2"/>
@@ -8501,12 +8498,12 @@
     </row>
     <row r="408" ht="15" customHeight="1">
       <c r="A408" s="5"/>
-      <c r="B408" s="33"/>
+      <c r="B408" s="7"/>
       <c r="C408" t="s" s="6">
-        <v>4</v>
-      </c>
-      <c r="D408" t="b" s="30">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="D408" t="s" s="34">
+        <v>19</v>
       </c>
       <c r="E408" s="13"/>
       <c r="F408" s="2"/>
@@ -8517,10 +8514,10 @@
       <c r="A409" s="5"/>
       <c r="B409" s="7"/>
       <c r="C409" t="s" s="6">
-        <v>66</v>
-      </c>
-      <c r="D409" t="s" s="35">
-        <v>67</v>
+        <v>20</v>
+      </c>
+      <c r="D409" t="s" s="34">
+        <v>21</v>
       </c>
       <c r="E409" s="13"/>
       <c r="F409" s="2"/>
@@ -8531,10 +8528,10 @@
       <c r="A410" s="5"/>
       <c r="B410" s="7"/>
       <c r="C410" t="s" s="6">
-        <v>5</v>
-      </c>
-      <c r="D410" t="s" s="35">
-        <v>6</v>
+        <v>22</v>
+      </c>
+      <c r="D410" t="s" s="34">
+        <v>23</v>
       </c>
       <c r="E410" s="13"/>
       <c r="F410" s="2"/>
@@ -8545,10 +8542,10 @@
       <c r="A411" s="5"/>
       <c r="B411" s="7"/>
       <c r="C411" t="s" s="6">
-        <v>7</v>
-      </c>
-      <c r="D411" t="s" s="35">
-        <v>230</v>
+        <v>24</v>
+      </c>
+      <c r="D411" t="s" s="34">
+        <v>25</v>
       </c>
       <c r="E411" s="13"/>
       <c r="F411" s="2"/>
@@ -8559,10 +8556,10 @@
       <c r="A412" s="5"/>
       <c r="B412" s="7"/>
       <c r="C412" t="s" s="6">
-        <v>9</v>
-      </c>
-      <c r="D412" t="s" s="35">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="D412" t="s" s="34">
+        <v>27</v>
       </c>
       <c r="E412" s="13"/>
       <c r="F412" s="2"/>
@@ -8573,10 +8570,10 @@
       <c r="A413" s="5"/>
       <c r="B413" s="7"/>
       <c r="C413" t="s" s="6">
-        <v>11</v>
-      </c>
-      <c r="D413" t="s" s="35">
-        <v>12</v>
+        <v>28</v>
+      </c>
+      <c r="D413" t="s" s="34">
+        <v>29</v>
       </c>
       <c r="E413" s="13"/>
       <c r="F413" s="2"/>
@@ -8587,10 +8584,10 @@
       <c r="A414" s="5"/>
       <c r="B414" s="7"/>
       <c r="C414" t="s" s="6">
-        <v>13</v>
-      </c>
-      <c r="D414" t="s" s="35">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="D414" s="36">
+        <v>41298</v>
       </c>
       <c r="E414" s="13"/>
       <c r="F414" s="2"/>
@@ -8601,10 +8598,10 @@
       <c r="A415" s="5"/>
       <c r="B415" s="7"/>
       <c r="C415" t="s" s="6">
-        <v>15</v>
-      </c>
-      <c r="D415" t="s" s="35">
-        <v>16</v>
+        <v>31</v>
+      </c>
+      <c r="D415" s="36">
+        <v>41275</v>
       </c>
       <c r="E415" s="13"/>
       <c r="F415" s="2"/>
@@ -8615,10 +8612,10 @@
       <c r="A416" s="5"/>
       <c r="B416" s="7"/>
       <c r="C416" t="s" s="6">
-        <v>17</v>
-      </c>
-      <c r="D416" t="s" s="35">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="D416" s="36">
+        <v>41670</v>
       </c>
       <c r="E416" s="13"/>
       <c r="F416" s="2"/>
@@ -8629,10 +8626,10 @@
       <c r="A417" s="5"/>
       <c r="B417" s="7"/>
       <c r="C417" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="D417" t="s" s="35">
-        <v>20</v>
+        <v>33</v>
+      </c>
+      <c r="D417" s="36">
+        <v>41646</v>
       </c>
       <c r="E417" s="13"/>
       <c r="F417" s="2"/>
@@ -8643,10 +8640,10 @@
       <c r="A418" s="5"/>
       <c r="B418" s="7"/>
       <c r="C418" t="s" s="6">
-        <v>21</v>
-      </c>
-      <c r="D418" t="s" s="35">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="D418" t="s" s="34">
+        <v>35</v>
       </c>
       <c r="E418" s="13"/>
       <c r="F418" s="2"/>
@@ -8657,10 +8654,10 @@
       <c r="A419" s="5"/>
       <c r="B419" s="7"/>
       <c r="C419" t="s" s="6">
-        <v>23</v>
-      </c>
-      <c r="D419" t="s" s="35">
-        <v>24</v>
+        <v>36</v>
+      </c>
+      <c r="D419" t="s" s="34">
+        <v>37</v>
       </c>
       <c r="E419" s="13"/>
       <c r="F419" s="2"/>
@@ -8671,10 +8668,10 @@
       <c r="A420" s="5"/>
       <c r="B420" s="7"/>
       <c r="C420" t="s" s="6">
-        <v>25</v>
-      </c>
-      <c r="D420" t="s" s="35">
-        <v>26</v>
+        <v>38</v>
+      </c>
+      <c r="D420" t="s" s="34">
+        <v>39</v>
       </c>
       <c r="E420" s="13"/>
       <c r="F420" s="2"/>
@@ -8685,10 +8682,10 @@
       <c r="A421" s="5"/>
       <c r="B421" s="7"/>
       <c r="C421" t="s" s="6">
-        <v>27</v>
-      </c>
-      <c r="D421" t="s" s="35">
-        <v>28</v>
+        <v>40</v>
+      </c>
+      <c r="D421" t="s" s="34">
+        <v>41</v>
       </c>
       <c r="E421" s="13"/>
       <c r="F421" s="2"/>
@@ -8698,11 +8695,11 @@
     <row r="422" ht="15" customHeight="1">
       <c r="A422" s="5"/>
       <c r="B422" s="7"/>
-      <c r="C422" t="s" s="6">
-        <v>29</v>
-      </c>
-      <c r="D422" t="s" s="35">
-        <v>30</v>
+      <c r="C422" t="s" s="20">
+        <v>42</v>
+      </c>
+      <c r="D422" t="s" s="34">
+        <v>43</v>
       </c>
       <c r="E422" s="13"/>
       <c r="F422" s="2"/>
@@ -8713,10 +8710,10 @@
       <c r="A423" s="5"/>
       <c r="B423" s="7"/>
       <c r="C423" t="s" s="6">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D423" s="36">
-        <v>41298</v>
+        <v>41648</v>
       </c>
       <c r="E423" s="13"/>
       <c r="F423" s="2"/>
@@ -8727,10 +8724,10 @@
       <c r="A424" s="5"/>
       <c r="B424" s="7"/>
       <c r="C424" t="s" s="6">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D424" s="36">
-        <v>41275</v>
+        <v>40919</v>
       </c>
       <c r="E424" s="13"/>
       <c r="F424" s="2"/>
@@ -8739,13 +8736,13 @@
     </row>
     <row r="425" ht="15" customHeight="1">
       <c r="A425" s="5"/>
-      <c r="B425" s="7"/>
-      <c r="C425" t="s" s="6">
-        <v>33</v>
-      </c>
-      <c r="D425" s="36">
-        <v>41670</v>
-      </c>
+      <c r="B425" t="s" s="6">
+        <v>230</v>
+      </c>
+      <c r="C425" t="s" s="46">
+        <v>231</v>
+      </c>
+      <c r="D425" s="49"/>
       <c r="E425" s="13"/>
       <c r="F425" s="2"/>
       <c r="G425" s="2"/>
@@ -8753,13 +8750,11 @@
     </row>
     <row r="426" ht="15" customHeight="1">
       <c r="A426" s="5"/>
-      <c r="B426" s="7"/>
-      <c r="C426" t="s" s="6">
-        <v>34</v>
-      </c>
-      <c r="D426" s="36">
-        <v>41646</v>
-      </c>
+      <c r="B426" t="s" s="6">
+        <v>232</v>
+      </c>
+      <c r="C426" s="7"/>
+      <c r="D426" s="7"/>
       <c r="E426" s="13"/>
       <c r="F426" s="2"/>
       <c r="G426" s="2"/>
@@ -8767,13 +8762,13 @@
     </row>
     <row r="427" ht="15" customHeight="1">
       <c r="A427" s="5"/>
-      <c r="B427" s="7"/>
-      <c r="C427" t="s" s="6">
-        <v>35</v>
-      </c>
-      <c r="D427" t="s" s="35">
-        <v>36</v>
-      </c>
+      <c r="B427" t="s" s="6">
+        <v>175</v>
+      </c>
+      <c r="C427" t="s" s="46">
+        <v>220</v>
+      </c>
+      <c r="D427" s="49"/>
       <c r="E427" s="13"/>
       <c r="F427" s="2"/>
       <c r="G427" s="2"/>
@@ -8781,279 +8776,152 @@
     </row>
     <row r="428" ht="15" customHeight="1">
       <c r="A428" s="5"/>
-      <c r="B428" s="7"/>
+      <c r="B428" t="s" s="6">
+        <v>71</v>
+      </c>
       <c r="C428" t="s" s="6">
-        <v>37</v>
-      </c>
-      <c r="D428" t="s" s="35">
-        <v>38</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="D428" s="7"/>
       <c r="E428" s="13"/>
       <c r="F428" s="2"/>
       <c r="G428" s="2"/>
       <c r="H428" s="2"/>
     </row>
-    <row r="429" ht="15" customHeight="1">
-      <c r="A429" s="5"/>
-      <c r="B429" s="7"/>
-      <c r="C429" t="s" s="6">
-        <v>39</v>
-      </c>
-      <c r="D429" t="s" s="35">
-        <v>40</v>
-      </c>
-      <c r="E429" s="13"/>
-      <c r="F429" s="2"/>
-      <c r="G429" s="2"/>
-      <c r="H429" s="2"/>
-    </row>
-    <row r="430" ht="15" customHeight="1">
-      <c r="A430" s="5"/>
-      <c r="B430" s="7"/>
-      <c r="C430" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D430" t="s" s="35">
-        <v>42</v>
-      </c>
-      <c r="E430" s="13"/>
-      <c r="F430" s="2"/>
-      <c r="G430" s="2"/>
-      <c r="H430" s="2"/>
-    </row>
-    <row r="431" ht="15" customHeight="1">
-      <c r="A431" s="5"/>
-      <c r="B431" s="7"/>
-      <c r="C431" t="s" s="20">
-        <v>43</v>
-      </c>
-      <c r="D431" t="s" s="35">
-        <v>44</v>
-      </c>
-      <c r="E431" s="13"/>
-      <c r="F431" s="2"/>
-      <c r="G431" s="2"/>
-      <c r="H431" s="2"/>
-    </row>
-    <row r="432" ht="15" customHeight="1">
-      <c r="A432" s="5"/>
-      <c r="B432" s="7"/>
-      <c r="C432" t="s" s="6">
-        <v>45</v>
-      </c>
-      <c r="D432" s="36">
-        <v>41648</v>
-      </c>
-      <c r="E432" s="13"/>
-      <c r="F432" s="2"/>
-      <c r="G432" s="2"/>
-      <c r="H432" s="2"/>
-    </row>
-    <row r="433" ht="15" customHeight="1">
-      <c r="A433" s="5"/>
-      <c r="B433" s="7"/>
-      <c r="C433" t="s" s="6">
-        <v>69</v>
-      </c>
-      <c r="D433" s="36">
-        <v>40919</v>
-      </c>
-      <c r="E433" s="13"/>
-      <c r="F433" s="2"/>
-      <c r="G433" s="2"/>
-      <c r="H433" s="2"/>
-    </row>
-    <row r="434" ht="15" customHeight="1">
-      <c r="A434" s="5"/>
-      <c r="B434" t="s" s="6">
-        <v>231</v>
-      </c>
-      <c r="C434" t="s" s="46">
-        <v>232</v>
-      </c>
-      <c r="D434" s="49"/>
-      <c r="E434" s="13"/>
-      <c r="F434" s="2"/>
-      <c r="G434" s="2"/>
-      <c r="H434" s="2"/>
-    </row>
-    <row r="435" ht="15" customHeight="1">
-      <c r="A435" s="5"/>
-      <c r="B435" t="s" s="6">
-        <v>233</v>
-      </c>
-      <c r="C435" s="7"/>
-      <c r="D435" s="7"/>
-      <c r="E435" s="13"/>
-      <c r="F435" s="2"/>
-      <c r="G435" s="2"/>
-      <c r="H435" s="2"/>
-    </row>
-    <row r="436" ht="15" customHeight="1">
-      <c r="A436" s="5"/>
-      <c r="B436" t="s" s="6">
-        <v>176</v>
-      </c>
-      <c r="C436" t="s" s="46">
-        <v>221</v>
-      </c>
-      <c r="D436" s="49"/>
-      <c r="E436" s="13"/>
-      <c r="F436" s="2"/>
-      <c r="G436" s="2"/>
-      <c r="H436" s="2"/>
-    </row>
-    <row r="437" ht="15" customHeight="1">
-      <c r="A437" s="5"/>
-      <c r="B437" t="s" s="6">
-        <v>72</v>
-      </c>
-      <c r="C437" t="s" s="6">
-        <v>73</v>
-      </c>
-      <c r="D437" s="7"/>
-      <c r="E437" s="13"/>
-      <c r="F437" s="2"/>
-      <c r="G437" s="2"/>
-      <c r="H437" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="135">
-    <mergeCell ref="C436:D436"/>
-    <mergeCell ref="B368:B371"/>
-    <mergeCell ref="B342:B349"/>
-    <mergeCell ref="C350:D350"/>
-    <mergeCell ref="B341:D341"/>
-    <mergeCell ref="D179:E179"/>
-    <mergeCell ref="D169:E169"/>
-    <mergeCell ref="D170:E170"/>
-    <mergeCell ref="D171:E171"/>
-    <mergeCell ref="D172:E172"/>
-    <mergeCell ref="D173:E173"/>
+  <mergeCells count="132">
+    <mergeCell ref="C427:D427"/>
+    <mergeCell ref="B360:B363"/>
+    <mergeCell ref="B334:B341"/>
+    <mergeCell ref="C342:D342"/>
+    <mergeCell ref="B333:D333"/>
     <mergeCell ref="D174:E174"/>
-    <mergeCell ref="D175:E175"/>
-    <mergeCell ref="D176:E176"/>
-    <mergeCell ref="B224:D224"/>
-    <mergeCell ref="B225:D225"/>
-    <mergeCell ref="D251:E251"/>
-    <mergeCell ref="D252:E252"/>
-    <mergeCell ref="D246:E246"/>
-    <mergeCell ref="D232:E232"/>
-    <mergeCell ref="D233:E233"/>
-    <mergeCell ref="D234:E234"/>
-    <mergeCell ref="B215:B223"/>
-    <mergeCell ref="B228:E228"/>
-    <mergeCell ref="D247:E247"/>
-    <mergeCell ref="D178:E178"/>
-    <mergeCell ref="B367:D367"/>
-    <mergeCell ref="D237:E237"/>
-    <mergeCell ref="B268:B296"/>
-    <mergeCell ref="B305:D305"/>
-    <mergeCell ref="B201:D201"/>
-    <mergeCell ref="B153:B179"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="B186:D186"/>
-    <mergeCell ref="D253:E253"/>
-    <mergeCell ref="D159:E159"/>
-    <mergeCell ref="D254:E254"/>
-    <mergeCell ref="D255:E255"/>
-    <mergeCell ref="D256:E256"/>
-    <mergeCell ref="D257:E257"/>
-    <mergeCell ref="D248:E248"/>
-    <mergeCell ref="D249:E249"/>
-    <mergeCell ref="D250:E250"/>
-    <mergeCell ref="D163:E163"/>
-    <mergeCell ref="D153:E153"/>
-    <mergeCell ref="D154:E154"/>
-    <mergeCell ref="D155:E155"/>
-    <mergeCell ref="D156:E156"/>
-    <mergeCell ref="D157:E157"/>
-    <mergeCell ref="D158:E158"/>
-    <mergeCell ref="D177:E177"/>
     <mergeCell ref="D164:E164"/>
     <mergeCell ref="D165:E165"/>
     <mergeCell ref="D166:E166"/>
     <mergeCell ref="D167:E167"/>
     <mergeCell ref="D168:E168"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="D169:E169"/>
+    <mergeCell ref="D170:E170"/>
+    <mergeCell ref="D171:E171"/>
+    <mergeCell ref="B219:D219"/>
+    <mergeCell ref="B220:D220"/>
+    <mergeCell ref="D245:E245"/>
+    <mergeCell ref="D246:E246"/>
+    <mergeCell ref="D240:E240"/>
+    <mergeCell ref="D227:E227"/>
+    <mergeCell ref="D228:E228"/>
+    <mergeCell ref="B210:B218"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="D241:E241"/>
+    <mergeCell ref="D173:E173"/>
+    <mergeCell ref="B359:D359"/>
+    <mergeCell ref="D231:E231"/>
+    <mergeCell ref="B262:B289"/>
+    <mergeCell ref="B298:D298"/>
+    <mergeCell ref="B196:D196"/>
+    <mergeCell ref="B149:B174"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="B181:D181"/>
+    <mergeCell ref="D247:E247"/>
+    <mergeCell ref="D154:E154"/>
+    <mergeCell ref="D248:E248"/>
+    <mergeCell ref="D249:E249"/>
+    <mergeCell ref="D250:E250"/>
+    <mergeCell ref="D251:E251"/>
+    <mergeCell ref="D242:E242"/>
+    <mergeCell ref="D243:E243"/>
+    <mergeCell ref="D244:E244"/>
+    <mergeCell ref="D158:E158"/>
+    <mergeCell ref="D149:E149"/>
+    <mergeCell ref="D150:E150"/>
+    <mergeCell ref="D151:E151"/>
+    <mergeCell ref="D152:E152"/>
+    <mergeCell ref="D153:E153"/>
+    <mergeCell ref="D172:E172"/>
+    <mergeCell ref="D159:E159"/>
+    <mergeCell ref="D160:E160"/>
+    <mergeCell ref="D161:E161"/>
+    <mergeCell ref="D162:E162"/>
+    <mergeCell ref="D163:E163"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D86:F86"/>
     <mergeCell ref="D87:F87"/>
     <mergeCell ref="D88:F88"/>
     <mergeCell ref="D89:F89"/>
     <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C69:D69"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B152:E152"/>
-    <mergeCell ref="B4:B29"/>
-    <mergeCell ref="B214:D214"/>
-    <mergeCell ref="B202:B210"/>
-    <mergeCell ref="C211:D211"/>
-    <mergeCell ref="C212:D212"/>
-    <mergeCell ref="B187:B195"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B4:B28"/>
+    <mergeCell ref="B209:D209"/>
+    <mergeCell ref="B197:B205"/>
+    <mergeCell ref="C206:D206"/>
+    <mergeCell ref="C207:D207"/>
+    <mergeCell ref="B182:B190"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
     <mergeCell ref="D75:F75"/>
     <mergeCell ref="D76:F76"/>
     <mergeCell ref="D77:F77"/>
     <mergeCell ref="D78:F78"/>
     <mergeCell ref="D79:F79"/>
     <mergeCell ref="D80:F80"/>
+    <mergeCell ref="B40:B67"/>
+    <mergeCell ref="C192:D192"/>
     <mergeCell ref="D81:F81"/>
     <mergeCell ref="D82:F82"/>
     <mergeCell ref="D83:F83"/>
-    <mergeCell ref="B41:B69"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="B404:D404"/>
-    <mergeCell ref="B405:B433"/>
-    <mergeCell ref="C435:D435"/>
-    <mergeCell ref="C437:D437"/>
-    <mergeCell ref="C434:D434"/>
-    <mergeCell ref="B109:B135"/>
-    <mergeCell ref="B75:B101"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="B139:B146"/>
-    <mergeCell ref="B138:D138"/>
-    <mergeCell ref="B147:D147"/>
-    <mergeCell ref="B148:D148"/>
-    <mergeCell ref="B149:D149"/>
+    <mergeCell ref="B396:D396"/>
+    <mergeCell ref="B397:B424"/>
+    <mergeCell ref="C426:D426"/>
+    <mergeCell ref="C428:D428"/>
+    <mergeCell ref="C425:D425"/>
+    <mergeCell ref="B106:B131"/>
+    <mergeCell ref="B73:B98"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="B135:B142"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="B143:D143"/>
+    <mergeCell ref="B144:D144"/>
+    <mergeCell ref="B145:D145"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="D93:F93"/>
     <mergeCell ref="D94:F94"/>
     <mergeCell ref="D95:F95"/>
-    <mergeCell ref="B108:D108"/>
     <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="D160:E160"/>
-    <mergeCell ref="D161:E161"/>
-    <mergeCell ref="D162:E162"/>
+    <mergeCell ref="D155:E155"/>
+    <mergeCell ref="D156:E156"/>
+    <mergeCell ref="D157:E157"/>
+    <mergeCell ref="D232:E232"/>
+    <mergeCell ref="D233:E233"/>
+    <mergeCell ref="D224:E224"/>
+    <mergeCell ref="D225:E225"/>
+    <mergeCell ref="D226:E226"/>
+    <mergeCell ref="B345:D345"/>
+    <mergeCell ref="C356:D356"/>
+    <mergeCell ref="C355:D355"/>
+    <mergeCell ref="C354:D354"/>
+    <mergeCell ref="B346:B353"/>
+    <mergeCell ref="B299:B326"/>
+    <mergeCell ref="B224:B251"/>
+    <mergeCell ref="B261:D261"/>
+    <mergeCell ref="D237:E237"/>
     <mergeCell ref="D238:E238"/>
     <mergeCell ref="D239:E239"/>
     <mergeCell ref="D229:E229"/>
     <mergeCell ref="D230:E230"/>
-    <mergeCell ref="D231:E231"/>
-    <mergeCell ref="B353:D353"/>
-    <mergeCell ref="C364:D364"/>
-    <mergeCell ref="C363:D363"/>
-    <mergeCell ref="C362:D362"/>
-    <mergeCell ref="B354:B361"/>
-    <mergeCell ref="B306:B334"/>
-    <mergeCell ref="B229:B257"/>
-    <mergeCell ref="B267:D267"/>
-    <mergeCell ref="D243:E243"/>
-    <mergeCell ref="D244:E244"/>
-    <mergeCell ref="D245:E245"/>
+    <mergeCell ref="D234:E234"/>
     <mergeCell ref="D235:E235"/>
     <mergeCell ref="D236:E236"/>
-    <mergeCell ref="D240:E240"/>
-    <mergeCell ref="D241:E241"/>
-    <mergeCell ref="D242:E242"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
